--- a/Excel/Validasi/Hasil_Pengujian_Map_1_128_avg_length.xlsx
+++ b/Excel/Validasi/Hasil_Pengujian_Map_1_128_avg_length.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEMHAS\TA_Python_Server\Excel\Validasi\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B759D762-FA6F-4882-AC7C-E4072AC48D15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Waktu Pencarian" sheetId="1" r:id="rId1"/>
@@ -14,7 +20,7 @@
     <sheet name="Jumlah Close" sheetId="5" r:id="rId5"/>
     <sheet name="Jumlah Belok" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -237,8 +243,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -301,13 +307,1540 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="id-ID"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>A*</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$2:$F$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>4.9179999999999992E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.0006E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.9612999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.13250819999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A2B1-4D75-8551-FB4AFADF9BB4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>BDS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$3:$F$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>3.1330000000000003E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.3492999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.1652E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.2051600000000001E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-A2B1-4D75-8551-FB4AFADF9BB4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>BRC</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$4:$F$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>4.5659999999999999E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.1857999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.72503E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.18647659999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-A2B1-4D75-8551-FB4AFADF9BB4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>GL</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$5:$F$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>4.2789999999999999E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.3919000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.65019E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.1149251</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-A2B1-4D75-8551-FB4AFADF9BB4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>JPS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$6:$F$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>3.6749999999999999E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0816000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.5506000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.29208E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-A2B1-4D75-8551-FB4AFADF9BB4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PPO</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$7:$F$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>5.9119999999999995E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.1369000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.9774799999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.13209070000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-A2B1-4D75-8551-FB4AFADF9BB4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TPF</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$8:$F$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>5.350000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.8988E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.8714100000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.12540699999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-A2B1-4D75-8551-FB4AFADF9BB4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1087410447"/>
+        <c:axId val="1087413807"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1087410447"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="id-ID"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="id-ID"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1087413807"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1087413807"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="id-ID"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="id-ID"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1087410447"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="id-ID"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="id-ID"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>34290</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>34290</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9AF63F3B-A941-1ABF-DF4B-DE83F87300AC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -345,7 +1878,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -379,6 +1912,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -413,9 +1947,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -588,11 +2123,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -615,7 +2150,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -623,22 +2158,22 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>0.0004917999999999999</v>
+        <v>4.9179999999999992E-4</v>
       </c>
       <c r="D2">
-        <v>0.0030006</v>
+        <v>3.0006E-3</v>
       </c>
       <c r="E2">
-        <v>0.019613</v>
+        <v>1.9612999999999998E-2</v>
       </c>
       <c r="F2">
-        <v>0.1325082</v>
+        <v>0.13250819999999999</v>
       </c>
       <c r="G2">
-        <v>0.0389034</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>3.8903399999999998E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -646,22 +2181,22 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>0.0003133</v>
+        <v>3.1330000000000003E-4</v>
       </c>
       <c r="D3">
-        <v>0.0013493</v>
+        <v>1.3492999999999999E-3</v>
       </c>
       <c r="E3">
-        <v>0.0051652</v>
+        <v>5.1652E-3</v>
       </c>
       <c r="F3">
-        <v>0.0220516</v>
+        <v>2.2051600000000001E-2</v>
       </c>
       <c r="G3">
-        <v>0.00721985</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>7.2198499999999999E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -669,22 +2204,22 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>0.0004566</v>
+        <v>4.5659999999999999E-4</v>
       </c>
       <c r="D4">
-        <v>0.0021858</v>
+        <v>2.1857999999999999E-3</v>
       </c>
       <c r="E4">
-        <v>0.0172503</v>
+        <v>1.72503E-2</v>
       </c>
       <c r="F4">
-        <v>0.1864766</v>
+        <v>0.18647659999999999</v>
       </c>
       <c r="G4">
-        <v>0.05159232500000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>5.1592325000000008E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -692,22 +2227,22 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>0.0004279</v>
+        <v>4.2789999999999999E-4</v>
       </c>
       <c r="D5">
-        <v>0.0023919</v>
+        <v>2.3919000000000002E-3</v>
       </c>
       <c r="E5">
-        <v>0.0165019</v>
+        <v>1.65019E-2</v>
       </c>
       <c r="F5">
         <v>0.1149251</v>
       </c>
       <c r="G5">
-        <v>0.0335617</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>3.35617E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -715,22 +2250,22 @@
         <v>11</v>
       </c>
       <c r="C6">
-        <v>0.0003675</v>
+        <v>3.6749999999999999E-4</v>
       </c>
       <c r="D6">
-        <v>0.0010816</v>
+        <v>1.0816000000000001E-3</v>
       </c>
       <c r="E6">
-        <v>0.0035506</v>
+        <v>3.5506000000000001E-3</v>
       </c>
       <c r="F6">
-        <v>0.0129208</v>
+        <v>1.29208E-2</v>
       </c>
       <c r="G6">
-        <v>0.004480125</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>4.4801249999999997E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -738,22 +2273,22 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>0.0005912</v>
+        <v>5.9119999999999995E-4</v>
       </c>
       <c r="D7">
-        <v>0.0031369</v>
+        <v>3.1369000000000002E-3</v>
       </c>
       <c r="E7">
-        <v>0.0197748</v>
+        <v>1.9774799999999999E-2</v>
       </c>
       <c r="F7">
-        <v>0.1320907</v>
+        <v>0.13209070000000001</v>
       </c>
       <c r="G7">
-        <v>0.0388984</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>3.88984E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -761,22 +2296,22 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>0.0005350000000000001</v>
+        <v>5.350000000000001E-4</v>
       </c>
       <c r="D8">
-        <v>0.0028988</v>
+        <v>2.8988E-3</v>
       </c>
       <c r="E8">
-        <v>0.0187141</v>
+        <v>1.8714100000000001E-2</v>
       </c>
       <c r="F8">
-        <v>0.125407</v>
+        <v>0.12540699999999999</v>
       </c>
       <c r="G8">
-        <v>0.036888725</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>3.6888724999999997E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -784,22 +2319,22 @@
         <v>14</v>
       </c>
       <c r="C9">
-        <v>0.0004888</v>
+        <v>4.8879999999999996E-4</v>
       </c>
       <c r="D9">
-        <v>0.0018497</v>
+        <v>1.8496999999999999E-3</v>
       </c>
       <c r="E9">
-        <v>0.008888400000000001</v>
+        <v>8.8884000000000012E-3</v>
       </c>
       <c r="F9">
-        <v>0.05528620000000001</v>
+        <v>5.5286200000000008E-2</v>
       </c>
       <c r="G9">
-        <v>0.016628275</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>1.6628275000000001E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -807,22 +2342,22 @@
         <v>15</v>
       </c>
       <c r="C10">
-        <v>0.0003373</v>
+        <v>3.3730000000000001E-4</v>
       </c>
       <c r="D10">
-        <v>0.0014367</v>
+        <v>1.4367E-3</v>
       </c>
       <c r="E10">
-        <v>0.0061828</v>
+        <v>6.1827999999999996E-3</v>
       </c>
       <c r="F10">
-        <v>0.0261967</v>
+        <v>2.61967E-2</v>
       </c>
       <c r="G10">
-        <v>0.008538375000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>8.5383750000000008E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -830,22 +2365,22 @@
         <v>16</v>
       </c>
       <c r="C11">
-        <v>0.0003606</v>
+        <v>3.6059999999999998E-4</v>
       </c>
       <c r="D11">
-        <v>0.0014064</v>
+        <v>1.4063999999999999E-3</v>
       </c>
       <c r="E11">
-        <v>0.0056706</v>
+        <v>5.6705999999999996E-3</v>
       </c>
       <c r="F11">
-        <v>0.0230846</v>
+        <v>2.30846E-2</v>
       </c>
       <c r="G11">
-        <v>0.00763055</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>7.6305499999999998E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -853,22 +2388,22 @@
         <v>17</v>
       </c>
       <c r="C12">
-        <v>0.0003624</v>
+        <v>3.6240000000000003E-4</v>
       </c>
       <c r="D12">
-        <v>0.0015202</v>
+        <v>1.5202E-3</v>
       </c>
       <c r="E12">
-        <v>0.005672399999999999</v>
+        <v>5.6723999999999993E-3</v>
       </c>
       <c r="F12">
-        <v>0.0227775</v>
+        <v>2.2777499999999999E-2</v>
       </c>
       <c r="G12">
-        <v>0.007583125</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>7.5831249999999996E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2</v>
       </c>
@@ -876,22 +2411,22 @@
         <v>18</v>
       </c>
       <c r="C13">
-        <v>0.0004934999999999999</v>
+        <v>4.9349999999999991E-4</v>
       </c>
       <c r="D13">
-        <v>0.0023208</v>
+        <v>2.3208E-3</v>
       </c>
       <c r="E13">
-        <v>0.0174965</v>
+        <v>1.7496500000000002E-2</v>
       </c>
       <c r="F13">
         <v>0.188642</v>
       </c>
       <c r="G13">
-        <v>0.0522382</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>5.2238199999999999E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -899,22 +2434,22 @@
         <v>19</v>
       </c>
       <c r="C14">
-        <v>0.0005176</v>
+        <v>5.176E-4</v>
       </c>
       <c r="D14">
-        <v>0.0022897</v>
+        <v>2.2897E-3</v>
       </c>
       <c r="E14">
-        <v>0.0172479</v>
+        <v>1.72479E-2</v>
       </c>
       <c r="F14">
-        <v>0.1753475</v>
+        <v>0.17534749999999999</v>
       </c>
       <c r="G14">
-        <v>0.048850675</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>4.8850675000000003E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -922,22 +2457,22 @@
         <v>20</v>
       </c>
       <c r="C15">
-        <v>0.0005542</v>
+        <v>5.5420000000000003E-4</v>
       </c>
       <c r="D15">
-        <v>0.0029753</v>
+        <v>2.9753000000000002E-3</v>
       </c>
       <c r="E15">
-        <v>0.0217295</v>
+        <v>2.1729499999999999E-2</v>
       </c>
       <c r="F15">
-        <v>0.222127</v>
+        <v>0.22212699999999999</v>
       </c>
       <c r="G15">
-        <v>0.06184650000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>6.1846500000000013E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2</v>
       </c>
@@ -945,22 +2480,22 @@
         <v>21</v>
       </c>
       <c r="C16">
-        <v>0.0004581</v>
+        <v>4.5810000000000002E-4</v>
       </c>
       <c r="D16">
-        <v>0.0025499</v>
+        <v>2.5498999999999999E-3</v>
       </c>
       <c r="E16">
-        <v>0.0168301</v>
+        <v>1.6830100000000001E-2</v>
       </c>
       <c r="F16">
         <v>0.1159927</v>
       </c>
       <c r="G16">
-        <v>0.0339577</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>3.39577E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2</v>
       </c>
@@ -968,22 +2503,22 @@
         <v>22</v>
       </c>
       <c r="C17">
-        <v>0.0005802000000000001</v>
+        <v>5.8020000000000012E-4</v>
       </c>
       <c r="D17">
-        <v>0.003556300000000001</v>
+        <v>3.556300000000001E-3</v>
       </c>
       <c r="E17">
-        <v>0.016619</v>
+        <v>1.6618999999999998E-2</v>
       </c>
       <c r="F17">
         <v>0.1112421</v>
       </c>
       <c r="G17">
-        <v>0.03299940000000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>3.2999400000000012E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2</v>
       </c>
@@ -991,22 +2526,22 @@
         <v>23</v>
       </c>
       <c r="C18">
-        <v>0.0003708</v>
+        <v>3.7080000000000001E-4</v>
       </c>
       <c r="D18">
-        <v>0.0009771999999999999</v>
+        <v>9.771999999999999E-4</v>
       </c>
       <c r="E18">
-        <v>0.003033</v>
+        <v>3.0330000000000001E-3</v>
       </c>
       <c r="F18">
-        <v>0.0114609</v>
+        <v>1.14609E-2</v>
       </c>
       <c r="G18">
-        <v>0.003960475</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>3.9604749999999998E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -1014,22 +2549,22 @@
         <v>24</v>
       </c>
       <c r="C19">
-        <v>0.0003208</v>
+        <v>3.2079999999999999E-4</v>
       </c>
       <c r="D19">
-        <v>0.0010382</v>
+        <v>1.0382E-3</v>
       </c>
       <c r="E19">
-        <v>0.003272</v>
+        <v>3.2720000000000002E-3</v>
       </c>
       <c r="F19">
-        <v>0.0124311</v>
+        <v>1.24311E-2</v>
       </c>
       <c r="G19">
-        <v>0.004265525</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>4.265525E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -1037,22 +2572,22 @@
         <v>25</v>
       </c>
       <c r="C20">
-        <v>0.0003701</v>
+        <v>3.701E-4</v>
       </c>
       <c r="D20">
-        <v>0.0011515</v>
+        <v>1.1515E-3</v>
       </c>
       <c r="E20">
-        <v>0.0037772</v>
+        <v>3.7772000000000001E-3</v>
       </c>
       <c r="F20">
-        <v>0.0140915</v>
+        <v>1.40915E-2</v>
       </c>
       <c r="G20">
-        <v>0.004847575</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>4.8475749999999998E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
@@ -1060,22 +2595,22 @@
         <v>26</v>
       </c>
       <c r="C21">
-        <v>0.0004107000000000001</v>
+        <v>4.1070000000000012E-4</v>
       </c>
       <c r="D21">
-        <v>0.0012167</v>
+        <v>1.2167E-3</v>
       </c>
       <c r="E21">
-        <v>0.003600299999999999</v>
+        <v>3.600299999999999E-3</v>
       </c>
       <c r="F21">
-        <v>0.0129089</v>
+        <v>1.2908899999999999E-2</v>
       </c>
       <c r="G21">
-        <v>0.00453415</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>4.5341499999999998E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -1083,22 +2618,22 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>0.0003565</v>
+        <v>3.5649999999999999E-4</v>
       </c>
       <c r="D22">
-        <v>0.0012822</v>
+        <v>1.2822E-3</v>
       </c>
       <c r="E22">
-        <v>0.0031847</v>
+        <v>3.1846999999999999E-3</v>
       </c>
       <c r="F22">
-        <v>0.0114371</v>
+        <v>1.14371E-2</v>
       </c>
       <c r="G22">
-        <v>0.004065125</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>4.0651250000000002E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2</v>
       </c>
@@ -1106,22 +2641,22 @@
         <v>28</v>
       </c>
       <c r="C23">
-        <v>0.0005857</v>
+        <v>5.8569999999999998E-4</v>
       </c>
       <c r="D23">
-        <v>0.0030051</v>
+        <v>3.0051000000000001E-3</v>
       </c>
       <c r="E23">
-        <v>0.0188002</v>
+        <v>1.88002E-2</v>
       </c>
       <c r="F23">
         <v>0.1267848</v>
       </c>
       <c r="G23">
-        <v>0.03729394999999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>3.7293949999999992E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>3</v>
       </c>
@@ -1129,22 +2664,22 @@
         <v>29</v>
       </c>
       <c r="C24">
-        <v>0.0005301</v>
+        <v>5.3010000000000004E-4</v>
       </c>
       <c r="D24">
-        <v>0.0019467</v>
+        <v>1.9467E-3</v>
       </c>
       <c r="E24">
-        <v>0.009185599999999999</v>
+        <v>9.1855999999999986E-3</v>
       </c>
       <c r="F24">
-        <v>0.0562427</v>
+        <v>5.62427E-2</v>
       </c>
       <c r="G24">
-        <v>0.016976275</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>1.6976274999999999E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>3</v>
       </c>
@@ -1152,22 +2687,22 @@
         <v>30</v>
       </c>
       <c r="C25">
-        <v>0.0005136</v>
+        <v>5.1360000000000002E-4</v>
       </c>
       <c r="D25">
-        <v>0.0020586</v>
+        <v>2.0585999999999998E-3</v>
       </c>
       <c r="E25">
-        <v>0.009476799999999999</v>
+        <v>9.4767999999999988E-3</v>
       </c>
       <c r="F25">
-        <v>0.0561227</v>
+        <v>5.6122699999999998E-2</v>
       </c>
       <c r="G25">
-        <v>0.017042925</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>1.7042925E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>3</v>
       </c>
@@ -1175,22 +2710,22 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>0.0005476000000000001</v>
+        <v>5.4760000000000008E-4</v>
       </c>
       <c r="D26">
-        <v>0.0030069</v>
+        <v>3.0068999999999999E-3</v>
       </c>
       <c r="E26">
-        <v>0.0142595</v>
+        <v>1.42595E-2</v>
       </c>
       <c r="F26">
-        <v>0.092566</v>
+        <v>9.2565999999999996E-2</v>
       </c>
       <c r="G26">
-        <v>0.027595</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>2.7595000000000001E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>3</v>
       </c>
@@ -1198,22 +2733,22 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>0.0004094</v>
+        <v>4.0939999999999998E-4</v>
       </c>
       <c r="D27">
-        <v>0.0016725</v>
+        <v>1.6724999999999999E-3</v>
       </c>
       <c r="E27">
-        <v>0.0064419</v>
+        <v>6.4419000000000004E-3</v>
       </c>
       <c r="F27">
-        <v>0.0272127</v>
+        <v>2.7212699999999999E-2</v>
       </c>
       <c r="G27">
-        <v>0.008934124999999999</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>8.9341249999999994E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -1221,22 +2756,22 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>0.0003836</v>
+        <v>3.836E-4</v>
       </c>
       <c r="D28">
-        <v>0.0015914</v>
+        <v>1.5914E-3</v>
       </c>
       <c r="E28">
-        <v>0.0065758</v>
+        <v>6.5757999999999997E-3</v>
       </c>
       <c r="F28">
-        <v>0.0271555</v>
+        <v>2.7155499999999999E-2</v>
       </c>
       <c r="G28">
-        <v>0.008926574999999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>8.9265749999999991E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>3</v>
       </c>
@@ -1244,22 +2779,22 @@
         <v>34</v>
       </c>
       <c r="C29">
-        <v>0.000419</v>
+        <v>4.1899999999999999E-4</v>
       </c>
       <c r="D29">
-        <v>0.0015942</v>
+        <v>1.5942E-3</v>
       </c>
       <c r="E29">
-        <v>0.0059845</v>
+        <v>5.9845000000000002E-3</v>
       </c>
       <c r="F29">
-        <v>0.023905</v>
+        <v>2.3904999999999999E-2</v>
       </c>
       <c r="G29">
-        <v>0.007975675000000002</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>7.9756750000000015E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
@@ -1267,22 +2802,22 @@
         <v>35</v>
       </c>
       <c r="C30">
-        <v>0.0005853</v>
+        <v>5.8529999999999997E-4</v>
       </c>
       <c r="D30">
-        <v>0.0024127</v>
+        <v>2.4126999999999998E-3</v>
       </c>
       <c r="E30">
-        <v>0.0173358</v>
+        <v>1.7335799999999998E-2</v>
       </c>
       <c r="F30">
         <v>0.1762128</v>
       </c>
       <c r="G30">
-        <v>0.04913665</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>4.9136649999999997E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
@@ -1290,22 +2825,22 @@
         <v>36</v>
       </c>
       <c r="C31">
-        <v>0.0005932999999999999</v>
+        <v>5.9329999999999995E-4</v>
       </c>
       <c r="D31">
-        <v>0.0030467</v>
+        <v>3.0466999999999998E-3</v>
       </c>
       <c r="E31">
-        <v>0.0218867</v>
+        <v>2.1886699999999999E-2</v>
       </c>
       <c r="F31">
         <v>0.2224198</v>
       </c>
       <c r="G31">
-        <v>0.061986625</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>6.1986624999999997E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
@@ -1313,22 +2848,22 @@
         <v>37</v>
       </c>
       <c r="C32">
-        <v>0.0006016000000000001</v>
+        <v>6.0160000000000009E-4</v>
       </c>
       <c r="D32">
-        <v>0.0029675</v>
+        <v>2.9675000000000001E-3</v>
       </c>
       <c r="E32">
-        <v>0.0218362</v>
+        <v>2.18362E-2</v>
       </c>
       <c r="F32">
-        <v>0.217385</v>
+        <v>0.21738499999999999</v>
       </c>
       <c r="G32">
-        <v>0.060697575</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+        <v>6.0697574999999997E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>3</v>
       </c>
@@ -1336,22 +2871,22 @@
         <v>38</v>
       </c>
       <c r="C33">
-        <v>0.0006204</v>
+        <v>6.2040000000000001E-4</v>
       </c>
       <c r="D33">
-        <v>0.004153</v>
+        <v>4.1529999999999996E-3</v>
       </c>
       <c r="E33">
-        <v>0.0170915</v>
+        <v>1.7091499999999999E-2</v>
       </c>
       <c r="F33">
-        <v>0.1122733</v>
+        <v>0.11227330000000001</v>
       </c>
       <c r="G33">
-        <v>0.03353455</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>3.3534550000000003E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>3</v>
       </c>
@@ -1359,22 +2894,22 @@
         <v>39</v>
       </c>
       <c r="C34">
-        <v>0.0004412</v>
+        <v>4.4119999999999999E-4</v>
       </c>
       <c r="D34">
-        <v>0.001106</v>
+        <v>1.106E-3</v>
       </c>
       <c r="E34">
-        <v>0.0034586</v>
+        <v>3.4586E-3</v>
       </c>
       <c r="F34">
-        <v>0.012142</v>
+        <v>1.2142E-2</v>
       </c>
       <c r="G34">
-        <v>0.004286949999999999</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+        <v>4.2869499999999986E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>3</v>
       </c>
@@ -1382,22 +2917,22 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>0.0003275</v>
+        <v>3.2749999999999999E-4</v>
       </c>
       <c r="D35">
-        <v>0.0010366</v>
+        <v>1.0365999999999999E-3</v>
       </c>
       <c r="E35">
-        <v>0.0030801</v>
+        <v>3.0801000000000001E-3</v>
       </c>
       <c r="F35">
-        <v>0.0118299</v>
+        <v>1.1829900000000001E-2</v>
       </c>
       <c r="G35">
-        <v>0.004068525</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+        <v>4.0685249999999999E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>3</v>
       </c>
@@ -1405,22 +2940,22 @@
         <v>41</v>
       </c>
       <c r="C36">
-        <v>0.0004182</v>
+        <v>4.1819999999999997E-4</v>
       </c>
       <c r="D36">
-        <v>0.0010701</v>
+        <v>1.0701E-3</v>
       </c>
       <c r="E36">
-        <v>0.0031381</v>
+        <v>3.1381E-3</v>
       </c>
       <c r="F36">
-        <v>0.0116473</v>
+        <v>1.1647299999999999E-2</v>
       </c>
       <c r="G36">
-        <v>0.004068425000000001</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+        <v>4.0684250000000014E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>3</v>
       </c>
@@ -1428,22 +2963,22 @@
         <v>42</v>
       </c>
       <c r="C37">
-        <v>0.0004134</v>
+        <v>4.1340000000000002E-4</v>
       </c>
       <c r="D37">
-        <v>0.0012048</v>
+        <v>1.2048E-3</v>
       </c>
       <c r="E37">
-        <v>0.0046449</v>
+        <v>4.6449000000000004E-3</v>
       </c>
       <c r="F37">
-        <v>0.0203688</v>
+        <v>2.0368799999999999E-2</v>
       </c>
       <c r="G37">
-        <v>0.006657975</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+        <v>6.657975E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>3</v>
       </c>
@@ -1451,22 +2986,22 @@
         <v>43</v>
       </c>
       <c r="C38">
-        <v>0.0003688</v>
+        <v>3.6880000000000002E-4</v>
       </c>
       <c r="D38">
-        <v>0.001075</v>
+        <v>1.075E-3</v>
       </c>
       <c r="E38">
-        <v>0.003381400000000001</v>
+        <v>3.381400000000001E-3</v>
       </c>
       <c r="F38">
-        <v>0.0125874</v>
+        <v>1.25874E-2</v>
       </c>
       <c r="G38">
-        <v>0.00435315</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+        <v>4.3531500000000001E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>3</v>
       </c>
@@ -1474,22 +3009,22 @@
         <v>44</v>
       </c>
       <c r="C39">
-        <v>0.0003561</v>
+        <v>3.5609999999999998E-4</v>
       </c>
       <c r="D39">
-        <v>0.0010607</v>
+        <v>1.0606999999999999E-3</v>
       </c>
       <c r="E39">
-        <v>0.0032945</v>
+        <v>3.2945000000000001E-3</v>
       </c>
       <c r="F39">
-        <v>0.0124883</v>
+        <v>1.2488300000000001E-2</v>
       </c>
       <c r="G39">
-        <v>0.004299900000000001</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+        <v>4.2999000000000006E-3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3</v>
       </c>
@@ -1497,22 +3032,22 @@
         <v>45</v>
       </c>
       <c r="C40">
-        <v>0.0003326</v>
+        <v>3.3260000000000001E-4</v>
       </c>
       <c r="D40">
-        <v>0.0010706</v>
+        <v>1.0705999999999999E-3</v>
       </c>
       <c r="E40">
-        <v>0.0030184</v>
+        <v>3.0184000000000001E-3</v>
       </c>
       <c r="F40">
-        <v>0.0132772</v>
+        <v>1.3277199999999999E-2</v>
       </c>
       <c r="G40">
-        <v>0.0044247</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+        <v>4.4247000000000002E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>3</v>
       </c>
@@ -1520,22 +3055,22 @@
         <v>46</v>
       </c>
       <c r="C41">
-        <v>0.0004115</v>
+        <v>4.1149999999999997E-4</v>
       </c>
       <c r="D41">
-        <v>0.0012287</v>
+        <v>1.2287000000000001E-3</v>
       </c>
       <c r="E41">
-        <v>0.0038426</v>
+        <v>3.8425999999999998E-3</v>
       </c>
       <c r="F41">
-        <v>0.014215</v>
+        <v>1.4215E-2</v>
       </c>
       <c r="G41">
-        <v>0.00492445</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+        <v>4.9244500000000004E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>3</v>
       </c>
@@ -1543,22 +3078,22 @@
         <v>47</v>
       </c>
       <c r="C42">
-        <v>0.0003965</v>
+        <v>3.9649999999999999E-4</v>
       </c>
       <c r="D42">
-        <v>0.001176</v>
+        <v>1.176E-3</v>
       </c>
       <c r="E42">
-        <v>0.0038327</v>
+        <v>3.8327000000000001E-3</v>
       </c>
       <c r="F42">
-        <v>0.0140857</v>
+        <v>1.40857E-2</v>
       </c>
       <c r="G42">
-        <v>0.004872725</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
+        <v>4.8727249999999996E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3</v>
       </c>
@@ -1566,22 +3101,22 @@
         <v>48</v>
       </c>
       <c r="C43">
-        <v>0.0003989999999999999</v>
+        <v>3.9899999999999989E-4</v>
       </c>
       <c r="D43">
-        <v>0.0012118</v>
+        <v>1.2118000000000001E-3</v>
       </c>
       <c r="E43">
-        <v>0.003259500000000001</v>
+        <v>3.2595000000000011E-3</v>
       </c>
       <c r="F43">
-        <v>0.0114999</v>
+        <v>1.14999E-2</v>
       </c>
       <c r="G43">
-        <v>0.00409255</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+        <v>4.0925500000000004E-3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>4</v>
       </c>
@@ -1589,22 +3124,22 @@
         <v>49</v>
       </c>
       <c r="C44">
-        <v>0.0005765999999999999</v>
+        <v>5.7659999999999992E-4</v>
       </c>
       <c r="D44">
-        <v>0.002117200000000001</v>
+        <v>2.1172000000000009E-3</v>
       </c>
       <c r="E44">
-        <v>0.009887700000000001</v>
+        <v>9.887700000000001E-3</v>
       </c>
       <c r="F44">
-        <v>0.0566571</v>
+        <v>5.6657100000000002E-2</v>
       </c>
       <c r="G44">
-        <v>0.01730965</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+        <v>1.7309649999999999E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>4</v>
       </c>
@@ -1612,22 +3147,22 @@
         <v>50</v>
       </c>
       <c r="C45">
-        <v>0.0006001</v>
+        <v>6.001E-4</v>
       </c>
       <c r="D45">
-        <v>0.0030012</v>
+        <v>3.0011999999999999E-3</v>
       </c>
       <c r="E45">
-        <v>0.0145758</v>
+        <v>1.45758E-2</v>
       </c>
       <c r="F45">
-        <v>0.0936124</v>
+        <v>9.3612399999999998E-2</v>
       </c>
       <c r="G45">
-        <v>0.027947375</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
+        <v>2.7947375E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>4</v>
       </c>
@@ -1635,22 +3170,22 @@
         <v>51</v>
       </c>
       <c r="C46">
-        <v>0.0006345</v>
+        <v>6.3449999999999997E-4</v>
       </c>
       <c r="D46">
-        <v>0.0030347</v>
+        <v>3.0347E-3</v>
       </c>
       <c r="E46">
-        <v>0.0149877</v>
+        <v>1.49877E-2</v>
       </c>
       <c r="F46">
-        <v>0.0895137</v>
+        <v>8.9513700000000002E-2</v>
       </c>
       <c r="G46">
-        <v>0.02704265</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
+        <v>2.7042650000000001E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>4</v>
       </c>
@@ -1658,22 +3193,22 @@
         <v>52</v>
       </c>
       <c r="C47">
-        <v>0.0004358</v>
+        <v>4.3580000000000002E-4</v>
       </c>
       <c r="D47">
-        <v>0.0017495</v>
+        <v>1.7495E-3</v>
       </c>
       <c r="E47">
-        <v>0.006848299999999999</v>
+        <v>6.848299999999999E-3</v>
       </c>
       <c r="F47">
-        <v>0.0281361</v>
+        <v>2.8136100000000001E-2</v>
       </c>
       <c r="G47">
-        <v>0.009292425</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
+        <v>9.292425E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>4</v>
       </c>
@@ -1681,22 +3216,22 @@
         <v>53</v>
       </c>
       <c r="C48">
-        <v>0.0006459</v>
+        <v>6.4590000000000003E-4</v>
       </c>
       <c r="D48">
-        <v>0.0030918</v>
+        <v>3.0918E-3</v>
       </c>
       <c r="E48">
-        <v>0.0220738</v>
+        <v>2.2073800000000001E-2</v>
       </c>
       <c r="F48">
         <v>0.2182151</v>
       </c>
       <c r="G48">
-        <v>0.06100665</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+        <v>6.1006650000000003E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>4</v>
       </c>
@@ -1704,22 +3239,22 @@
         <v>54</v>
       </c>
       <c r="C49">
-        <v>0.0005031</v>
+        <v>5.0310000000000003E-4</v>
       </c>
       <c r="D49">
-        <v>0.0011891</v>
+        <v>1.1891E-3</v>
       </c>
       <c r="E49">
-        <v>0.0034122</v>
+        <v>3.4122000000000002E-3</v>
       </c>
       <c r="F49">
-        <v>0.0122171</v>
+        <v>1.22171E-2</v>
       </c>
       <c r="G49">
-        <v>0.004330375000000001</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
+        <v>4.3303750000000009E-3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>4</v>
       </c>
@@ -1727,22 +3262,22 @@
         <v>55</v>
       </c>
       <c r="C50">
-        <v>0.0004328</v>
+        <v>4.328E-4</v>
       </c>
       <c r="D50">
-        <v>0.0013237</v>
+        <v>1.3236999999999999E-3</v>
       </c>
       <c r="E50">
-        <v>0.0033126</v>
+        <v>3.3126000000000002E-3</v>
       </c>
       <c r="F50">
-        <v>0.0143449</v>
+        <v>1.4344900000000001E-2</v>
       </c>
       <c r="G50">
-        <v>0.0048535</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
+        <v>4.8535000000000002E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>4</v>
       </c>
@@ -1750,22 +3285,22 @@
         <v>56</v>
       </c>
       <c r="C51">
-        <v>0.0003755</v>
+        <v>3.7550000000000002E-4</v>
       </c>
       <c r="D51">
-        <v>0.0012639</v>
+        <v>1.2639000000000001E-3</v>
       </c>
       <c r="E51">
-        <v>0.0037448</v>
+        <v>3.7448E-3</v>
       </c>
       <c r="F51">
-        <v>0.0132088</v>
+        <v>1.32088E-2</v>
       </c>
       <c r="G51">
-        <v>0.00464825</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
+        <v>4.6482499999999996E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>4</v>
       </c>
@@ -1773,22 +3308,22 @@
         <v>57</v>
       </c>
       <c r="C52">
-        <v>0.000339</v>
+        <v>3.39E-4</v>
       </c>
       <c r="D52">
-        <v>0.0010848</v>
+        <v>1.0847999999999999E-3</v>
       </c>
       <c r="E52">
-        <v>0.0031808</v>
+        <v>3.1808000000000001E-3</v>
       </c>
       <c r="F52">
-        <v>0.0119883</v>
+        <v>1.19883E-2</v>
       </c>
       <c r="G52">
-        <v>0.004148224999999999</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
+        <v>4.1482249999999993E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>4</v>
       </c>
@@ -1796,22 +3331,22 @@
         <v>58</v>
       </c>
       <c r="C53">
-        <v>0.0003228</v>
+        <v>3.2279999999999999E-4</v>
       </c>
       <c r="D53">
-        <v>0.0010539</v>
+        <v>1.0539E-3</v>
       </c>
       <c r="E53">
-        <v>0.004409700000000001</v>
+        <v>4.4097000000000008E-3</v>
       </c>
       <c r="F53">
-        <v>0.020159</v>
+        <v>2.0159E-2</v>
       </c>
       <c r="G53">
-        <v>0.00648635</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
+        <v>6.4863500000000001E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>4</v>
       </c>
@@ -1819,22 +3354,22 @@
         <v>59</v>
       </c>
       <c r="C54">
-        <v>0.0004310000000000001</v>
+        <v>4.3100000000000012E-4</v>
       </c>
       <c r="D54">
-        <v>0.0012344</v>
+        <v>1.2344000000000001E-3</v>
       </c>
       <c r="E54">
-        <v>0.0047125</v>
+        <v>4.7124999999999997E-3</v>
       </c>
       <c r="F54">
-        <v>0.0204736</v>
+        <v>2.0473600000000002E-2</v>
       </c>
       <c r="G54">
-        <v>0.006712875</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
+        <v>6.7128750000000001E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>4</v>
       </c>
@@ -1842,22 +3377,22 @@
         <v>60</v>
       </c>
       <c r="C55">
-        <v>0.0003773</v>
+        <v>3.7730000000000001E-4</v>
       </c>
       <c r="D55">
-        <v>0.0010424</v>
+        <v>1.0424E-3</v>
       </c>
       <c r="E55">
-        <v>0.0033772</v>
+        <v>3.3771999999999999E-3</v>
       </c>
       <c r="F55">
-        <v>0.01264</v>
+        <v>1.264E-2</v>
       </c>
       <c r="G55">
-        <v>0.004359225</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
+        <v>4.3592250000000004E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>4</v>
       </c>
@@ -1865,22 +3400,22 @@
         <v>61</v>
       </c>
       <c r="C56">
-        <v>0.0003898</v>
+        <v>3.8979999999999999E-4</v>
       </c>
       <c r="D56">
-        <v>0.0011705</v>
+        <v>1.1705000000000001E-3</v>
       </c>
       <c r="E56">
-        <v>0.0030499</v>
+        <v>3.0498999999999999E-3</v>
       </c>
       <c r="F56">
-        <v>0.0135152</v>
+        <v>1.35152E-2</v>
       </c>
       <c r="G56">
-        <v>0.00453135</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
+        <v>4.53135E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>4</v>
       </c>
@@ -1888,22 +3423,22 @@
         <v>62</v>
       </c>
       <c r="C57">
-        <v>0.0004279999999999999</v>
+        <v>4.2799999999999989E-4</v>
       </c>
       <c r="D57">
-        <v>0.0010835</v>
+        <v>1.0835E-3</v>
       </c>
       <c r="E57">
-        <v>0.0030325</v>
+        <v>3.0325E-3</v>
       </c>
       <c r="F57">
-        <v>0.013322</v>
+        <v>1.3322000000000001E-2</v>
       </c>
       <c r="G57">
-        <v>0.004466499999999999</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
+        <v>4.4664999999999991E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>4</v>
       </c>
@@ -1911,22 +3446,22 @@
         <v>63</v>
       </c>
       <c r="C58">
-        <v>0.0004308</v>
+        <v>4.3080000000000001E-4</v>
       </c>
       <c r="D58">
-        <v>0.0012882</v>
+        <v>1.2882E-3</v>
       </c>
       <c r="E58">
-        <v>0.003862</v>
+        <v>3.862E-3</v>
       </c>
       <c r="F58">
-        <v>0.0142932</v>
+        <v>1.4293200000000001E-2</v>
       </c>
       <c r="G58">
-        <v>0.00496855</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
+        <v>4.9685500000000004E-3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>5</v>
       </c>
@@ -1934,22 +3469,22 @@
         <v>64</v>
       </c>
       <c r="C59">
-        <v>0.0007218000000000001</v>
+        <v>7.2180000000000009E-4</v>
       </c>
       <c r="D59">
-        <v>0.0031521</v>
+        <v>3.1521000000000001E-3</v>
       </c>
       <c r="E59">
-        <v>0.0151418</v>
+        <v>1.51418E-2</v>
       </c>
       <c r="F59">
-        <v>0.09098229999999999</v>
+        <v>9.0982299999999988E-2</v>
       </c>
       <c r="G59">
-        <v>0.0274995</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
+        <v>2.74995E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>5</v>
       </c>
@@ -1957,22 +3492,22 @@
         <v>65</v>
       </c>
       <c r="C60">
-        <v>0.0004704</v>
+        <v>4.704E-4</v>
       </c>
       <c r="D60">
-        <v>0.0013913</v>
+        <v>1.3913E-3</v>
       </c>
       <c r="E60">
-        <v>0.0034596</v>
+        <v>3.4596000000000002E-3</v>
       </c>
       <c r="F60">
-        <v>0.0145677</v>
+        <v>1.4567699999999999E-2</v>
       </c>
       <c r="G60">
-        <v>0.00497225</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
+        <v>4.9722500000000001E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>5</v>
       </c>
@@ -1980,22 +3515,22 @@
         <v>66</v>
       </c>
       <c r="C61">
-        <v>0.0004303999999999999</v>
+        <v>4.3039999999999989E-4</v>
       </c>
       <c r="D61">
-        <v>0.0013801</v>
+        <v>1.3801E-3</v>
       </c>
       <c r="E61">
-        <v>0.0038207</v>
+        <v>3.8206999999999998E-3</v>
       </c>
       <c r="F61">
-        <v>0.0133742</v>
+        <v>1.3374199999999999E-2</v>
       </c>
       <c r="G61">
-        <v>0.00475135</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
+        <v>4.7513499999999997E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>5</v>
       </c>
@@ -2003,22 +3538,22 @@
         <v>67</v>
       </c>
       <c r="C62">
-        <v>0.0004373</v>
+        <v>4.373E-4</v>
       </c>
       <c r="D62">
-        <v>0.0013852</v>
+        <v>1.3852000000000001E-3</v>
       </c>
       <c r="E62">
-        <v>0.004093100000000001</v>
+        <v>4.0931000000000014E-3</v>
       </c>
       <c r="F62">
-        <v>0.0140323</v>
+        <v>1.4032299999999999E-2</v>
       </c>
       <c r="G62">
-        <v>0.004986974999999999</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
+        <v>4.9869749999999994E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>5</v>
       </c>
@@ -2026,22 +3561,22 @@
         <v>68</v>
       </c>
       <c r="C63">
-        <v>0.0003759</v>
+        <v>3.7589999999999998E-4</v>
       </c>
       <c r="D63">
-        <v>0.0011687</v>
+        <v>1.1686999999999999E-3</v>
       </c>
       <c r="E63">
-        <v>0.0044683</v>
+        <v>4.4682999999999997E-3</v>
       </c>
       <c r="F63">
-        <v>0.0202903</v>
+        <v>2.0290300000000001E-2</v>
       </c>
       <c r="G63">
-        <v>0.0065758</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
+        <v>6.5757999999999997E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>5</v>
       </c>
@@ -2049,22 +3584,22 @@
         <v>69</v>
       </c>
       <c r="C64">
-        <v>0.0004195999999999999</v>
+        <v>4.195999999999999E-4</v>
       </c>
       <c r="D64">
-        <v>0.0011564</v>
+        <v>1.1563999999999999E-3</v>
       </c>
       <c r="E64">
-        <v>0.0030672</v>
+        <v>3.0672E-3</v>
       </c>
       <c r="F64">
-        <v>0.0135291</v>
+        <v>1.3529100000000001E-2</v>
       </c>
       <c r="G64">
-        <v>0.004543075</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
+        <v>4.5430749999999997E-3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>6</v>
       </c>
@@ -2072,32 +3607,33 @@
         <v>70</v>
       </c>
       <c r="C65">
-        <v>0.0005395</v>
+        <v>5.3950000000000005E-4</v>
       </c>
       <c r="D65">
-        <v>0.0014773</v>
+        <v>1.4773E-3</v>
       </c>
       <c r="E65">
-        <v>0.0042453</v>
+        <v>4.2452999999999996E-3</v>
       </c>
       <c r="F65">
-        <v>0.0141643</v>
+        <v>1.4164299999999999E-2</v>
       </c>
       <c r="G65">
-        <v>0.005106599999999999</v>
+        <v>5.1065999999999993E-3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2120,7 +3656,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2143,7 +3679,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2166,7 +3702,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -2189,7 +3725,7 @@
         <v>82.75</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -2212,7 +3748,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -2235,7 +3771,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -2258,7 +3794,7 @@
         <v>10.25</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -2281,7 +3817,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -2304,7 +3840,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -2327,7 +3863,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -2350,7 +3886,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -2373,7 +3909,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2</v>
       </c>
@@ -2396,7 +3932,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -2419,7 +3955,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -2442,7 +3978,7 @@
         <v>88.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2</v>
       </c>
@@ -2465,7 +4001,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2</v>
       </c>
@@ -2488,7 +4024,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2</v>
       </c>
@@ -2511,7 +4047,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -2534,7 +4070,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -2557,7 +4093,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
@@ -2580,7 +4116,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -2603,7 +4139,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2</v>
       </c>
@@ -2626,7 +4162,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>3</v>
       </c>
@@ -2649,7 +4185,7 @@
         <v>11.25</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>3</v>
       </c>
@@ -2672,7 +4208,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>3</v>
       </c>
@@ -2695,7 +4231,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>3</v>
       </c>
@@ -2718,7 +4254,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -2741,7 +4277,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>3</v>
       </c>
@@ -2764,7 +4300,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
@@ -2787,7 +4323,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
@@ -2810,7 +4346,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
@@ -2833,7 +4369,7 @@
         <v>88.5</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>3</v>
       </c>
@@ -2856,7 +4392,7 @@
         <v>10.75</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>3</v>
       </c>
@@ -2879,7 +4415,7 @@
         <v>19.25</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>3</v>
       </c>
@@ -2902,7 +4438,7 @@
         <v>19.25</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>3</v>
       </c>
@@ -2925,7 +4461,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>3</v>
       </c>
@@ -2948,7 +4484,7 @@
         <v>19.25</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>3</v>
       </c>
@@ -2971,7 +4507,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>3</v>
       </c>
@@ -2994,7 +4530,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3</v>
       </c>
@@ -3017,7 +4553,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>3</v>
       </c>
@@ -3040,7 +4576,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>3</v>
       </c>
@@ -3063,7 +4599,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3</v>
       </c>
@@ -3086,7 +4622,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>4</v>
       </c>
@@ -3109,7 +4645,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>4</v>
       </c>
@@ -3132,7 +4668,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>4</v>
       </c>
@@ -3155,7 +4691,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>4</v>
       </c>
@@ -3178,7 +4714,7 @@
         <v>11.75</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>4</v>
       </c>
@@ -3201,7 +4737,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>4</v>
       </c>
@@ -3224,7 +4760,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>4</v>
       </c>
@@ -3247,7 +4783,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>4</v>
       </c>
@@ -3270,7 +4806,7 @@
         <v>19.25</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>4</v>
       </c>
@@ -3293,7 +4829,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>4</v>
       </c>
@@ -3316,7 +4852,7 @@
         <v>20.25</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>4</v>
       </c>
@@ -3339,7 +4875,7 @@
         <v>11.75</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>4</v>
       </c>
@@ -3362,7 +4898,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>4</v>
       </c>
@@ -3385,7 +4921,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>4</v>
       </c>
@@ -3408,7 +4944,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>4</v>
       </c>
@@ -3431,7 +4967,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>5</v>
       </c>
@@ -3454,7 +4990,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>5</v>
       </c>
@@ -3477,7 +5013,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>5</v>
       </c>
@@ -3500,7 +5036,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>5</v>
       </c>
@@ -3523,7 +5059,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>5</v>
       </c>
@@ -3546,7 +5082,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>5</v>
       </c>
@@ -3569,7 +5105,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>6</v>
       </c>
@@ -3598,11 +5134,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3625,7 +5161,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -3636,19 +5172,19 @@
         <v>25.55634918610405</v>
       </c>
       <c r="D2">
-        <v>51.69848480983499</v>
+        <v>51.698484809834987</v>
       </c>
       <c r="E2">
         <v>103.9827560572969</v>
       </c>
       <c r="F2">
-        <v>208.5512985522207</v>
+        <v>208.55129855222069</v>
       </c>
       <c r="G2">
-        <v>97.44722215136416</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>97.447222151364159</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -3656,10 +5192,10 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>26.38477631085023</v>
+        <v>26.384776310850231</v>
       </c>
       <c r="D3">
-        <v>52.52691193458119</v>
+        <v>52.526911934581193</v>
       </c>
       <c r="E3">
         <v>104.8111831820431</v>
@@ -3668,10 +5204,10 @@
         <v>209.3797256769669</v>
       </c>
       <c r="G3">
-        <v>98.27564927611034</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>98.275649276110343</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -3679,22 +5215,22 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>26.97056274847714</v>
+        <v>26.970562748477139</v>
       </c>
       <c r="D4">
-        <v>52.52691193458119</v>
+        <v>52.526911934581193</v>
       </c>
       <c r="E4">
-        <v>106.4680374315355</v>
+        <v>106.46803743153551</v>
       </c>
       <c r="F4">
-        <v>214.350288425444</v>
+        <v>214.35028842544401</v>
       </c>
       <c r="G4">
-        <v>100.0789501350095</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>100.07895013500951</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -3705,19 +5241,19 @@
         <v>25.55634918610405</v>
       </c>
       <c r="D5">
-        <v>51.69848480983499</v>
+        <v>51.698484809834987</v>
       </c>
       <c r="E5">
         <v>103.9827560572969</v>
       </c>
       <c r="F5">
-        <v>208.5512985522207</v>
+        <v>208.55129855222069</v>
       </c>
       <c r="G5">
-        <v>97.44722215136416</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>97.447222151364159</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -3728,19 +5264,19 @@
         <v>25.55634918610405</v>
       </c>
       <c r="D6">
-        <v>51.69848480983499</v>
+        <v>51.698484809834987</v>
       </c>
       <c r="E6">
         <v>103.9827560572969</v>
       </c>
       <c r="F6">
-        <v>208.5512985522207</v>
+        <v>208.55129855222069</v>
       </c>
       <c r="G6">
-        <v>97.44722215136414</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>97.447222151364144</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -3748,10 +5284,10 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>24.88362701190674</v>
+        <v>24.883627011906739</v>
       </c>
       <c r="D7">
-        <v>49.97264776279763</v>
+        <v>49.972647762797628</v>
       </c>
       <c r="E7">
         <v>100.6259579416699</v>
@@ -3760,10 +5296,10 @@
         <v>201.6665280368868</v>
       </c>
       <c r="G7">
-        <v>94.28719018831526</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>94.287190188315265</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -3774,19 +5310,19 @@
         <v>25.55634918610405</v>
       </c>
       <c r="D8">
-        <v>51.69848480983499</v>
+        <v>51.698484809834987</v>
       </c>
       <c r="E8">
         <v>103.9827560572969</v>
       </c>
       <c r="F8">
-        <v>208.5512985522207</v>
+        <v>208.55129855222069</v>
       </c>
       <c r="G8">
-        <v>97.44722215136416</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>97.447222151364159</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -3797,19 +5333,19 @@
         <v>25.55634918610405</v>
       </c>
       <c r="D9">
-        <v>53.35533905932738</v>
+        <v>53.355339059327378</v>
       </c>
       <c r="E9">
-        <v>107.2964645562817</v>
+        <v>107.29646455628171</v>
       </c>
       <c r="F9">
-        <v>215.1787155501902</v>
+        <v>215.17871555019019</v>
       </c>
       <c r="G9">
         <v>100.3467170879758</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -3826,13 +5362,13 @@
         <v>109.4974746830583</v>
       </c>
       <c r="F10">
-        <v>218.7523086789974</v>
+        <v>218.75230867899739</v>
       </c>
       <c r="G10">
         <v>102.6690475583121</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -3843,19 +5379,19 @@
         <v>24.65008380450606</v>
       </c>
       <c r="D11">
-        <v>49.27515134583025</v>
+        <v>49.275151345830253</v>
       </c>
       <c r="E11">
-        <v>98.56849267120391</v>
+        <v>98.568492671203913</v>
       </c>
       <c r="F11">
-        <v>197.6119386070031</v>
+        <v>197.61193860700311</v>
       </c>
       <c r="G11">
-        <v>92.52641660713583</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>92.526416607135829</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -3863,10 +5399,10 @@
         <v>17</v>
       </c>
       <c r="C12">
-        <v>26.38477631085023</v>
+        <v>26.384776310850231</v>
       </c>
       <c r="D12">
-        <v>51.69848480983499</v>
+        <v>51.698484809834987</v>
       </c>
       <c r="E12">
         <v>104.8111831820431</v>
@@ -3875,10 +5411,10 @@
         <v>209.3797256769669</v>
       </c>
       <c r="G12">
-        <v>98.0685424949238</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>98.068542494923804</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2</v>
       </c>
@@ -3886,22 +5422,22 @@
         <v>18</v>
       </c>
       <c r="C13">
-        <v>25.89681914012433</v>
+        <v>25.896819140124329</v>
       </c>
       <c r="D13">
-        <v>50.21975646423518</v>
+        <v>50.219756464235182</v>
       </c>
       <c r="E13">
         <v>101.5994483836505</v>
       </c>
       <c r="F13">
-        <v>204.5161634962677</v>
+        <v>204.51616349626769</v>
       </c>
       <c r="G13">
-        <v>95.55804687106941</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>95.558046871069408</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -3912,19 +5448,19 @@
         <v>25.55634918610405</v>
       </c>
       <c r="D14">
-        <v>52.52691193458119</v>
+        <v>52.526911934581193</v>
       </c>
       <c r="E14">
-        <v>106.4680374315355</v>
+        <v>106.46803743153551</v>
       </c>
       <c r="F14">
-        <v>214.350288425444</v>
+        <v>214.35028842544401</v>
       </c>
       <c r="G14">
-        <v>99.72539674441619</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>99.725396744416187</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -3935,19 +5471,19 @@
         <v>25.55634918610405</v>
       </c>
       <c r="D15">
-        <v>51.69848480983499</v>
+        <v>51.698484809834987</v>
       </c>
       <c r="E15">
         <v>109.4974746830583</v>
       </c>
       <c r="F15">
-        <v>218.7523086789974</v>
+        <v>218.75230867899739</v>
       </c>
       <c r="G15">
         <v>101.3761543394987</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2</v>
       </c>
@@ -3955,22 +5491,22 @@
         <v>21</v>
       </c>
       <c r="C16">
-        <v>24.61602089821564</v>
+        <v>24.616020898215641</v>
       </c>
       <c r="D16">
         <v>49.34816619039939</v>
       </c>
       <c r="E16">
-        <v>99.16649645830616</v>
+        <v>99.166496458306156</v>
       </c>
       <c r="F16">
-        <v>198.9303419903817</v>
+        <v>198.93034199038169</v>
       </c>
       <c r="G16">
-        <v>93.01525638432572</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>93.015256384325724</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2</v>
       </c>
@@ -3978,22 +5514,22 @@
         <v>22</v>
       </c>
       <c r="C17">
-        <v>26.72792206135786</v>
+        <v>26.727922061357859</v>
       </c>
       <c r="D17">
-        <v>54.04163056034262</v>
+        <v>54.041630560342618</v>
       </c>
       <c r="E17">
         <v>103.9827560572969</v>
       </c>
       <c r="F17">
-        <v>208.5512985522207</v>
+        <v>208.55129855222069</v>
       </c>
       <c r="G17">
-        <v>98.32590180780451</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>98.325901807804513</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2</v>
       </c>
@@ -4004,19 +5540,19 @@
         <v>25.55634918610405</v>
       </c>
       <c r="D18">
-        <v>51.69848480983499</v>
+        <v>51.698484809834987</v>
       </c>
       <c r="E18">
         <v>103.9827560572969</v>
       </c>
       <c r="F18">
-        <v>208.5512985522207</v>
+        <v>208.55129855222069</v>
       </c>
       <c r="G18">
-        <v>97.44722215136414</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>97.447222151364144</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -4024,22 +5560,22 @@
         <v>24</v>
       </c>
       <c r="C19">
-        <v>26.97056274847714</v>
+        <v>26.970562748477139</v>
       </c>
       <c r="D19">
-        <v>54.04163056034262</v>
+        <v>54.041630560342618</v>
       </c>
       <c r="E19">
         <v>111.8406204335659</v>
       </c>
       <c r="F19">
-        <v>217.9238815542512</v>
+        <v>217.92388155425121</v>
       </c>
       <c r="G19">
-        <v>102.6941738241592</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>102.69417382415919</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -4047,22 +5583,22 @@
         <v>25</v>
       </c>
       <c r="C20">
-        <v>26.14213562373095</v>
+        <v>26.142135623730951</v>
       </c>
       <c r="D20">
-        <v>51.69848480983499</v>
+        <v>51.698484809834987</v>
       </c>
       <c r="E20">
         <v>103.9827560572969</v>
       </c>
       <c r="F20">
-        <v>208.5512985522207</v>
+        <v>208.55129855222069</v>
       </c>
       <c r="G20">
-        <v>97.59366876077087</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>97.593668760770868</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
@@ -4070,22 +5606,22 @@
         <v>26</v>
       </c>
       <c r="C21">
-        <v>25.06177259678004</v>
+        <v>25.061772596780042</v>
       </c>
       <c r="D21">
-        <v>50.78481790424926</v>
+        <v>50.784817904249259</v>
       </c>
       <c r="E21">
-        <v>102.4457053266944</v>
+        <v>102.44570532669439</v>
       </c>
       <c r="F21">
-        <v>205.8290457947327</v>
+        <v>205.82904579473271</v>
       </c>
       <c r="G21">
-        <v>96.0303354056141</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>96.030335405614096</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -4096,19 +5632,19 @@
         <v>25.55634918610405</v>
       </c>
       <c r="D22">
-        <v>51.69848480983499</v>
+        <v>51.698484809834987</v>
       </c>
       <c r="E22">
         <v>103.9827560572969</v>
       </c>
       <c r="F22">
-        <v>208.5512985522207</v>
+        <v>208.55129855222069</v>
       </c>
       <c r="G22">
-        <v>97.44722215136414</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>97.447222151364144</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2</v>
       </c>
@@ -4116,22 +5652,22 @@
         <v>28</v>
       </c>
       <c r="C23">
-        <v>24.88362701190674</v>
+        <v>24.883627011906739</v>
       </c>
       <c r="D23">
-        <v>49.46877595838819</v>
+        <v>49.468775958388193</v>
       </c>
       <c r="E23">
-        <v>99.99556984410933</v>
+        <v>99.995569844109326</v>
       </c>
       <c r="F23">
-        <v>201.3076996126511</v>
+        <v>201.30769961265111</v>
       </c>
       <c r="G23">
-        <v>93.91391810676384</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>93.913918106763845</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>3</v>
       </c>
@@ -4139,22 +5675,22 @@
         <v>29</v>
       </c>
       <c r="C24">
-        <v>24.66075116262454</v>
+        <v>24.660751162624539</v>
       </c>
       <c r="D24">
-        <v>50.19374526579473</v>
+        <v>50.193745265794732</v>
       </c>
       <c r="E24">
         <v>100.9725808023951</v>
       </c>
       <c r="F24">
-        <v>203.1696139169028</v>
+        <v>203.16961391690279</v>
       </c>
       <c r="G24">
-        <v>94.74917278692931</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>94.749172786929307</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>3</v>
       </c>
@@ -4165,19 +5701,19 @@
         <v>25.55634918610405</v>
       </c>
       <c r="D25">
-        <v>52.52691193458119</v>
+        <v>52.526911934581193</v>
       </c>
       <c r="E25">
-        <v>106.4680374315355</v>
+        <v>106.46803743153551</v>
       </c>
       <c r="F25">
-        <v>214.350288425444</v>
+        <v>214.35028842544401</v>
       </c>
       <c r="G25">
-        <v>99.72539674441619</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>99.725396744416187</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>3</v>
       </c>
@@ -4188,19 +5724,19 @@
         <v>27.55634918610405</v>
       </c>
       <c r="D26">
-        <v>52.52691193458119</v>
+        <v>52.526911934581193</v>
       </c>
       <c r="E26">
         <v>110.3259018078045</v>
       </c>
       <c r="F26">
-        <v>219.5807358037436</v>
+        <v>219.58073580374361</v>
       </c>
       <c r="G26">
         <v>102.4974746830583</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>3</v>
       </c>
@@ -4208,22 +5744,22 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>25.87705430228725</v>
+        <v>25.877054302287249</v>
       </c>
       <c r="D27">
-        <v>51.45445947838049</v>
+        <v>51.454459478380492</v>
       </c>
       <c r="E27">
         <v>103.3736799535253</v>
       </c>
       <c r="F27">
-        <v>207.424882855446</v>
+        <v>207.42488285544599</v>
       </c>
       <c r="G27">
-        <v>97.03251914740976</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>97.032519147409758</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -4231,7 +5767,7 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>26.72792206135786</v>
+        <v>26.727922061357859</v>
       </c>
       <c r="D28">
         <v>54.87005768508881</v>
@@ -4240,13 +5776,13 @@
         <v>109.4974746830583</v>
       </c>
       <c r="F28">
-        <v>218.7523086789974</v>
+        <v>218.75230867899739</v>
       </c>
       <c r="G28">
         <v>102.4619407771256</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>3</v>
       </c>
@@ -4257,19 +5793,19 @@
         <v>24.65008380450606</v>
       </c>
       <c r="D29">
-        <v>49.95352392457285</v>
+        <v>49.953523924572849</v>
       </c>
       <c r="E29">
-        <v>98.90198678661714</v>
+        <v>98.901986786617144</v>
       </c>
       <c r="F29">
         <v>197.9415538688763</v>
       </c>
       <c r="G29">
-        <v>92.86178709614308</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>92.861787096143075</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
@@ -4277,22 +5813,22 @@
         <v>35</v>
       </c>
       <c r="C30">
-        <v>24.88362701190674</v>
+        <v>24.883627011906739</v>
       </c>
       <c r="D30">
-        <v>50.68849900905803</v>
+        <v>50.688499009058027</v>
       </c>
       <c r="E30">
         <v>102.5369334732962</v>
       </c>
       <c r="F30">
-        <v>206.4096207261664</v>
+        <v>206.40962072616639</v>
       </c>
       <c r="G30">
-        <v>96.12967005510683</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>96.129670055106828</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
@@ -4303,19 +5839,19 @@
         <v>24.65008380450606</v>
       </c>
       <c r="D31">
-        <v>49.54781268914662</v>
+        <v>49.547812689146618</v>
       </c>
       <c r="E31">
-        <v>104.6356807917362</v>
+        <v>104.63568079173621</v>
       </c>
       <c r="F31">
-        <v>209.67674266388</v>
+        <v>209.67674266387999</v>
       </c>
       <c r="G31">
-        <v>97.12757998731722</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>97.127579987317219</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
@@ -4326,19 +5862,19 @@
         <v>25.55634918610405</v>
       </c>
       <c r="D32">
-        <v>51.69848480983499</v>
+        <v>51.698484809834987</v>
       </c>
       <c r="E32">
         <v>109.4974746830583</v>
       </c>
       <c r="F32">
-        <v>218.7523086789974</v>
+        <v>218.75230867899739</v>
       </c>
       <c r="G32">
         <v>101.3761543394987</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>3</v>
       </c>
@@ -4346,22 +5882,22 @@
         <v>38</v>
       </c>
       <c r="C33">
-        <v>25.87705430228725</v>
+        <v>25.877054302287249</v>
       </c>
       <c r="D33">
-        <v>51.41705796526954</v>
+        <v>51.417057965269542</v>
       </c>
       <c r="E33">
-        <v>99.16649645830616</v>
+        <v>99.166496458306156</v>
       </c>
       <c r="F33">
-        <v>198.9303419903817</v>
+        <v>198.93034199038169</v>
       </c>
       <c r="G33">
-        <v>93.84773767906115</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>93.847737679061154</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>3</v>
       </c>
@@ -4372,19 +5908,19 @@
         <v>25.55634918610405</v>
       </c>
       <c r="D34">
-        <v>54.04163056034262</v>
+        <v>54.041630560342618</v>
       </c>
       <c r="E34">
         <v>108.6690475583121</v>
       </c>
       <c r="F34">
-        <v>217.9238815542512</v>
+        <v>217.92388155425121</v>
       </c>
       <c r="G34">
         <v>101.5477272147525</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>3</v>
       </c>
@@ -4392,22 +5928,22 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>26.72792206135786</v>
+        <v>26.727922061357859</v>
       </c>
       <c r="D35">
-        <v>54.04163056034262</v>
+        <v>54.041630560342618</v>
       </c>
       <c r="E35">
         <v>108.6690475583121</v>
       </c>
       <c r="F35">
-        <v>217.9238815542512</v>
+        <v>217.92388155425121</v>
       </c>
       <c r="G35">
         <v>101.8406204335659</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>3</v>
       </c>
@@ -4415,22 +5951,22 @@
         <v>41</v>
       </c>
       <c r="C36">
-        <v>25.06177259678004</v>
+        <v>25.061772596780042</v>
       </c>
       <c r="D36">
-        <v>50.21768795326422</v>
+        <v>50.217687953264218</v>
       </c>
       <c r="E36">
-        <v>100.9779513093111</v>
+        <v>100.97795130931109</v>
       </c>
       <c r="F36">
         <v>202.6246318390989</v>
       </c>
       <c r="G36">
-        <v>94.72051092461355</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+        <v>94.720510924613549</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>3</v>
       </c>
@@ -4441,19 +5977,19 @@
         <v>25.55634918610405</v>
       </c>
       <c r="D37">
-        <v>51.69848480983499</v>
+        <v>51.698484809834987</v>
       </c>
       <c r="E37">
         <v>107.1543289325507</v>
       </c>
       <c r="F37">
-        <v>233.6396103067893</v>
+        <v>233.63961030678931</v>
       </c>
       <c r="G37">
         <v>104.5121933088197</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>3</v>
       </c>
@@ -4461,22 +5997,22 @@
         <v>43</v>
       </c>
       <c r="C38">
-        <v>26.29784057427984</v>
+        <v>26.297840574279839</v>
       </c>
       <c r="D38">
-        <v>52.8500165541117</v>
+        <v>52.850016554111697</v>
       </c>
       <c r="E38">
         <v>111.1160456359106</v>
       </c>
       <c r="F38">
-        <v>214.0898403941825</v>
+        <v>214.08984039418249</v>
       </c>
       <c r="G38">
         <v>101.0884357896212</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>3</v>
       </c>
@@ -4484,22 +6020,22 @@
         <v>44</v>
       </c>
       <c r="C39">
-        <v>26.97056274847714</v>
+        <v>26.970562748477139</v>
       </c>
       <c r="D39">
-        <v>54.04163056034262</v>
+        <v>54.041630560342618</v>
       </c>
       <c r="E39">
         <v>111.8406204335659</v>
       </c>
       <c r="F39">
-        <v>217.9238815542512</v>
+        <v>217.92388155425121</v>
       </c>
       <c r="G39">
-        <v>102.6941738241592</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+        <v>102.69417382415919</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3</v>
       </c>
@@ -4507,22 +6043,22 @@
         <v>45</v>
       </c>
       <c r="C40">
-        <v>26.72792206135786</v>
+        <v>26.727922061357859</v>
       </c>
       <c r="D40">
-        <v>54.04163056034262</v>
+        <v>54.041630560342618</v>
       </c>
       <c r="E40">
         <v>108.6690475583121</v>
       </c>
       <c r="F40">
-        <v>217.9238815542512</v>
+        <v>217.92388155425121</v>
       </c>
       <c r="G40">
         <v>101.8406204335659</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>3</v>
       </c>
@@ -4533,19 +6069,19 @@
         <v>25.64755903440695</v>
       </c>
       <c r="D41">
-        <v>50.78481790424926</v>
+        <v>50.784817904249259</v>
       </c>
       <c r="E41">
-        <v>102.4457053266944</v>
+        <v>102.44570532669439</v>
       </c>
       <c r="F41">
-        <v>205.8290457947327</v>
+        <v>205.82904579473271</v>
       </c>
       <c r="G41">
-        <v>96.17678201502082</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+        <v>96.176782015020819</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>3</v>
       </c>
@@ -4553,22 +6089,22 @@
         <v>47</v>
       </c>
       <c r="C42">
-        <v>26.14213562373095</v>
+        <v>26.142135623730951</v>
       </c>
       <c r="D42">
-        <v>51.69848480983499</v>
+        <v>51.698484809834987</v>
       </c>
       <c r="E42">
         <v>103.9827560572969</v>
       </c>
       <c r="F42">
-        <v>208.5512985522207</v>
+        <v>208.55129855222069</v>
       </c>
       <c r="G42">
-        <v>97.59366876077087</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
+        <v>97.593668760770868</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3</v>
       </c>
@@ -4576,22 +6112,22 @@
         <v>48</v>
       </c>
       <c r="C43">
-        <v>25.06177259678004</v>
+        <v>25.061772596780042</v>
       </c>
       <c r="D43">
-        <v>50.78481790424926</v>
+        <v>50.784817904249259</v>
       </c>
       <c r="E43">
-        <v>102.4457053266944</v>
+        <v>102.44570532669439</v>
       </c>
       <c r="F43">
-        <v>205.8290457947327</v>
+        <v>205.82904579473271</v>
       </c>
       <c r="G43">
-        <v>96.0303354056141</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+        <v>96.030335405614096</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>4</v>
       </c>
@@ -4599,22 +6135,22 @@
         <v>49</v>
       </c>
       <c r="C44">
-        <v>24.88362701190674</v>
+        <v>24.883627011906739</v>
       </c>
       <c r="D44">
-        <v>51.00369305783835</v>
+        <v>51.003693057838348</v>
       </c>
       <c r="E44">
         <v>102.0330616688867</v>
       </c>
       <c r="F44">
-        <v>205.1558855636557</v>
+        <v>205.15588556365569</v>
       </c>
       <c r="G44">
-        <v>95.76906682557187</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+        <v>95.769066825571869</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>4</v>
       </c>
@@ -4622,22 +6158,22 @@
         <v>50</v>
       </c>
       <c r="C45">
-        <v>26.414373490278</v>
+        <v>26.414373490277999</v>
       </c>
       <c r="D45">
-        <v>49.69377351010213</v>
+        <v>49.693773510102133</v>
       </c>
       <c r="E45">
         <v>104.569998812953</v>
       </c>
       <c r="F45">
-        <v>209.3666334498428</v>
+        <v>209.36663344984279</v>
       </c>
       <c r="G45">
-        <v>97.51119481579398</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
+        <v>97.511194815793985</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>4</v>
       </c>
@@ -4648,19 +6184,19 @@
         <v>27.55634918610405</v>
       </c>
       <c r="D46">
-        <v>51.69848480983499</v>
+        <v>51.698484809834987</v>
       </c>
       <c r="E46">
         <v>110.3259018078045</v>
       </c>
       <c r="F46">
-        <v>219.5807358037436</v>
+        <v>219.58073580374361</v>
       </c>
       <c r="G46">
         <v>102.2903679018718</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>4</v>
       </c>
@@ -4668,22 +6204,22 @@
         <v>52</v>
       </c>
       <c r="C47">
-        <v>26.05519988716055</v>
+        <v>26.055199887160551</v>
       </c>
       <c r="D47">
-        <v>51.45445947838049</v>
+        <v>51.454459478380492</v>
       </c>
       <c r="E47">
-        <v>103.3271534819307</v>
+        <v>103.32715348193069</v>
       </c>
       <c r="F47">
-        <v>207.424882855446</v>
+        <v>207.42488285544599</v>
       </c>
       <c r="G47">
-        <v>97.06542392572945</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
+        <v>97.065423925729448</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>4</v>
       </c>
@@ -4694,19 +6230,19 @@
         <v>24.65008380450606</v>
       </c>
       <c r="D48">
-        <v>49.54781268914662</v>
+        <v>49.547812689146618</v>
       </c>
       <c r="E48">
-        <v>104.6356807917362</v>
+        <v>104.63568079173621</v>
       </c>
       <c r="F48">
-        <v>209.67674266388</v>
+        <v>209.67674266387999</v>
       </c>
       <c r="G48">
-        <v>97.12757998731722</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+        <v>97.127579987317219</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>4</v>
       </c>
@@ -4714,7 +6250,7 @@
         <v>54</v>
       </c>
       <c r="C49">
-        <v>25.06177259678004</v>
+        <v>25.061772596780042</v>
       </c>
       <c r="D49">
         <v>52.28288660312667</v>
@@ -4723,13 +6259,13 @@
         <v>105.108348609036</v>
       </c>
       <c r="F49">
-        <v>211.0430492799173</v>
+        <v>211.04304927991731</v>
       </c>
       <c r="G49">
-        <v>98.37401427221501</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
+        <v>98.374014272215007</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>4</v>
       </c>
@@ -4740,7 +6276,7 @@
         <v>25.55634918610405</v>
       </c>
       <c r="D50">
-        <v>51.69848480983499</v>
+        <v>51.698484809834987</v>
       </c>
       <c r="E50">
         <v>107.1543289325507</v>
@@ -4749,10 +6285,10 @@
         <v>214.0660171779821</v>
       </c>
       <c r="G50">
-        <v>99.61879502661797</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
+        <v>99.618795026617974</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>4</v>
       </c>
@@ -4760,22 +6296,22 @@
         <v>56</v>
       </c>
       <c r="C51">
-        <v>26.72792206135786</v>
+        <v>26.727922061357859</v>
       </c>
       <c r="D51">
-        <v>54.04163056034262</v>
+        <v>54.041630560342618</v>
       </c>
       <c r="E51">
         <v>108.6690475583121</v>
       </c>
       <c r="F51">
-        <v>217.9238815542512</v>
+        <v>217.92388155425121</v>
       </c>
       <c r="G51">
         <v>101.8406204335659</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>4</v>
       </c>
@@ -4783,7 +6319,7 @@
         <v>57</v>
       </c>
       <c r="C52">
-        <v>26.05519988716055</v>
+        <v>26.055199887160551</v>
       </c>
       <c r="D52">
         <v>52.28288660312667</v>
@@ -4792,13 +6328,13 @@
         <v>105.108348609036</v>
       </c>
       <c r="F52">
-        <v>211.0430492799173</v>
+        <v>211.04304927991731</v>
       </c>
       <c r="G52">
-        <v>98.62237109481013</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
+        <v>98.622371094810134</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>4</v>
       </c>
@@ -4806,22 +6342,22 @@
         <v>58</v>
       </c>
       <c r="C53">
-        <v>26.72792206135786</v>
+        <v>26.727922061357859</v>
       </c>
       <c r="D53">
-        <v>54.04163056034262</v>
+        <v>54.041630560342618</v>
       </c>
       <c r="E53">
         <v>119.39696961967</v>
       </c>
       <c r="F53">
-        <v>239.9655121145938</v>
+        <v>239.96551211459379</v>
       </c>
       <c r="G53">
-        <v>110.0330085889911</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
+        <v>110.03300858899109</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>4</v>
       </c>
@@ -4829,22 +6365,22 @@
         <v>59</v>
       </c>
       <c r="C54">
-        <v>25.06177259678004</v>
+        <v>25.061772596780042</v>
       </c>
       <c r="D54">
-        <v>50.21768795326422</v>
+        <v>50.217687953264218</v>
       </c>
       <c r="E54">
         <v>105.2369118846929</v>
       </c>
       <c r="F54">
-        <v>227.8582971510559</v>
+        <v>227.85829715105589</v>
       </c>
       <c r="G54">
         <v>102.0936673964483</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>4</v>
       </c>
@@ -4852,22 +6388,22 @@
         <v>60</v>
       </c>
       <c r="C55">
-        <v>26.29784057427984</v>
+        <v>26.297840574279839</v>
       </c>
       <c r="D55">
-        <v>52.8500165541117</v>
+        <v>52.850016554111697</v>
       </c>
       <c r="E55">
         <v>111.1160456359106</v>
       </c>
       <c r="F55">
-        <v>214.0898403941825</v>
+        <v>214.08984039418249</v>
       </c>
       <c r="G55">
         <v>101.0884357896212</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>4</v>
       </c>
@@ -4875,22 +6411,22 @@
         <v>61</v>
       </c>
       <c r="C56">
-        <v>25.87705430228725</v>
+        <v>25.877054302287249</v>
       </c>
       <c r="D56">
-        <v>52.8500165541117</v>
+        <v>52.850016554111697</v>
       </c>
       <c r="E56">
         <v>106.5761026264193</v>
       </c>
       <c r="F56">
-        <v>214.0898403941825</v>
+        <v>214.08984039418249</v>
       </c>
       <c r="G56">
-        <v>99.84825346925018</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
+        <v>99.848253469250182</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>4</v>
       </c>
@@ -4898,22 +6434,22 @@
         <v>62</v>
       </c>
       <c r="C57">
-        <v>26.72792206135786</v>
+        <v>26.727922061357859</v>
       </c>
       <c r="D57">
-        <v>54.04163056034262</v>
+        <v>54.041630560342618</v>
       </c>
       <c r="E57">
         <v>108.6690475583121</v>
       </c>
       <c r="F57">
-        <v>217.9238815542512</v>
+        <v>217.92388155425121</v>
       </c>
       <c r="G57">
         <v>101.8406204335659</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>4</v>
       </c>
@@ -4924,19 +6460,19 @@
         <v>25.64755903440695</v>
       </c>
       <c r="D58">
-        <v>50.78481790424926</v>
+        <v>50.784817904249259</v>
       </c>
       <c r="E58">
-        <v>102.4457053266944</v>
+        <v>102.44570532669439</v>
       </c>
       <c r="F58">
-        <v>205.8290457947327</v>
+        <v>205.82904579473271</v>
       </c>
       <c r="G58">
-        <v>96.17678201502082</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
+        <v>96.176782015020819</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>5</v>
       </c>
@@ -4944,22 +6480,22 @@
         <v>64</v>
       </c>
       <c r="C59">
-        <v>26.414373490278</v>
+        <v>26.414373490277999</v>
       </c>
       <c r="D59">
-        <v>49.41629200298021</v>
+        <v>49.416292002980207</v>
       </c>
       <c r="E59">
         <v>104.569998812953</v>
       </c>
       <c r="F59">
-        <v>209.3666334498428</v>
+        <v>209.36663344984279</v>
       </c>
       <c r="G59">
-        <v>97.4418244390135</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
+        <v>97.441824439013502</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>5</v>
       </c>
@@ -4967,22 +6503,22 @@
         <v>65</v>
       </c>
       <c r="C60">
-        <v>25.06177259678004</v>
+        <v>25.061772596780042</v>
       </c>
       <c r="D60">
-        <v>50.21768795326422</v>
+        <v>50.217687953264218</v>
       </c>
       <c r="E60">
         <v>105.2369118846929</v>
       </c>
       <c r="F60">
-        <v>211.0487754972852</v>
+        <v>211.04877549728519</v>
       </c>
       <c r="G60">
-        <v>97.89128698300561</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
+        <v>97.891286983005614</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>5</v>
       </c>
@@ -4990,7 +6526,7 @@
         <v>66</v>
       </c>
       <c r="C61">
-        <v>26.05519988716055</v>
+        <v>26.055199887160551</v>
       </c>
       <c r="D61">
         <v>52.28288660312667</v>
@@ -4999,13 +6535,13 @@
         <v>105.108348609036</v>
       </c>
       <c r="F61">
-        <v>211.0430492799173</v>
+        <v>211.04304927991731</v>
       </c>
       <c r="G61">
-        <v>98.62237109481013</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
+        <v>98.622371094810134</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>5</v>
       </c>
@@ -5016,7 +6552,7 @@
         <v>25.55634918610405</v>
       </c>
       <c r="D62">
-        <v>54.04163056034262</v>
+        <v>54.041630560342618</v>
       </c>
       <c r="E62">
         <v>103.9827560572969</v>
@@ -5025,10 +6561,10 @@
         <v>214.0660171779821</v>
       </c>
       <c r="G62">
-        <v>99.41168824543142</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
+        <v>99.411688245431421</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>5</v>
       </c>
@@ -5036,7 +6572,7 @@
         <v>68</v>
       </c>
       <c r="C63">
-        <v>26.05519988716055</v>
+        <v>26.055199887160551</v>
       </c>
       <c r="D63">
         <v>52.28288660312667</v>
@@ -5048,10 +6584,10 @@
         <v>209.604943347925</v>
       </c>
       <c r="G63">
-        <v>97.81147411121466</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
+        <v>97.811474111214665</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>5</v>
       </c>
@@ -5059,22 +6595,22 @@
         <v>69</v>
       </c>
       <c r="C64">
-        <v>25.87705430228725</v>
+        <v>25.877054302287249</v>
       </c>
       <c r="D64">
-        <v>52.8500165541117</v>
+        <v>52.850016554111697</v>
       </c>
       <c r="E64">
         <v>106.5761026264193</v>
       </c>
       <c r="F64">
-        <v>214.0898403941825</v>
+        <v>214.08984039418249</v>
       </c>
       <c r="G64">
-        <v>99.84825346925018</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
+        <v>99.848253469250182</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>6</v>
       </c>
@@ -5082,19 +6618,19 @@
         <v>70</v>
       </c>
       <c r="C65">
-        <v>25.06177259678004</v>
+        <v>25.061772596780042</v>
       </c>
       <c r="D65">
         <v>52.28288660312667</v>
       </c>
       <c r="E65">
-        <v>100.9779513093111</v>
+        <v>100.97795130931109</v>
       </c>
       <c r="F65">
-        <v>211.0487754972852</v>
+        <v>211.04877549728519</v>
       </c>
       <c r="G65">
-        <v>97.34284650162576</v>
+        <v>97.342846501625758</v>
       </c>
     </row>
   </sheetData>
@@ -5103,11 +6639,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5130,7 +6666,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -5153,7 +6689,7 @@
         <v>152.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5176,7 +6712,7 @@
         <v>338.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -5199,7 +6735,7 @@
         <v>268.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -5222,7 +6758,7 @@
         <v>237.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -5245,7 +6781,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -5268,7 +6804,7 @@
         <v>152.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -5291,7 +6827,7 @@
         <v>139.25</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -5314,7 +6850,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -5337,7 +6873,7 @@
         <v>171.25</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -5360,7 +6896,7 @@
         <v>338.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -5383,7 +6919,7 @@
         <v>269.25</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2</v>
       </c>
@@ -5406,7 +6942,7 @@
         <v>268.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -5429,7 +6965,7 @@
         <v>279.75</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -5452,7 +6988,7 @@
         <v>210.75</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2</v>
       </c>
@@ -5475,7 +7011,7 @@
         <v>237.5</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2</v>
       </c>
@@ -5498,7 +7034,7 @@
         <v>264.25</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2</v>
       </c>
@@ -5521,7 +7057,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -5544,7 +7080,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -5567,7 +7103,7 @@
         <v>15.25</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
@@ -5590,7 +7126,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -5613,7 +7149,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2</v>
       </c>
@@ -5636,7 +7172,7 @@
         <v>139.25</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>3</v>
       </c>
@@ -5659,7 +7195,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>3</v>
       </c>
@@ -5682,7 +7218,7 @@
         <v>243.75</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>3</v>
       </c>
@@ -5705,7 +7241,7 @@
         <v>207.75</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>3</v>
       </c>
@@ -5728,7 +7264,7 @@
         <v>171.25</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -5751,7 +7287,7 @@
         <v>161.25</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>3</v>
       </c>
@@ -5774,7 +7310,7 @@
         <v>269.25</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
@@ -5797,7 +7333,7 @@
         <v>279.75</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
@@ -5820,7 +7356,7 @@
         <v>210.75</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
@@ -5843,7 +7379,7 @@
         <v>227.25</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>3</v>
       </c>
@@ -5866,7 +7402,7 @@
         <v>264.25</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>3</v>
       </c>
@@ -5889,7 +7425,7 @@
         <v>16.25</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>3</v>
       </c>
@@ -5912,7 +7448,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>3</v>
       </c>
@@ -5935,7 +7471,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>3</v>
       </c>
@@ -5958,7 +7494,7 @@
         <v>17.75</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>3</v>
       </c>
@@ -5981,7 +7517,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>3</v>
       </c>
@@ -6004,7 +7540,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3</v>
       </c>
@@ -6027,7 +7563,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>3</v>
       </c>
@@ -6050,7 +7586,7 @@
         <v>15.25</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>3</v>
       </c>
@@ -6073,7 +7609,7 @@
         <v>15.25</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3</v>
       </c>
@@ -6096,7 +7632,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>4</v>
       </c>
@@ -6119,7 +7655,7 @@
         <v>243.75</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>4</v>
       </c>
@@ -6142,7 +7678,7 @@
         <v>207.75</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>4</v>
       </c>
@@ -6165,7 +7701,7 @@
         <v>231.25</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>4</v>
       </c>
@@ -6188,7 +7724,7 @@
         <v>161.25</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>4</v>
       </c>
@@ -6211,7 +7747,7 @@
         <v>227.25</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>4</v>
       </c>
@@ -6234,7 +7770,7 @@
         <v>16.25</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>4</v>
       </c>
@@ -6257,7 +7793,7 @@
         <v>17.75</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>4</v>
       </c>
@@ -6280,7 +7816,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>4</v>
       </c>
@@ -6303,7 +7839,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>4</v>
       </c>
@@ -6326,7 +7862,7 @@
         <v>18.25</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>4</v>
       </c>
@@ -6349,7 +7885,7 @@
         <v>17.75</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>4</v>
       </c>
@@ -6372,7 +7908,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>4</v>
       </c>
@@ -6395,7 +7931,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>4</v>
       </c>
@@ -6418,7 +7954,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>4</v>
       </c>
@@ -6441,7 +7977,7 @@
         <v>15.25</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>5</v>
       </c>
@@ -6464,7 +8000,7 @@
         <v>231.25</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>5</v>
       </c>
@@ -6487,7 +8023,7 @@
         <v>17.75</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>5</v>
       </c>
@@ -6510,7 +8046,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>5</v>
       </c>
@@ -6533,7 +8069,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>5</v>
       </c>
@@ -6556,7 +8092,7 @@
         <v>18.25</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>5</v>
       </c>
@@ -6579,7 +8115,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>6</v>
       </c>
@@ -6608,11 +8144,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6635,7 +8171,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -6658,7 +8194,7 @@
         <v>1378.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -6681,7 +8217,7 @@
         <v>1201.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -6704,7 +8240,7 @@
         <v>703.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -6727,7 +8263,7 @@
         <v>998.75</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -6750,7 +8286,7 @@
         <v>40.75</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -6773,7 +8309,7 @@
         <v>1378.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -6796,7 +8332,7 @@
         <v>1398.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -6819,7 +8355,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -6842,7 +8378,7 @@
         <v>979.75</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -6865,7 +8401,7 @@
         <v>1201.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -6888,7 +8424,7 @@
         <v>1164.75</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2</v>
       </c>
@@ -6911,7 +8447,7 @@
         <v>703.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -6934,7 +8470,7 @@
         <v>694.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -6957,7 +8493,7 @@
         <v>881.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2</v>
       </c>
@@ -6980,7 +8516,7 @@
         <v>998.75</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2</v>
       </c>
@@ -7003,7 +8539,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2</v>
       </c>
@@ -7026,7 +8562,7 @@
         <v>33.75</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -7049,7 +8585,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -7072,7 +8608,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
@@ -7095,7 +8631,7 @@
         <v>40.75</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -7118,7 +8654,7 @@
         <v>37.25</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2</v>
       </c>
@@ -7141,7 +8677,7 @@
         <v>1398.5</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>3</v>
       </c>
@@ -7164,7 +8700,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>3</v>
       </c>
@@ -7187,7 +8723,7 @@
         <v>703.25</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>3</v>
       </c>
@@ -7210,7 +8746,7 @@
         <v>836.75</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>3</v>
       </c>
@@ -7233,7 +8769,7 @@
         <v>979.75</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -7256,7 +8792,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>3</v>
       </c>
@@ -7279,7 +8815,7 @@
         <v>1164.75</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
@@ -7302,7 +8838,7 @@
         <v>694.5</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
@@ -7325,7 +8861,7 @@
         <v>881.5</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
@@ -7348,7 +8884,7 @@
         <v>886.75</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>3</v>
       </c>
@@ -7371,7 +8907,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>3</v>
       </c>
@@ -7394,7 +8930,7 @@
         <v>36.25</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>3</v>
       </c>
@@ -7417,7 +8953,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>3</v>
       </c>
@@ -7440,7 +8976,7 @@
         <v>33.75</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>3</v>
       </c>
@@ -7463,7 +8999,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>3</v>
       </c>
@@ -7486,7 +9022,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>3</v>
       </c>
@@ -7509,7 +9045,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3</v>
       </c>
@@ -7532,7 +9068,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>3</v>
       </c>
@@ -7555,7 +9091,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>3</v>
       </c>
@@ -7578,7 +9114,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3</v>
       </c>
@@ -7601,7 +9137,7 @@
         <v>37.25</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>4</v>
       </c>
@@ -7624,7 +9160,7 @@
         <v>703.25</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>4</v>
       </c>
@@ -7647,7 +9183,7 @@
         <v>836.75</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>4</v>
       </c>
@@ -7670,7 +9206,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>4</v>
       </c>
@@ -7693,7 +9229,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>4</v>
       </c>
@@ -7716,7 +9252,7 @@
         <v>886.75</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>4</v>
       </c>
@@ -7739,7 +9275,7 @@
         <v>36.25</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>4</v>
       </c>
@@ -7762,7 +9298,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>4</v>
       </c>
@@ -7785,7 +9321,7 @@
         <v>38.25</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>4</v>
       </c>
@@ -7808,7 +9344,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>4</v>
       </c>
@@ -7831,7 +9367,7 @@
         <v>45.75</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>4</v>
       </c>
@@ -7854,7 +9390,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>4</v>
       </c>
@@ -7877,7 +9413,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>4</v>
       </c>
@@ -7900,7 +9436,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>4</v>
       </c>
@@ -7923,7 +9459,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>4</v>
       </c>
@@ -7946,7 +9482,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>5</v>
       </c>
@@ -7969,7 +9505,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>5</v>
       </c>
@@ -7992,7 +9528,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>5</v>
       </c>
@@ -8015,7 +9551,7 @@
         <v>38.25</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>5</v>
       </c>
@@ -8038,7 +9574,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>5</v>
       </c>
@@ -8061,7 +9597,7 @@
         <v>45.75</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>5</v>
       </c>
@@ -8084,7 +9620,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>6</v>
       </c>
@@ -8113,11 +9649,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8140,7 +9676,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -8163,7 +9699,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -8186,7 +9722,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -8209,7 +9745,7 @@
         <v>16.75</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -8232,7 +9768,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -8255,7 +9791,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -8278,7 +9814,7 @@
         <v>8.25</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -8301,7 +9837,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -8324,7 +9860,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -8347,7 +9883,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -8370,7 +9906,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -8393,7 +9929,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2</v>
       </c>
@@ -8416,7 +9952,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -8439,7 +9975,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -8462,7 +9998,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2</v>
       </c>
@@ -8485,7 +10021,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2</v>
       </c>
@@ -8508,7 +10044,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2</v>
       </c>
@@ -8531,7 +10067,7 @@
         <v>11.75</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -8554,7 +10090,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -8577,7 +10113,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
@@ -8600,7 +10136,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -8623,7 +10159,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2</v>
       </c>
@@ -8646,7 +10182,7 @@
         <v>8.25</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>3</v>
       </c>
@@ -8669,7 +10205,7 @@
         <v>9.25</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>3</v>
       </c>
@@ -8692,7 +10228,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>3</v>
       </c>
@@ -8715,7 +10251,7 @@
         <v>16.75</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>3</v>
       </c>
@@ -8738,7 +10274,7 @@
         <v>9.75</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -8761,7 +10297,7 @@
         <v>17.75</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>3</v>
       </c>
@@ -8784,7 +10320,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
@@ -8807,7 +10343,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
@@ -8830,7 +10366,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
@@ -8853,7 +10389,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>3</v>
       </c>
@@ -8876,7 +10412,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>3</v>
       </c>
@@ -8899,7 +10435,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>3</v>
       </c>
@@ -8922,7 +10458,7 @@
         <v>13.75</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>3</v>
       </c>
@@ -8945,7 +10481,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>3</v>
       </c>
@@ -8968,7 +10504,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>3</v>
       </c>
@@ -8991,7 +10527,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>3</v>
       </c>
@@ -9014,7 +10550,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3</v>
       </c>
@@ -9037,7 +10573,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>3</v>
       </c>
@@ -9060,7 +10596,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>3</v>
       </c>
@@ -9083,7 +10619,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3</v>
       </c>
@@ -9106,7 +10642,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>4</v>
       </c>
@@ -9129,7 +10665,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>4</v>
       </c>
@@ -9152,7 +10688,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>4</v>
       </c>
@@ -9175,7 +10711,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>4</v>
       </c>
@@ -9198,7 +10734,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>4</v>
       </c>
@@ -9221,7 +10757,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>4</v>
       </c>
@@ -9244,7 +10780,7 @@
         <v>9.75</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>4</v>
       </c>
@@ -9267,7 +10803,7 @@
         <v>12.75</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>4</v>
       </c>
@@ -9290,7 +10826,7 @@
         <v>13.75</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>4</v>
       </c>
@@ -9313,7 +10849,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>4</v>
       </c>
@@ -9336,7 +10872,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>4</v>
       </c>
@@ -9359,7 +10895,7 @@
         <v>9.75</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>4</v>
       </c>
@@ -9382,7 +10918,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>4</v>
       </c>
@@ -9405,7 +10941,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>4</v>
       </c>
@@ -9428,7 +10964,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>4</v>
       </c>
@@ -9451,7 +10987,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>5</v>
       </c>
@@ -9474,7 +11010,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>5</v>
       </c>
@@ -9497,7 +11033,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>5</v>
       </c>
@@ -9520,7 +11056,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>5</v>
       </c>
@@ -9543,7 +11079,7 @@
         <v>12.75</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>5</v>
       </c>
@@ -9566,7 +11102,7 @@
         <v>10.25</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>5</v>
       </c>
@@ -9589,7 +11125,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>6</v>
       </c>

--- a/Excel/Validasi/Hasil_Pengujian_Map_1_128_avg_length.xlsx
+++ b/Excel/Validasi/Hasil_Pengujian_Map_1_128_avg_length.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEMHAS\TA_Python_Server\Excel\Validasi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B759D762-FA6F-4882-AC7C-E4072AC48D15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9968E71-DC3B-478B-B47F-8ED2D38AF7E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="55">
   <si>
     <t>Jumlah Kombinasi</t>
   </si>
@@ -108,9 +108,6 @@
     <t>JPS-PPO</t>
   </si>
   <si>
-    <t>JPS-TPF</t>
-  </si>
-  <si>
     <t>TPF-PPO</t>
   </si>
   <si>
@@ -153,25 +150,13 @@
     <t>JPS-BDS-PPO</t>
   </si>
   <si>
-    <t>JPS-BDS-TPF</t>
-  </si>
-  <si>
     <t>JPS-BRC-PPO</t>
-  </si>
-  <si>
-    <t>JPS-BRC-TPF</t>
   </si>
   <si>
     <t>JPS-GL-BRC</t>
   </si>
   <si>
     <t>JPS-GL-PPO</t>
-  </si>
-  <si>
-    <t>JPS-GL-TPF</t>
-  </si>
-  <si>
-    <t>JPS-TPF-PPO</t>
   </si>
   <si>
     <t>BDS-BRC-TPF-PPO</t>
@@ -192,52 +177,19 @@
     <t>JPS-BDS-BRC-PPO</t>
   </si>
   <si>
-    <t>JPS-BDS-BRC-TPF</t>
-  </si>
-  <si>
     <t>JPS-BDS-GL-BRC</t>
   </si>
   <si>
     <t>JPS-BDS-GL-PPO</t>
   </si>
   <si>
-    <t>JPS-BDS-GL-TPF</t>
-  </si>
-  <si>
-    <t>JPS-BDS-TPF-PPO</t>
-  </si>
-  <si>
-    <t>JPS-BRC-TPF-PPO</t>
-  </si>
-  <si>
     <t>JPS-GL-BRC-PPO</t>
-  </si>
-  <si>
-    <t>JPS-GL-BRC-TPF</t>
-  </si>
-  <si>
-    <t>JPS-GL-TPF-PPO</t>
   </si>
   <si>
     <t>BDS-GL-BRC-TPF-PPO</t>
   </si>
   <si>
-    <t>JPS-BDS-BRC-TPF-PPO</t>
-  </si>
-  <si>
     <t>JPS-BDS-GL-BRC-PPO</t>
-  </si>
-  <si>
-    <t>JPS-BDS-GL-BRC-TPF</t>
-  </si>
-  <si>
-    <t>JPS-BDS-GL-TPF-PPO</t>
-  </si>
-  <si>
-    <t>JPS-GL-BRC-TPF-PPO</t>
-  </si>
-  <si>
-    <t>JPS-BDS-GL-BRC-TPF-PPO</t>
   </si>
 </sst>
 </file>
@@ -433,16 +385,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>4.9179999999999992E-4</c:v>
+                  <c:v>4.9379999999999997E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.0006E-3</c:v>
+                  <c:v>2.8850999999999998E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.9612999999999998E-2</c:v>
+                  <c:v>1.8933499999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.13250819999999999</c:v>
+                  <c:v>0.12529689999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -450,7 +402,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A2B1-4D75-8551-FB4AFADF9BB4}"/>
+              <c16:uniqueId val="{00000000-4C9B-4881-8EED-80B5538409C7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -519,16 +471,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>3.1330000000000003E-4</c:v>
+                  <c:v>2.7970000000000002E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.3492999999999999E-3</c:v>
+                  <c:v>1.2294000000000001E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.1652E-3</c:v>
+                  <c:v>4.9227000000000003E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.2051600000000001E-2</c:v>
+                  <c:v>2.0550700000000002E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -536,7 +488,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-A2B1-4D75-8551-FB4AFADF9BB4}"/>
+              <c16:uniqueId val="{00000001-4C9B-4881-8EED-80B5538409C7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -605,16 +557,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>4.5659999999999999E-4</c:v>
+                  <c:v>4.5229999999999988E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.1857999999999999E-3</c:v>
+                  <c:v>2.020399999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.72503E-2</c:v>
+                  <c:v>1.6072300000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.18647659999999999</c:v>
+                  <c:v>0.18012449999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -622,7 +574,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-A2B1-4D75-8551-FB4AFADF9BB4}"/>
+              <c16:uniqueId val="{00000002-4C9B-4881-8EED-80B5538409C7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -691,16 +643,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>4.2789999999999999E-4</c:v>
+                  <c:v>4.0739999999999987E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.3919000000000002E-3</c:v>
+                  <c:v>2.2921E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.65019E-2</c:v>
+                  <c:v>1.5739400000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.1149251</c:v>
+                  <c:v>0.1123504</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -708,7 +660,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-A2B1-4D75-8551-FB4AFADF9BB4}"/>
+              <c16:uniqueId val="{00000003-4C9B-4881-8EED-80B5538409C7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -777,16 +729,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>3.6749999999999999E-4</c:v>
+                  <c:v>3.5849999999999999E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0816000000000001E-3</c:v>
+                  <c:v>1.0181000000000001E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.5506000000000001E-3</c:v>
+                  <c:v>3.5002000000000002E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.29208E-2</c:v>
+                  <c:v>1.2126899999999999E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -794,7 +746,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-A2B1-4D75-8551-FB4AFADF9BB4}"/>
+              <c16:uniqueId val="{00000004-4C9B-4881-8EED-80B5538409C7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -863,16 +815,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>5.9119999999999995E-4</c:v>
+                  <c:v>5.6109999999999992E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.1369000000000002E-3</c:v>
+                  <c:v>2.9761000000000002E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.9774799999999999E-2</c:v>
+                  <c:v>1.9082100000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.13209070000000001</c:v>
+                  <c:v>0.1257644</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -880,7 +832,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-A2B1-4D75-8551-FB4AFADF9BB4}"/>
+              <c16:uniqueId val="{00000005-4C9B-4881-8EED-80B5538409C7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -955,16 +907,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>5.350000000000001E-4</c:v>
+                  <c:v>5.2979999999999998E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.8988E-3</c:v>
+                  <c:v>2.8898000000000001E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.8714100000000001E-2</c:v>
+                  <c:v>1.7512699999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.12540699999999999</c:v>
+                  <c:v>0.1189119</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -972,7 +924,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-A2B1-4D75-8551-FB4AFADF9BB4}"/>
+              <c16:uniqueId val="{00000006-4C9B-4881-8EED-80B5538409C7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1000,11 +952,11 @@
         </c:hiLowLines>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="1087410447"/>
-        <c:axId val="1087413807"/>
+        <c:axId val="693613583"/>
+        <c:axId val="693570863"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1087410447"/>
+        <c:axId val="693613583"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1077,7 +1029,7 @@
             <a:endParaRPr lang="id-ID"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1087413807"/>
+        <c:crossAx val="693570863"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1085,7 +1037,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1087413807"/>
+        <c:axId val="693570863"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1166,7 +1118,7 @@
             <a:endParaRPr lang="id-ID"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1087410447"/>
+        <c:crossAx val="693613583"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1816,7 +1768,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9AF63F3B-A941-1ABF-DF4B-DE83F87300AC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80C790E0-5C57-54A4-2B28-4435CFB00C3F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1840,7 +1792,7 @@
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Red Orange">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1848,34 +1800,34 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="505046"/>
       </a:dk2>
       <a:lt2>
         <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="E84C22"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="FFBD47"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="B64926"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FF8427"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="CC9900"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="B22600"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="CC9900"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="666699"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office 2007 - 2010">
@@ -2124,7 +2076,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -2158,19 +2110,19 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>4.9179999999999992E-4</v>
+        <v>4.9379999999999997E-4</v>
       </c>
       <c r="D2">
-        <v>3.0006E-3</v>
+        <v>2.8850999999999998E-3</v>
       </c>
       <c r="E2">
-        <v>1.9612999999999998E-2</v>
+        <v>1.8933499999999999E-2</v>
       </c>
       <c r="F2">
-        <v>0.13250819999999999</v>
+        <v>0.12529689999999999</v>
       </c>
       <c r="G2">
-        <v>3.8903399999999998E-2</v>
+        <v>3.6902325E-2</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -2181,19 +2133,19 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>3.1330000000000003E-4</v>
+        <v>2.7970000000000002E-4</v>
       </c>
       <c r="D3">
-        <v>1.3492999999999999E-3</v>
+        <v>1.2294000000000001E-3</v>
       </c>
       <c r="E3">
-        <v>5.1652E-3</v>
+        <v>4.9227000000000003E-3</v>
       </c>
       <c r="F3">
-        <v>2.2051600000000001E-2</v>
+        <v>2.0550700000000002E-2</v>
       </c>
       <c r="G3">
-        <v>7.2198499999999999E-3</v>
+        <v>6.7456250000000008E-3</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -2204,19 +2156,19 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>4.5659999999999999E-4</v>
+        <v>4.5229999999999988E-4</v>
       </c>
       <c r="D4">
-        <v>2.1857999999999999E-3</v>
+        <v>2.020399999999999E-3</v>
       </c>
       <c r="E4">
-        <v>1.72503E-2</v>
+        <v>1.6072300000000001E-2</v>
       </c>
       <c r="F4">
-        <v>0.18647659999999999</v>
+        <v>0.18012449999999999</v>
       </c>
       <c r="G4">
-        <v>5.1592325000000008E-2</v>
+        <v>4.9667374999999993E-2</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -2227,19 +2179,19 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>4.2789999999999999E-4</v>
+        <v>4.0739999999999987E-4</v>
       </c>
       <c r="D5">
-        <v>2.3919000000000002E-3</v>
+        <v>2.2921E-3</v>
       </c>
       <c r="E5">
-        <v>1.65019E-2</v>
+        <v>1.5739400000000001E-2</v>
       </c>
       <c r="F5">
-        <v>0.1149251</v>
+        <v>0.1123504</v>
       </c>
       <c r="G5">
-        <v>3.35617E-2</v>
+        <v>3.2697324999999999E-2</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -2250,19 +2202,19 @@
         <v>11</v>
       </c>
       <c r="C6">
-        <v>3.6749999999999999E-4</v>
+        <v>3.5849999999999999E-4</v>
       </c>
       <c r="D6">
-        <v>1.0816000000000001E-3</v>
+        <v>1.0181000000000001E-3</v>
       </c>
       <c r="E6">
-        <v>3.5506000000000001E-3</v>
+        <v>3.5002000000000002E-3</v>
       </c>
       <c r="F6">
-        <v>1.29208E-2</v>
+        <v>1.2126899999999999E-2</v>
       </c>
       <c r="G6">
-        <v>4.4801249999999997E-3</v>
+        <v>4.250925E-3</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -2273,19 +2225,19 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>5.9119999999999995E-4</v>
+        <v>5.6109999999999992E-4</v>
       </c>
       <c r="D7">
-        <v>3.1369000000000002E-3</v>
+        <v>2.9761000000000002E-3</v>
       </c>
       <c r="E7">
-        <v>1.9774799999999999E-2</v>
+        <v>1.9082100000000001E-2</v>
       </c>
       <c r="F7">
-        <v>0.13209070000000001</v>
+        <v>0.1257644</v>
       </c>
       <c r="G7">
-        <v>3.88984E-2</v>
+        <v>3.7095925000000002E-2</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -2296,19 +2248,19 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>5.350000000000001E-4</v>
+        <v>5.2979999999999998E-4</v>
       </c>
       <c r="D8">
-        <v>2.8988E-3</v>
+        <v>2.8898000000000001E-3</v>
       </c>
       <c r="E8">
-        <v>1.8714100000000001E-2</v>
+        <v>1.7512699999999999E-2</v>
       </c>
       <c r="F8">
-        <v>0.12540699999999999</v>
+        <v>0.1189119</v>
       </c>
       <c r="G8">
-        <v>3.6888724999999997E-2</v>
+        <v>3.4961049999999987E-2</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -2319,19 +2271,19 @@
         <v>14</v>
       </c>
       <c r="C9">
-        <v>4.8879999999999996E-4</v>
+        <v>4.6579999999999999E-4</v>
       </c>
       <c r="D9">
-        <v>1.8496999999999999E-3</v>
+        <v>1.7442E-3</v>
       </c>
       <c r="E9">
-        <v>8.8884000000000012E-3</v>
+        <v>8.5352000000000015E-3</v>
       </c>
       <c r="F9">
-        <v>5.5286200000000008E-2</v>
+        <v>5.1208799999999999E-2</v>
       </c>
       <c r="G9">
-        <v>1.6628275000000001E-2</v>
+        <v>1.5488500000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -2342,19 +2294,19 @@
         <v>15</v>
       </c>
       <c r="C10">
-        <v>3.3730000000000001E-4</v>
+        <v>3.4220000000000002E-4</v>
       </c>
       <c r="D10">
-        <v>1.4367E-3</v>
+        <v>1.3734000000000001E-3</v>
       </c>
       <c r="E10">
-        <v>6.1827999999999996E-3</v>
+        <v>5.916600000000001E-3</v>
       </c>
       <c r="F10">
-        <v>2.61967E-2</v>
+        <v>2.4535499999999998E-2</v>
       </c>
       <c r="G10">
-        <v>8.5383750000000008E-3</v>
+        <v>8.0419250000000001E-3</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -2365,19 +2317,19 @@
         <v>16</v>
       </c>
       <c r="C11">
-        <v>3.6059999999999998E-4</v>
+        <v>3.1639999999999999E-4</v>
       </c>
       <c r="D11">
-        <v>1.4063999999999999E-3</v>
+        <v>1.3039E-3</v>
       </c>
       <c r="E11">
-        <v>5.6705999999999996E-3</v>
+        <v>5.0924999999999998E-3</v>
       </c>
       <c r="F11">
-        <v>2.30846E-2</v>
+        <v>2.12602E-2</v>
       </c>
       <c r="G11">
-        <v>7.6305499999999998E-3</v>
+        <v>6.9932499999999986E-3</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -2388,19 +2340,19 @@
         <v>17</v>
       </c>
       <c r="C12">
-        <v>3.6240000000000003E-4</v>
+        <v>3.4200000000000002E-4</v>
       </c>
       <c r="D12">
-        <v>1.5202E-3</v>
+        <v>1.4683000000000001E-3</v>
       </c>
       <c r="E12">
-        <v>5.6723999999999993E-3</v>
+        <v>5.4098999999999996E-3</v>
       </c>
       <c r="F12">
-        <v>2.2777499999999999E-2</v>
+        <v>2.1597700000000001E-2</v>
       </c>
       <c r="G12">
-        <v>7.5831249999999996E-3</v>
+        <v>7.204475000000001E-3</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -2411,19 +2363,19 @@
         <v>18</v>
       </c>
       <c r="C13">
-        <v>4.9349999999999991E-4</v>
+        <v>4.6440000000000001E-4</v>
       </c>
       <c r="D13">
-        <v>2.3208E-3</v>
+        <v>2.2074E-3</v>
       </c>
       <c r="E13">
-        <v>1.7496500000000002E-2</v>
+        <v>1.6632299999999999E-2</v>
       </c>
       <c r="F13">
-        <v>0.188642</v>
+        <v>0.17948030000000001</v>
       </c>
       <c r="G13">
-        <v>5.2238199999999999E-2</v>
+        <v>4.9696099999999993E-2</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -2434,19 +2386,19 @@
         <v>19</v>
       </c>
       <c r="C14">
-        <v>5.176E-4</v>
+        <v>4.9330000000000001E-4</v>
       </c>
       <c r="D14">
-        <v>2.2897E-3</v>
+        <v>2.2282000000000001E-3</v>
       </c>
       <c r="E14">
-        <v>1.72479E-2</v>
+        <v>1.61285E-2</v>
       </c>
       <c r="F14">
-        <v>0.17534749999999999</v>
+        <v>0.17113900000000001</v>
       </c>
       <c r="G14">
-        <v>4.8850675000000003E-2</v>
+        <v>4.7497249999999998E-2</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -2457,19 +2409,19 @@
         <v>20</v>
       </c>
       <c r="C15">
-        <v>5.5420000000000003E-4</v>
+        <v>5.107E-4</v>
       </c>
       <c r="D15">
-        <v>2.9753000000000002E-3</v>
+        <v>2.7369999999999998E-3</v>
       </c>
       <c r="E15">
-        <v>2.1729499999999999E-2</v>
+        <v>2.0884699999999999E-2</v>
       </c>
       <c r="F15">
-        <v>0.22212699999999999</v>
+        <v>0.21187819999999999</v>
       </c>
       <c r="G15">
-        <v>6.1846500000000013E-2</v>
+        <v>5.9002649999999997E-2</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -2480,19 +2432,19 @@
         <v>21</v>
       </c>
       <c r="C16">
-        <v>4.5810000000000002E-4</v>
+        <v>4.5580000000000002E-4</v>
       </c>
       <c r="D16">
-        <v>2.5498999999999999E-3</v>
+        <v>2.4453000000000001E-3</v>
       </c>
       <c r="E16">
-        <v>1.6830100000000001E-2</v>
+        <v>1.6251600000000001E-2</v>
       </c>
       <c r="F16">
-        <v>0.1159927</v>
+        <v>0.11184620000000001</v>
       </c>
       <c r="G16">
-        <v>3.39577E-2</v>
+        <v>3.2749725E-2</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -2503,19 +2455,19 @@
         <v>22</v>
       </c>
       <c r="C17">
-        <v>5.8020000000000012E-4</v>
+        <v>5.5910000000000009E-4</v>
       </c>
       <c r="D17">
-        <v>3.556300000000001E-3</v>
+        <v>3.4920000000000012E-3</v>
       </c>
       <c r="E17">
-        <v>1.6618999999999998E-2</v>
+        <v>1.6085700000000001E-2</v>
       </c>
       <c r="F17">
-        <v>0.1112421</v>
+        <v>0.106137</v>
       </c>
       <c r="G17">
-        <v>3.2999400000000012E-2</v>
+        <v>3.1568449999999998E-2</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -2526,19 +2478,19 @@
         <v>23</v>
       </c>
       <c r="C18">
-        <v>3.7080000000000001E-4</v>
+        <v>3.7500000000000001E-4</v>
       </c>
       <c r="D18">
-        <v>9.771999999999999E-4</v>
+        <v>9.4190000000000007E-4</v>
       </c>
       <c r="E18">
-        <v>3.0330000000000001E-3</v>
+        <v>2.9147999999999999E-3</v>
       </c>
       <c r="F18">
-        <v>1.14609E-2</v>
+        <v>1.06172E-2</v>
       </c>
       <c r="G18">
-        <v>3.9604749999999998E-3</v>
+        <v>3.712225E-3</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -2549,19 +2501,19 @@
         <v>24</v>
       </c>
       <c r="C19">
-        <v>3.2079999999999999E-4</v>
+        <v>3.212E-4</v>
       </c>
       <c r="D19">
-        <v>1.0382E-3</v>
+        <v>9.323999999999999E-4</v>
       </c>
       <c r="E19">
-        <v>3.2720000000000002E-3</v>
+        <v>3.1335E-3</v>
       </c>
       <c r="F19">
-        <v>1.24311E-2</v>
+        <v>1.15268E-2</v>
       </c>
       <c r="G19">
-        <v>4.265525E-3</v>
+        <v>3.9784750000000004E-3</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -2572,19 +2524,19 @@
         <v>25</v>
       </c>
       <c r="C20">
-        <v>3.701E-4</v>
+        <v>4.7649999999999993E-4</v>
       </c>
       <c r="D20">
-        <v>1.1515E-3</v>
+        <v>1.1236E-3</v>
       </c>
       <c r="E20">
-        <v>3.7772000000000001E-3</v>
+        <v>3.5431999999999998E-3</v>
       </c>
       <c r="F20">
-        <v>1.40915E-2</v>
+        <v>1.3403200000000001E-2</v>
       </c>
       <c r="G20">
-        <v>4.8475749999999998E-3</v>
+        <v>4.6366250000000001E-3</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -2595,19 +2547,19 @@
         <v>26</v>
       </c>
       <c r="C21">
-        <v>4.1070000000000012E-4</v>
+        <v>3.926E-4</v>
       </c>
       <c r="D21">
-        <v>1.2167E-3</v>
+        <v>1.0494E-3</v>
       </c>
       <c r="E21">
-        <v>3.600299999999999E-3</v>
+        <v>3.3776000000000001E-3</v>
       </c>
       <c r="F21">
-        <v>1.2908899999999999E-2</v>
+        <v>1.1986200000000001E-2</v>
       </c>
       <c r="G21">
-        <v>4.5341499999999998E-3</v>
+        <v>4.2014499999999998E-3</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -2618,42 +2570,42 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>3.5649999999999999E-4</v>
+        <v>5.6949999999999991E-4</v>
       </c>
       <c r="D22">
-        <v>1.2822E-3</v>
+        <v>2.9991000000000002E-3</v>
       </c>
       <c r="E22">
-        <v>3.1846999999999999E-3</v>
+        <v>1.7790400000000001E-2</v>
       </c>
       <c r="F22">
-        <v>1.14371E-2</v>
+        <v>0.1218943</v>
       </c>
       <c r="G22">
-        <v>4.0651250000000002E-3</v>
+        <v>3.5813325000000007E-2</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="s">
         <v>28</v>
       </c>
       <c r="C23">
-        <v>5.8569999999999998E-4</v>
+        <v>4.9589999999999996E-4</v>
       </c>
       <c r="D23">
-        <v>3.0051000000000001E-3</v>
+        <v>1.7639999999999999E-3</v>
       </c>
       <c r="E23">
-        <v>1.88002E-2</v>
+        <v>8.8319000000000002E-3</v>
       </c>
       <c r="F23">
-        <v>0.1267848</v>
+        <v>5.2588099999999992E-2</v>
       </c>
       <c r="G23">
-        <v>3.7293949999999992E-2</v>
+        <v>1.5919974999999999E-2</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -2664,19 +2616,19 @@
         <v>29</v>
       </c>
       <c r="C24">
-        <v>5.3010000000000004E-4</v>
+        <v>4.3619999999999998E-4</v>
       </c>
       <c r="D24">
-        <v>1.9467E-3</v>
+        <v>1.9517E-3</v>
       </c>
       <c r="E24">
-        <v>9.1855999999999986E-3</v>
+        <v>9.2374000000000015E-3</v>
       </c>
       <c r="F24">
-        <v>5.62427E-2</v>
+        <v>5.3368100000000009E-2</v>
       </c>
       <c r="G24">
-        <v>1.6976274999999999E-2</v>
+        <v>1.6248350000000002E-2</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -2687,19 +2639,19 @@
         <v>30</v>
       </c>
       <c r="C25">
-        <v>5.1360000000000002E-4</v>
+        <v>5.1239999999999999E-4</v>
       </c>
       <c r="D25">
-        <v>2.0585999999999998E-3</v>
+        <v>2.7553999999999999E-3</v>
       </c>
       <c r="E25">
-        <v>9.4767999999999988E-3</v>
+        <v>1.35646E-2</v>
       </c>
       <c r="F25">
-        <v>5.6122699999999998E-2</v>
+        <v>8.7090799999999996E-2</v>
       </c>
       <c r="G25">
-        <v>1.7042925E-2</v>
+        <v>2.5980799999999998E-2</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -2710,19 +2662,19 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>5.4760000000000008E-4</v>
+        <v>3.5090000000000002E-4</v>
       </c>
       <c r="D26">
-        <v>3.0068999999999999E-3</v>
+        <v>1.4966000000000001E-3</v>
       </c>
       <c r="E26">
-        <v>1.42595E-2</v>
+        <v>6.0125999999999999E-3</v>
       </c>
       <c r="F26">
-        <v>9.2565999999999996E-2</v>
+        <v>2.53899E-2</v>
       </c>
       <c r="G26">
-        <v>2.7595000000000001E-2</v>
+        <v>8.3125000000000004E-3</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -2733,19 +2685,19 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>4.0939999999999998E-4</v>
+        <v>3.7240000000000011E-4</v>
       </c>
       <c r="D27">
-        <v>1.6724999999999999E-3</v>
+        <v>1.6012999999999999E-3</v>
       </c>
       <c r="E27">
-        <v>6.4419000000000004E-3</v>
+        <v>6.2833999999999997E-3</v>
       </c>
       <c r="F27">
-        <v>2.7212699999999999E-2</v>
+        <v>2.7113999999999999E-2</v>
       </c>
       <c r="G27">
-        <v>8.9341249999999994E-3</v>
+        <v>8.8427750000000006E-3</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -2756,19 +2708,19 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>3.836E-4</v>
+        <v>3.9300000000000001E-4</v>
       </c>
       <c r="D28">
-        <v>1.5914E-3</v>
+        <v>1.555E-3</v>
       </c>
       <c r="E28">
-        <v>6.5757999999999997E-3</v>
+        <v>5.8628999999999999E-3</v>
       </c>
       <c r="F28">
-        <v>2.7155499999999999E-2</v>
+        <v>2.26804E-2</v>
       </c>
       <c r="G28">
-        <v>8.9265749999999991E-3</v>
+        <v>7.6228249999999997E-3</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -2779,19 +2731,19 @@
         <v>34</v>
       </c>
       <c r="C29">
-        <v>4.1899999999999999E-4</v>
+        <v>5.3459999999999988E-4</v>
       </c>
       <c r="D29">
-        <v>1.5942E-3</v>
+        <v>2.2845999999999999E-3</v>
       </c>
       <c r="E29">
-        <v>5.9845000000000002E-3</v>
+        <v>1.6494499999999999E-2</v>
       </c>
       <c r="F29">
-        <v>2.3904999999999999E-2</v>
+        <v>0.17120179999999999</v>
       </c>
       <c r="G29">
-        <v>7.9756750000000015E-3</v>
+        <v>4.7628875000000001E-2</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -2802,19 +2754,19 @@
         <v>35</v>
       </c>
       <c r="C30">
-        <v>5.8529999999999997E-4</v>
+        <v>5.5150000000000002E-4</v>
       </c>
       <c r="D30">
-        <v>2.4126999999999998E-3</v>
+        <v>2.8059000000000001E-3</v>
       </c>
       <c r="E30">
-        <v>1.7335799999999998E-2</v>
+        <v>2.11451E-2</v>
       </c>
       <c r="F30">
-        <v>0.1762128</v>
+        <v>0.21209259999999999</v>
       </c>
       <c r="G30">
-        <v>4.9136649999999997E-2</v>
+        <v>5.9148775000000001E-2</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -2825,19 +2777,19 @@
         <v>36</v>
       </c>
       <c r="C31">
-        <v>5.9329999999999995E-4</v>
+        <v>5.5210000000000003E-4</v>
       </c>
       <c r="D31">
-        <v>3.0466999999999998E-3</v>
+        <v>2.9053E-3</v>
       </c>
       <c r="E31">
-        <v>2.1886699999999999E-2</v>
+        <v>2.1082099999999999E-2</v>
       </c>
       <c r="F31">
-        <v>0.2224198</v>
+        <v>0.20836560000000001</v>
       </c>
       <c r="G31">
-        <v>6.1986624999999997E-2</v>
+        <v>5.8226274999999987E-2</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -2848,19 +2800,19 @@
         <v>37</v>
       </c>
       <c r="C32">
-        <v>6.0160000000000009E-4</v>
+        <v>5.824999999999999E-4</v>
       </c>
       <c r="D32">
-        <v>2.9675000000000001E-3</v>
+        <v>3.4924999999999999E-3</v>
       </c>
       <c r="E32">
-        <v>2.18362E-2</v>
+        <v>1.6322199999999999E-2</v>
       </c>
       <c r="F32">
-        <v>0.21738499999999999</v>
+        <v>0.106556</v>
       </c>
       <c r="G32">
-        <v>6.0697574999999997E-2</v>
+        <v>3.1738299999999997E-2</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -2871,19 +2823,19 @@
         <v>38</v>
       </c>
       <c r="C33">
-        <v>6.2040000000000001E-4</v>
+        <v>4.2739999999999998E-4</v>
       </c>
       <c r="D33">
-        <v>4.1529999999999996E-3</v>
+        <v>1.1126E-3</v>
       </c>
       <c r="E33">
-        <v>1.7091499999999999E-2</v>
+        <v>3.1419999999999998E-3</v>
       </c>
       <c r="F33">
-        <v>0.11227330000000001</v>
+        <v>1.14371E-2</v>
       </c>
       <c r="G33">
-        <v>3.3534550000000003E-2</v>
+        <v>4.0297750000000002E-3</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -2894,19 +2846,19 @@
         <v>39</v>
       </c>
       <c r="C34">
-        <v>4.4119999999999999E-4</v>
+        <v>2.8130000000000012E-4</v>
       </c>
       <c r="D34">
-        <v>1.106E-3</v>
+        <v>1.0296999999999999E-3</v>
       </c>
       <c r="E34">
-        <v>3.4586E-3</v>
+        <v>2.9332E-3</v>
       </c>
       <c r="F34">
-        <v>1.2142E-2</v>
+        <v>1.1029300000000001E-2</v>
       </c>
       <c r="G34">
-        <v>4.2869499999999986E-3</v>
+        <v>3.8183750000000002E-3</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -2917,19 +2869,19 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>3.2749999999999999E-4</v>
+        <v>4.4049999999999997E-4</v>
       </c>
       <c r="D35">
-        <v>1.0365999999999999E-3</v>
+        <v>1.0322E-3</v>
       </c>
       <c r="E35">
-        <v>3.0801000000000001E-3</v>
+        <v>2.9897999999999999E-3</v>
       </c>
       <c r="F35">
-        <v>1.1829900000000001E-2</v>
+        <v>1.09438E-2</v>
       </c>
       <c r="G35">
-        <v>4.0685249999999999E-3</v>
+        <v>3.851574999999999E-3</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -2940,19 +2892,19 @@
         <v>41</v>
       </c>
       <c r="C36">
-        <v>4.1819999999999997E-4</v>
+        <v>3.3839999999999999E-4</v>
       </c>
       <c r="D36">
-        <v>1.0701E-3</v>
+        <v>9.8380000000000017E-4</v>
       </c>
       <c r="E36">
-        <v>3.1381E-3</v>
+        <v>3.2701000000000002E-3</v>
       </c>
       <c r="F36">
-        <v>1.1647299999999999E-2</v>
+        <v>1.19174E-2</v>
       </c>
       <c r="G36">
-        <v>4.0684250000000014E-3</v>
+        <v>4.1274249999999997E-3</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -2963,19 +2915,19 @@
         <v>42</v>
       </c>
       <c r="C37">
-        <v>4.1340000000000002E-4</v>
+        <v>3.5070000000000001E-4</v>
       </c>
       <c r="D37">
-        <v>1.2048E-3</v>
+        <v>1.0594000000000001E-3</v>
       </c>
       <c r="E37">
-        <v>4.6449000000000004E-3</v>
+        <v>2.8119999999999998E-3</v>
       </c>
       <c r="F37">
-        <v>2.0368799999999999E-2</v>
+        <v>1.2728700000000001E-2</v>
       </c>
       <c r="G37">
-        <v>6.657975E-3</v>
+        <v>4.2376999999999996E-3</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -2986,134 +2938,134 @@
         <v>43</v>
       </c>
       <c r="C38">
-        <v>3.6880000000000002E-4</v>
+        <v>3.882E-4</v>
       </c>
       <c r="D38">
-        <v>1.075E-3</v>
+        <v>1.1693000000000001E-3</v>
       </c>
       <c r="E38">
-        <v>3.381400000000001E-3</v>
+        <v>3.6083E-3</v>
       </c>
       <c r="F38">
-        <v>1.25874E-2</v>
+        <v>1.34076E-2</v>
       </c>
       <c r="G38">
-        <v>4.3531500000000001E-3</v>
+        <v>4.6433500000000001E-3</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B39" t="s">
         <v>44</v>
       </c>
       <c r="C39">
-        <v>3.5609999999999998E-4</v>
+        <v>5.1539999999999995E-4</v>
       </c>
       <c r="D39">
-        <v>1.0606999999999999E-3</v>
+        <v>2.0387000000000001E-3</v>
       </c>
       <c r="E39">
-        <v>3.2945000000000001E-3</v>
+        <v>9.5207999999999994E-3</v>
       </c>
       <c r="F39">
-        <v>1.2488300000000001E-2</v>
+        <v>5.3929099999999987E-2</v>
       </c>
       <c r="G39">
-        <v>4.2999000000000006E-3</v>
+        <v>1.6500999999999998E-2</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B40" t="s">
         <v>45</v>
       </c>
       <c r="C40">
-        <v>3.3260000000000001E-4</v>
+        <v>5.6050000000000002E-4</v>
       </c>
       <c r="D40">
-        <v>1.0705999999999999E-3</v>
+        <v>2.7542000000000001E-3</v>
       </c>
       <c r="E40">
-        <v>3.0184000000000001E-3</v>
+        <v>1.3998E-2</v>
       </c>
       <c r="F40">
-        <v>1.3277199999999999E-2</v>
+        <v>8.8623900000000005E-2</v>
       </c>
       <c r="G40">
-        <v>4.4247000000000002E-3</v>
+        <v>2.6484150000000001E-2</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B41" t="s">
         <v>46</v>
       </c>
       <c r="C41">
-        <v>4.1149999999999997E-4</v>
+        <v>6.2229999999999989E-4</v>
       </c>
       <c r="D41">
-        <v>1.2287000000000001E-3</v>
+        <v>3.0252999999999999E-3</v>
       </c>
       <c r="E41">
-        <v>3.8425999999999998E-3</v>
+        <v>1.47192E-2</v>
       </c>
       <c r="F41">
-        <v>1.4215E-2</v>
+        <v>8.6871300000000012E-2</v>
       </c>
       <c r="G41">
-        <v>4.9244500000000004E-3</v>
+        <v>2.6309525E-2</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B42" t="s">
         <v>47</v>
       </c>
       <c r="C42">
-        <v>3.9649999999999999E-4</v>
+        <v>4.035000000000001E-4</v>
       </c>
       <c r="D42">
-        <v>1.176E-3</v>
+        <v>1.6724000000000001E-3</v>
       </c>
       <c r="E42">
-        <v>3.8327000000000001E-3</v>
+        <v>6.5813E-3</v>
       </c>
       <c r="F42">
-        <v>1.40857E-2</v>
+        <v>2.6708699999999998E-2</v>
       </c>
       <c r="G42">
-        <v>4.8727249999999996E-3</v>
+        <v>8.8414750000000014E-3</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B43" t="s">
         <v>48</v>
       </c>
       <c r="C43">
-        <v>3.9899999999999989E-4</v>
+        <v>5.9009999999999998E-4</v>
       </c>
       <c r="D43">
-        <v>1.2118000000000001E-3</v>
+        <v>2.9277999999999999E-3</v>
       </c>
       <c r="E43">
-        <v>3.2595000000000011E-3</v>
+        <v>2.1913200000000001E-2</v>
       </c>
       <c r="F43">
-        <v>1.14999E-2</v>
+        <v>0.2078333</v>
       </c>
       <c r="G43">
-        <v>4.0925500000000004E-3</v>
+        <v>5.831610000000001E-2</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -3124,19 +3076,19 @@
         <v>49</v>
       </c>
       <c r="C44">
-        <v>5.7659999999999992E-4</v>
+        <v>4.6260000000000002E-4</v>
       </c>
       <c r="D44">
-        <v>2.1172000000000009E-3</v>
+        <v>1.1374E-3</v>
       </c>
       <c r="E44">
-        <v>9.887700000000001E-3</v>
+        <v>3.2699000000000001E-3</v>
       </c>
       <c r="F44">
-        <v>5.6657100000000002E-2</v>
+        <v>1.1563199999999999E-2</v>
       </c>
       <c r="G44">
-        <v>1.7309649999999999E-2</v>
+        <v>4.1082749999999998E-3</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -3147,19 +3099,19 @@
         <v>50</v>
       </c>
       <c r="C45">
-        <v>6.001E-4</v>
+        <v>3.6360000000000011E-4</v>
       </c>
       <c r="D45">
-        <v>3.0011999999999999E-3</v>
+        <v>1.4534000000000001E-3</v>
       </c>
       <c r="E45">
-        <v>1.45758E-2</v>
+        <v>3.6001000000000002E-3</v>
       </c>
       <c r="F45">
-        <v>9.3612399999999998E-2</v>
+        <v>1.23131E-2</v>
       </c>
       <c r="G45">
-        <v>2.7947375E-2</v>
+        <v>4.4325500000000004E-3</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -3170,19 +3122,19 @@
         <v>51</v>
       </c>
       <c r="C46">
-        <v>6.3449999999999997E-4</v>
+        <v>3.191E-4</v>
       </c>
       <c r="D46">
-        <v>3.0347E-3</v>
+        <v>1.1915999999999999E-3</v>
       </c>
       <c r="E46">
-        <v>1.49877E-2</v>
+        <v>2.9635999999999998E-3</v>
       </c>
       <c r="F46">
-        <v>8.9513700000000002E-2</v>
+        <v>1.1420700000000001E-2</v>
       </c>
       <c r="G46">
-        <v>2.7042650000000001E-2</v>
+        <v>3.9737499999999999E-3</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -3193,433 +3145,65 @@
         <v>52</v>
       </c>
       <c r="C47">
-        <v>4.3580000000000002E-4</v>
+        <v>3.9239999999999989E-4</v>
       </c>
       <c r="D47">
-        <v>1.7495E-3</v>
+        <v>1.1172000000000001E-3</v>
       </c>
       <c r="E47">
-        <v>6.848299999999999E-3</v>
+        <v>3.7997999999999999E-3</v>
       </c>
       <c r="F47">
-        <v>2.8136100000000001E-2</v>
+        <v>1.23894E-2</v>
       </c>
       <c r="G47">
-        <v>9.292425E-3</v>
+        <v>4.4247000000000002E-3</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B48" t="s">
         <v>53</v>
       </c>
       <c r="C48">
-        <v>6.4590000000000003E-4</v>
+        <v>6.1689999999999998E-4</v>
       </c>
       <c r="D48">
-        <v>3.0918E-3</v>
+        <v>3.0723999999999999E-3</v>
       </c>
       <c r="E48">
-        <v>2.2073800000000001E-2</v>
+        <v>1.49134E-2</v>
       </c>
       <c r="F48">
-        <v>0.2182151</v>
+        <v>8.7208699999999986E-2</v>
       </c>
       <c r="G48">
-        <v>6.1006650000000003E-2</v>
+        <v>2.645285E-2</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B49" t="s">
         <v>54</v>
       </c>
       <c r="C49">
-        <v>5.0310000000000003E-4</v>
+        <v>4.3169999999999998E-4</v>
       </c>
       <c r="D49">
-        <v>1.1891E-3</v>
+        <v>1.5219999999999999E-3</v>
       </c>
       <c r="E49">
-        <v>3.4122000000000002E-3</v>
+        <v>3.754700000000001E-3</v>
       </c>
       <c r="F49">
-        <v>1.22171E-2</v>
+        <v>1.2436300000000001E-2</v>
       </c>
       <c r="G49">
-        <v>4.3303750000000009E-3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50">
-        <v>4</v>
-      </c>
-      <c r="B50" t="s">
-        <v>55</v>
-      </c>
-      <c r="C50">
-        <v>4.328E-4</v>
-      </c>
-      <c r="D50">
-        <v>1.3236999999999999E-3</v>
-      </c>
-      <c r="E50">
-        <v>3.3126000000000002E-3</v>
-      </c>
-      <c r="F50">
-        <v>1.4344900000000001E-2</v>
-      </c>
-      <c r="G50">
-        <v>4.8535000000000002E-3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51">
-        <v>4</v>
-      </c>
-      <c r="B51" t="s">
-        <v>56</v>
-      </c>
-      <c r="C51">
-        <v>3.7550000000000002E-4</v>
-      </c>
-      <c r="D51">
-        <v>1.2639000000000001E-3</v>
-      </c>
-      <c r="E51">
-        <v>3.7448E-3</v>
-      </c>
-      <c r="F51">
-        <v>1.32088E-2</v>
-      </c>
-      <c r="G51">
-        <v>4.6482499999999996E-3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52">
-        <v>4</v>
-      </c>
-      <c r="B52" t="s">
-        <v>57</v>
-      </c>
-      <c r="C52">
-        <v>3.39E-4</v>
-      </c>
-      <c r="D52">
-        <v>1.0847999999999999E-3</v>
-      </c>
-      <c r="E52">
-        <v>3.1808000000000001E-3</v>
-      </c>
-      <c r="F52">
-        <v>1.19883E-2</v>
-      </c>
-      <c r="G52">
-        <v>4.1482249999999993E-3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53">
-        <v>4</v>
-      </c>
-      <c r="B53" t="s">
-        <v>58</v>
-      </c>
-      <c r="C53">
-        <v>3.2279999999999999E-4</v>
-      </c>
-      <c r="D53">
-        <v>1.0539E-3</v>
-      </c>
-      <c r="E53">
-        <v>4.4097000000000008E-3</v>
-      </c>
-      <c r="F53">
-        <v>2.0159E-2</v>
-      </c>
-      <c r="G53">
-        <v>6.4863500000000001E-3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54">
-        <v>4</v>
-      </c>
-      <c r="B54" t="s">
-        <v>59</v>
-      </c>
-      <c r="C54">
-        <v>4.3100000000000012E-4</v>
-      </c>
-      <c r="D54">
-        <v>1.2344000000000001E-3</v>
-      </c>
-      <c r="E54">
-        <v>4.7124999999999997E-3</v>
-      </c>
-      <c r="F54">
-        <v>2.0473600000000002E-2</v>
-      </c>
-      <c r="G54">
-        <v>6.7128750000000001E-3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55">
-        <v>4</v>
-      </c>
-      <c r="B55" t="s">
-        <v>60</v>
-      </c>
-      <c r="C55">
-        <v>3.7730000000000001E-4</v>
-      </c>
-      <c r="D55">
-        <v>1.0424E-3</v>
-      </c>
-      <c r="E55">
-        <v>3.3771999999999999E-3</v>
-      </c>
-      <c r="F55">
-        <v>1.264E-2</v>
-      </c>
-      <c r="G55">
-        <v>4.3592250000000004E-3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56">
-        <v>4</v>
-      </c>
-      <c r="B56" t="s">
-        <v>61</v>
-      </c>
-      <c r="C56">
-        <v>3.8979999999999999E-4</v>
-      </c>
-      <c r="D56">
-        <v>1.1705000000000001E-3</v>
-      </c>
-      <c r="E56">
-        <v>3.0498999999999999E-3</v>
-      </c>
-      <c r="F56">
-        <v>1.35152E-2</v>
-      </c>
-      <c r="G56">
-        <v>4.53135E-3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57">
-        <v>4</v>
-      </c>
-      <c r="B57" t="s">
-        <v>62</v>
-      </c>
-      <c r="C57">
-        <v>4.2799999999999989E-4</v>
-      </c>
-      <c r="D57">
-        <v>1.0835E-3</v>
-      </c>
-      <c r="E57">
-        <v>3.0325E-3</v>
-      </c>
-      <c r="F57">
-        <v>1.3322000000000001E-2</v>
-      </c>
-      <c r="G57">
-        <v>4.4664999999999991E-3</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58">
-        <v>4</v>
-      </c>
-      <c r="B58" t="s">
-        <v>63</v>
-      </c>
-      <c r="C58">
-        <v>4.3080000000000001E-4</v>
-      </c>
-      <c r="D58">
-        <v>1.2882E-3</v>
-      </c>
-      <c r="E58">
-        <v>3.862E-3</v>
-      </c>
-      <c r="F58">
-        <v>1.4293200000000001E-2</v>
-      </c>
-      <c r="G58">
-        <v>4.9685500000000004E-3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59">
-        <v>5</v>
-      </c>
-      <c r="B59" t="s">
-        <v>64</v>
-      </c>
-      <c r="C59">
-        <v>7.2180000000000009E-4</v>
-      </c>
-      <c r="D59">
-        <v>3.1521000000000001E-3</v>
-      </c>
-      <c r="E59">
-        <v>1.51418E-2</v>
-      </c>
-      <c r="F59">
-        <v>9.0982299999999988E-2</v>
-      </c>
-      <c r="G59">
-        <v>2.74995E-2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>5</v>
-      </c>
-      <c r="B60" t="s">
-        <v>65</v>
-      </c>
-      <c r="C60">
-        <v>4.704E-4</v>
-      </c>
-      <c r="D60">
-        <v>1.3913E-3</v>
-      </c>
-      <c r="E60">
-        <v>3.4596000000000002E-3</v>
-      </c>
-      <c r="F60">
-        <v>1.4567699999999999E-2</v>
-      </c>
-      <c r="G60">
-        <v>4.9722500000000001E-3</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61">
-        <v>5</v>
-      </c>
-      <c r="B61" t="s">
-        <v>66</v>
-      </c>
-      <c r="C61">
-        <v>4.3039999999999989E-4</v>
-      </c>
-      <c r="D61">
-        <v>1.3801E-3</v>
-      </c>
-      <c r="E61">
-        <v>3.8206999999999998E-3</v>
-      </c>
-      <c r="F61">
-        <v>1.3374199999999999E-2</v>
-      </c>
-      <c r="G61">
-        <v>4.7513499999999997E-3</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62">
-        <v>5</v>
-      </c>
-      <c r="B62" t="s">
-        <v>67</v>
-      </c>
-      <c r="C62">
-        <v>4.373E-4</v>
-      </c>
-      <c r="D62">
-        <v>1.3852000000000001E-3</v>
-      </c>
-      <c r="E62">
-        <v>4.0931000000000014E-3</v>
-      </c>
-      <c r="F62">
-        <v>1.4032299999999999E-2</v>
-      </c>
-      <c r="G62">
-        <v>4.9869749999999994E-3</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63">
-        <v>5</v>
-      </c>
-      <c r="B63" t="s">
-        <v>68</v>
-      </c>
-      <c r="C63">
-        <v>3.7589999999999998E-4</v>
-      </c>
-      <c r="D63">
-        <v>1.1686999999999999E-3</v>
-      </c>
-      <c r="E63">
-        <v>4.4682999999999997E-3</v>
-      </c>
-      <c r="F63">
-        <v>2.0290300000000001E-2</v>
-      </c>
-      <c r="G63">
-        <v>6.5757999999999997E-3</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64">
-        <v>5</v>
-      </c>
-      <c r="B64" t="s">
-        <v>69</v>
-      </c>
-      <c r="C64">
-        <v>4.195999999999999E-4</v>
-      </c>
-      <c r="D64">
-        <v>1.1563999999999999E-3</v>
-      </c>
-      <c r="E64">
-        <v>3.0672E-3</v>
-      </c>
-      <c r="F64">
-        <v>1.3529100000000001E-2</v>
-      </c>
-      <c r="G64">
-        <v>4.5430749999999997E-3</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65">
-        <v>6</v>
-      </c>
-      <c r="B65" t="s">
-        <v>70</v>
-      </c>
-      <c r="C65">
-        <v>5.3950000000000005E-4</v>
-      </c>
-      <c r="D65">
-        <v>1.4773E-3</v>
-      </c>
-      <c r="E65">
-        <v>4.2452999999999996E-3</v>
-      </c>
-      <c r="F65">
-        <v>1.4164299999999999E-2</v>
-      </c>
-      <c r="G65">
-        <v>5.1065999999999993E-3</v>
+        <v>4.5361749999999999E-3</v>
       </c>
     </row>
   </sheetData>
@@ -3630,7 +3214,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -4124,24 +3708,24 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D22">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E22">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F22">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G22">
-        <v>18.75</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="s">
         <v>28</v>
@@ -4150,16 +3734,16 @@
         <v>11</v>
       </c>
       <c r="D23">
+        <v>12</v>
+      </c>
+      <c r="E23">
         <v>11</v>
       </c>
-      <c r="E23">
-        <v>10</v>
-      </c>
       <c r="F23">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G23">
-        <v>10.5</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -4170,19 +3754,19 @@
         <v>29</v>
       </c>
       <c r="C24">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D24">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="E24">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="F24">
-        <v>11</v>
+        <v>176</v>
       </c>
       <c r="G24">
-        <v>11.25</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -4193,19 +3777,19 @@
         <v>30</v>
       </c>
       <c r="C25">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D25">
         <v>44</v>
       </c>
       <c r="E25">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="F25">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="G25">
-        <v>82.5</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -4216,19 +3800,19 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D26">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="E26">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="F26">
-        <v>192</v>
+        <v>12</v>
       </c>
       <c r="G26">
-        <v>89</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -4239,19 +3823,19 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D27">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="E27">
-        <v>12</v>
+        <v>96</v>
       </c>
       <c r="F27">
-        <v>12</v>
+        <v>192</v>
       </c>
       <c r="G27">
-        <v>12.25</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -4262,19 +3846,19 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D28">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="E28">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="F28">
-        <v>192</v>
+        <v>10</v>
       </c>
       <c r="G28">
-        <v>90</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -4285,19 +3869,19 @@
         <v>34</v>
       </c>
       <c r="C29">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D29">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E29">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F29">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G29">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -4308,10 +3892,10 @@
         <v>35</v>
       </c>
       <c r="C30">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D30">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E30">
         <v>11</v>
@@ -4320,7 +3904,7 @@
         <v>11</v>
       </c>
       <c r="G30">
-        <v>11</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -4331,19 +3915,19 @@
         <v>36</v>
       </c>
       <c r="C31">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D31">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="E31">
-        <v>11</v>
+        <v>96</v>
       </c>
       <c r="F31">
-        <v>11</v>
+        <v>192</v>
       </c>
       <c r="G31">
-        <v>10.5</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -4354,19 +3938,19 @@
         <v>37</v>
       </c>
       <c r="C32">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D32">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="E32">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="F32">
-        <v>192</v>
+        <v>10</v>
       </c>
       <c r="G32">
-        <v>88.5</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -4377,19 +3961,19 @@
         <v>38</v>
       </c>
       <c r="C33">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D33">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E33">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F33">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G33">
-        <v>10.75</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -4423,19 +4007,19 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D35">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E35">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F35">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G35">
-        <v>19.25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -4449,16 +4033,16 @@
         <v>11</v>
       </c>
       <c r="D36">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E36">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F36">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G36">
-        <v>11</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -4469,19 +4053,19 @@
         <v>42</v>
       </c>
       <c r="C37">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D37">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E37">
         <v>20</v>
       </c>
       <c r="F37">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G37">
-        <v>19.25</v>
+        <v>19.75</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -4492,125 +4076,125 @@
         <v>43</v>
       </c>
       <c r="C38">
+        <v>9</v>
+      </c>
+      <c r="D38">
         <v>11</v>
       </c>
-      <c r="D38">
-        <v>12</v>
-      </c>
       <c r="E38">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F38">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G38">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B39" t="s">
         <v>44</v>
       </c>
       <c r="C39">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D39">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E39">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F39">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G39">
-        <v>19.75</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B40" t="s">
         <v>45</v>
       </c>
       <c r="C40">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D40">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E40">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F40">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G40">
-        <v>19.75</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B41" t="s">
         <v>46</v>
       </c>
       <c r="C41">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D41">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="E41">
-        <v>11</v>
+        <v>96</v>
       </c>
       <c r="F41">
-        <v>11</v>
+        <v>192</v>
       </c>
       <c r="G41">
-        <v>10.5</v>
+        <v>89</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B42" t="s">
         <v>47</v>
       </c>
       <c r="C42">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D42">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E42">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F42">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G42">
-        <v>18.5</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B43" t="s">
         <v>48</v>
       </c>
       <c r="C43">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D43">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E43">
         <v>11</v>
@@ -4619,7 +4203,7 @@
         <v>11</v>
       </c>
       <c r="G43">
-        <v>11</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -4633,16 +4217,16 @@
         <v>11</v>
       </c>
       <c r="D44">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E44">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F44">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G44">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -4653,19 +4237,19 @@
         <v>50</v>
       </c>
       <c r="C45">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D45">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E45">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F45">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G45">
-        <v>11</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -4676,19 +4260,19 @@
         <v>51</v>
       </c>
       <c r="C46">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D46">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="E46">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="F46">
-        <v>192</v>
+        <v>13</v>
       </c>
       <c r="G46">
-        <v>89</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -4699,7 +4283,7 @@
         <v>52</v>
       </c>
       <c r="C47">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D47">
         <v>12</v>
@@ -4711,18 +4295,18 @@
         <v>12</v>
       </c>
       <c r="G47">
-        <v>11.75</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B48" t="s">
         <v>53</v>
       </c>
       <c r="C48">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D48">
         <v>10</v>
@@ -4734,18 +4318,18 @@
         <v>11</v>
       </c>
       <c r="G48">
-        <v>10.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B49" t="s">
         <v>54</v>
       </c>
       <c r="C49">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D49">
         <v>12</v>
@@ -4757,375 +4341,7 @@
         <v>13</v>
       </c>
       <c r="G49">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50">
-        <v>4</v>
-      </c>
-      <c r="B50" t="s">
-        <v>55</v>
-      </c>
-      <c r="C50">
-        <v>17</v>
-      </c>
-      <c r="D50">
-        <v>19</v>
-      </c>
-      <c r="E50">
-        <v>20</v>
-      </c>
-      <c r="F50">
-        <v>20</v>
-      </c>
-      <c r="G50">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51">
-        <v>4</v>
-      </c>
-      <c r="B51" t="s">
-        <v>56</v>
-      </c>
-      <c r="C51">
-        <v>17</v>
-      </c>
-      <c r="D51">
-        <v>20</v>
-      </c>
-      <c r="E51">
-        <v>20</v>
-      </c>
-      <c r="F51">
-        <v>20</v>
-      </c>
-      <c r="G51">
-        <v>19.25</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52">
-        <v>4</v>
-      </c>
-      <c r="B52" t="s">
-        <v>57</v>
-      </c>
-      <c r="C52">
-        <v>12</v>
-      </c>
-      <c r="D52">
-        <v>12</v>
-      </c>
-      <c r="E52">
-        <v>12</v>
-      </c>
-      <c r="F52">
-        <v>13</v>
-      </c>
-      <c r="G52">
         <v>12.25</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53">
-        <v>4</v>
-      </c>
-      <c r="B53" t="s">
-        <v>58</v>
-      </c>
-      <c r="C53">
-        <v>17</v>
-      </c>
-      <c r="D53">
-        <v>20</v>
-      </c>
-      <c r="E53">
-        <v>22</v>
-      </c>
-      <c r="F53">
-        <v>22</v>
-      </c>
-      <c r="G53">
-        <v>20.25</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54">
-        <v>4</v>
-      </c>
-      <c r="B54" t="s">
-        <v>59</v>
-      </c>
-      <c r="C54">
-        <v>11</v>
-      </c>
-      <c r="D54">
-        <v>11</v>
-      </c>
-      <c r="E54">
-        <v>12</v>
-      </c>
-      <c r="F54">
-        <v>13</v>
-      </c>
-      <c r="G54">
-        <v>11.75</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55">
-        <v>4</v>
-      </c>
-      <c r="B55" t="s">
-        <v>60</v>
-      </c>
-      <c r="C55">
-        <v>11</v>
-      </c>
-      <c r="D55">
-        <v>12</v>
-      </c>
-      <c r="E55">
-        <v>15</v>
-      </c>
-      <c r="F55">
-        <v>12</v>
-      </c>
-      <c r="G55">
-        <v>12.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56">
-        <v>4</v>
-      </c>
-      <c r="B56" t="s">
-        <v>61</v>
-      </c>
-      <c r="C56">
-        <v>12</v>
-      </c>
-      <c r="D56">
-        <v>12</v>
-      </c>
-      <c r="E56">
-        <v>12</v>
-      </c>
-      <c r="F56">
-        <v>12</v>
-      </c>
-      <c r="G56">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57">
-        <v>4</v>
-      </c>
-      <c r="B57" t="s">
-        <v>62</v>
-      </c>
-      <c r="C57">
-        <v>19</v>
-      </c>
-      <c r="D57">
-        <v>20</v>
-      </c>
-      <c r="E57">
-        <v>20</v>
-      </c>
-      <c r="F57">
-        <v>20</v>
-      </c>
-      <c r="G57">
-        <v>19.75</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58">
-        <v>4</v>
-      </c>
-      <c r="B58" t="s">
-        <v>63</v>
-      </c>
-      <c r="C58">
-        <v>9</v>
-      </c>
-      <c r="D58">
-        <v>11</v>
-      </c>
-      <c r="E58">
-        <v>11</v>
-      </c>
-      <c r="F58">
-        <v>11</v>
-      </c>
-      <c r="G58">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59">
-        <v>5</v>
-      </c>
-      <c r="B59" t="s">
-        <v>64</v>
-      </c>
-      <c r="C59">
-        <v>12</v>
-      </c>
-      <c r="D59">
-        <v>10</v>
-      </c>
-      <c r="E59">
-        <v>11</v>
-      </c>
-      <c r="F59">
-        <v>11</v>
-      </c>
-      <c r="G59">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>5</v>
-      </c>
-      <c r="B60" t="s">
-        <v>65</v>
-      </c>
-      <c r="C60">
-        <v>11</v>
-      </c>
-      <c r="D60">
-        <v>11</v>
-      </c>
-      <c r="E60">
-        <v>12</v>
-      </c>
-      <c r="F60">
-        <v>12</v>
-      </c>
-      <c r="G60">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61">
-        <v>5</v>
-      </c>
-      <c r="B61" t="s">
-        <v>66</v>
-      </c>
-      <c r="C61">
-        <v>12</v>
-      </c>
-      <c r="D61">
-        <v>12</v>
-      </c>
-      <c r="E61">
-        <v>12</v>
-      </c>
-      <c r="F61">
-        <v>13</v>
-      </c>
-      <c r="G61">
-        <v>12.25</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62">
-        <v>5</v>
-      </c>
-      <c r="B62" t="s">
-        <v>67</v>
-      </c>
-      <c r="C62">
-        <v>17</v>
-      </c>
-      <c r="D62">
-        <v>20</v>
-      </c>
-      <c r="E62">
-        <v>19</v>
-      </c>
-      <c r="F62">
-        <v>20</v>
-      </c>
-      <c r="G62">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63">
-        <v>5</v>
-      </c>
-      <c r="B63" t="s">
-        <v>68</v>
-      </c>
-      <c r="C63">
-        <v>12</v>
-      </c>
-      <c r="D63">
-        <v>12</v>
-      </c>
-      <c r="E63">
-        <v>13</v>
-      </c>
-      <c r="F63">
-        <v>13</v>
-      </c>
-      <c r="G63">
-        <v>12.5</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64">
-        <v>5</v>
-      </c>
-      <c r="B64" t="s">
-        <v>69</v>
-      </c>
-      <c r="C64">
-        <v>12</v>
-      </c>
-      <c r="D64">
-        <v>12</v>
-      </c>
-      <c r="E64">
-        <v>12</v>
-      </c>
-      <c r="F64">
-        <v>12</v>
-      </c>
-      <c r="G64">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65">
-        <v>6</v>
-      </c>
-      <c r="B65" t="s">
-        <v>70</v>
-      </c>
-      <c r="C65">
-        <v>11</v>
-      </c>
-      <c r="D65">
-        <v>12</v>
-      </c>
-      <c r="E65">
-        <v>11</v>
-      </c>
-      <c r="F65">
-        <v>12</v>
-      </c>
-      <c r="G65">
-        <v>11.5</v>
       </c>
     </row>
   </sheetData>
@@ -5135,7 +4351,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -5629,42 +4845,42 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>25.55634918610405</v>
+        <v>24.883627011906739</v>
       </c>
       <c r="D22">
-        <v>51.698484809834987</v>
+        <v>49.468775958388193</v>
       </c>
       <c r="E22">
-        <v>103.9827560572969</v>
+        <v>99.995569844109326</v>
       </c>
       <c r="F22">
-        <v>208.55129855222069</v>
+        <v>201.30769961265111</v>
       </c>
       <c r="G22">
-        <v>97.447222151364144</v>
+        <v>93.913918106763845</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="s">
         <v>28</v>
       </c>
       <c r="C23">
-        <v>24.883627011906739</v>
+        <v>24.660751162624539</v>
       </c>
       <c r="D23">
-        <v>49.468775958388193</v>
+        <v>50.193745265794732</v>
       </c>
       <c r="E23">
-        <v>99.995569844109326</v>
+        <v>100.9725808023951</v>
       </c>
       <c r="F23">
-        <v>201.30769961265111</v>
+        <v>203.16961391690279</v>
       </c>
       <c r="G23">
-        <v>93.913918106763845</v>
+        <v>94.749172786929307</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -5675,19 +4891,19 @@
         <v>29</v>
       </c>
       <c r="C24">
-        <v>24.660751162624539</v>
+        <v>25.55634918610405</v>
       </c>
       <c r="D24">
-        <v>50.193745265794732</v>
+        <v>52.526911934581193</v>
       </c>
       <c r="E24">
-        <v>100.9725808023951</v>
+        <v>106.46803743153551</v>
       </c>
       <c r="F24">
-        <v>203.16961391690279</v>
+        <v>214.35028842544401</v>
       </c>
       <c r="G24">
-        <v>94.749172786929307</v>
+        <v>99.725396744416187</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -5698,19 +4914,19 @@
         <v>30</v>
       </c>
       <c r="C25">
-        <v>25.55634918610405</v>
+        <v>27.55634918610405</v>
       </c>
       <c r="D25">
         <v>52.526911934581193</v>
       </c>
       <c r="E25">
-        <v>106.46803743153551</v>
+        <v>110.3259018078045</v>
       </c>
       <c r="F25">
-        <v>214.35028842544401</v>
+        <v>219.58073580374361</v>
       </c>
       <c r="G25">
-        <v>99.725396744416187</v>
+        <v>102.4974746830583</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -5721,19 +4937,19 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>27.55634918610405</v>
+        <v>25.877054302287249</v>
       </c>
       <c r="D26">
-        <v>52.526911934581193</v>
+        <v>51.454459478380492</v>
       </c>
       <c r="E26">
-        <v>110.3259018078045</v>
+        <v>103.3736799535253</v>
       </c>
       <c r="F26">
-        <v>219.58073580374361</v>
+        <v>207.42488285544599</v>
       </c>
       <c r="G26">
-        <v>102.4974746830583</v>
+        <v>97.032519147409758</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -5744,19 +4960,19 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>25.877054302287249</v>
+        <v>26.727922061357859</v>
       </c>
       <c r="D27">
-        <v>51.454459478380492</v>
+        <v>54.87005768508881</v>
       </c>
       <c r="E27">
-        <v>103.3736799535253</v>
+        <v>109.4974746830583</v>
       </c>
       <c r="F27">
-        <v>207.42488285544599</v>
+        <v>218.75230867899739</v>
       </c>
       <c r="G27">
-        <v>97.032519147409758</v>
+        <v>102.4619407771256</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -5767,19 +4983,19 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>26.727922061357859</v>
+        <v>24.65008380450606</v>
       </c>
       <c r="D28">
-        <v>54.87005768508881</v>
+        <v>49.953523924572849</v>
       </c>
       <c r="E28">
-        <v>109.4974746830583</v>
+        <v>98.901986786617144</v>
       </c>
       <c r="F28">
-        <v>218.75230867899739</v>
+        <v>197.88084452787041</v>
       </c>
       <c r="G28">
-        <v>102.4619407771256</v>
+        <v>92.846609760891596</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -5790,19 +5006,19 @@
         <v>34</v>
       </c>
       <c r="C29">
-        <v>24.65008380450606</v>
+        <v>24.883627011906739</v>
       </c>
       <c r="D29">
-        <v>49.953523924572849</v>
+        <v>50.688499009058027</v>
       </c>
       <c r="E29">
-        <v>98.901986786617144</v>
+        <v>102.5369334732962</v>
       </c>
       <c r="F29">
-        <v>197.9415538688763</v>
+        <v>206.40962072616639</v>
       </c>
       <c r="G29">
-        <v>92.861787096143075</v>
+        <v>96.129670055106828</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -5813,19 +5029,19 @@
         <v>35</v>
       </c>
       <c r="C30">
-        <v>24.883627011906739</v>
+        <v>24.65008380450606</v>
       </c>
       <c r="D30">
-        <v>50.688499009058027</v>
+        <v>49.547812689146618</v>
       </c>
       <c r="E30">
-        <v>102.5369334732962</v>
+        <v>104.63568079173621</v>
       </c>
       <c r="F30">
-        <v>206.40962072616639</v>
+        <v>209.67674266387999</v>
       </c>
       <c r="G30">
-        <v>96.129670055106828</v>
+        <v>97.127579987317219</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -5836,19 +5052,19 @@
         <v>36</v>
       </c>
       <c r="C31">
-        <v>24.65008380450606</v>
+        <v>25.55634918610405</v>
       </c>
       <c r="D31">
-        <v>49.547812689146618</v>
+        <v>51.698484809834987</v>
       </c>
       <c r="E31">
-        <v>104.63568079173621</v>
+        <v>109.4974746830583</v>
       </c>
       <c r="F31">
-        <v>209.67674266387999</v>
+        <v>218.75230867899739</v>
       </c>
       <c r="G31">
-        <v>97.127579987317219</v>
+        <v>101.3761543394987</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -5859,19 +5075,19 @@
         <v>37</v>
       </c>
       <c r="C32">
-        <v>25.55634918610405</v>
+        <v>25.877054302287249</v>
       </c>
       <c r="D32">
-        <v>51.698484809834987</v>
+        <v>51.417057965269542</v>
       </c>
       <c r="E32">
-        <v>109.4974746830583</v>
+        <v>99.166496458306156</v>
       </c>
       <c r="F32">
-        <v>218.75230867899739</v>
+        <v>198.93034199038169</v>
       </c>
       <c r="G32">
-        <v>101.3761543394987</v>
+        <v>93.847737679061154</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -5882,19 +5098,19 @@
         <v>38</v>
       </c>
       <c r="C33">
-        <v>25.877054302287249</v>
+        <v>25.55634918610405</v>
       </c>
       <c r="D33">
-        <v>51.417057965269542</v>
+        <v>54.041630560342618</v>
       </c>
       <c r="E33">
-        <v>99.166496458306156</v>
+        <v>108.6690475583121</v>
       </c>
       <c r="F33">
-        <v>198.93034199038169</v>
+        <v>217.92388155425121</v>
       </c>
       <c r="G33">
-        <v>93.847737679061154</v>
+        <v>101.5477272147525</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -5905,7 +5121,7 @@
         <v>39</v>
       </c>
       <c r="C34">
-        <v>25.55634918610405</v>
+        <v>26.727922061357859</v>
       </c>
       <c r="D34">
         <v>54.041630560342618</v>
@@ -5917,7 +5133,7 @@
         <v>217.92388155425121</v>
       </c>
       <c r="G34">
-        <v>101.5477272147525</v>
+        <v>101.8406204335659</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -5928,19 +5144,19 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>26.727922061357859</v>
+        <v>25.061772596780042</v>
       </c>
       <c r="D35">
-        <v>54.041630560342618</v>
+        <v>50.217687953264218</v>
       </c>
       <c r="E35">
-        <v>108.6690475583121</v>
+        <v>100.97795130931109</v>
       </c>
       <c r="F35">
-        <v>217.92388155425121</v>
+        <v>202.6246318390989</v>
       </c>
       <c r="G35">
-        <v>101.8406204335659</v>
+        <v>94.720510924613549</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -5951,19 +5167,19 @@
         <v>41</v>
       </c>
       <c r="C36">
-        <v>25.061772596780042</v>
+        <v>26.297840574279839</v>
       </c>
       <c r="D36">
-        <v>50.217687953264218</v>
+        <v>52.850016554111697</v>
       </c>
       <c r="E36">
-        <v>100.97795130931109</v>
+        <v>111.1160456359106</v>
       </c>
       <c r="F36">
-        <v>202.6246318390989</v>
+        <v>214.08984039418249</v>
       </c>
       <c r="G36">
-        <v>94.720510924613549</v>
+        <v>101.0884357896212</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -5974,19 +5190,19 @@
         <v>42</v>
       </c>
       <c r="C37">
-        <v>25.55634918610405</v>
+        <v>26.727922061357859</v>
       </c>
       <c r="D37">
-        <v>51.698484809834987</v>
+        <v>54.041630560342618</v>
       </c>
       <c r="E37">
-        <v>107.1543289325507</v>
+        <v>108.6690475583121</v>
       </c>
       <c r="F37">
-        <v>233.63961030678931</v>
+        <v>217.92388155425121</v>
       </c>
       <c r="G37">
-        <v>104.5121933088197</v>
+        <v>101.8406204335659</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -5997,134 +5213,134 @@
         <v>43</v>
       </c>
       <c r="C38">
-        <v>26.297840574279839</v>
+        <v>25.64755903440695</v>
       </c>
       <c r="D38">
-        <v>52.850016554111697</v>
+        <v>50.784817904249259</v>
       </c>
       <c r="E38">
-        <v>111.1160456359106</v>
+        <v>102.44570532669439</v>
       </c>
       <c r="F38">
-        <v>214.08984039418249</v>
+        <v>205.82904579473271</v>
       </c>
       <c r="G38">
-        <v>101.0884357896212</v>
+        <v>96.176782015020819</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B39" t="s">
         <v>44</v>
       </c>
       <c r="C39">
-        <v>26.970562748477139</v>
+        <v>24.883627011906739</v>
       </c>
       <c r="D39">
-        <v>54.041630560342618</v>
+        <v>51.003693057838348</v>
       </c>
       <c r="E39">
-        <v>111.8406204335659</v>
+        <v>102.0330616688867</v>
       </c>
       <c r="F39">
-        <v>217.92388155425121</v>
+        <v>205.15588556365569</v>
       </c>
       <c r="G39">
-        <v>102.69417382415919</v>
+        <v>95.769066825571869</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B40" t="s">
         <v>45</v>
       </c>
       <c r="C40">
-        <v>26.727922061357859</v>
+        <v>26.414373490277999</v>
       </c>
       <c r="D40">
-        <v>54.041630560342618</v>
+        <v>49.693773510102133</v>
       </c>
       <c r="E40">
-        <v>108.6690475583121</v>
+        <v>104.569998812953</v>
       </c>
       <c r="F40">
-        <v>217.92388155425121</v>
+        <v>209.36663344984279</v>
       </c>
       <c r="G40">
-        <v>101.8406204335659</v>
+        <v>97.511194815793985</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B41" t="s">
         <v>46</v>
       </c>
       <c r="C41">
-        <v>25.64755903440695</v>
+        <v>27.55634918610405</v>
       </c>
       <c r="D41">
-        <v>50.784817904249259</v>
+        <v>52.526911934581193</v>
       </c>
       <c r="E41">
-        <v>102.44570532669439</v>
+        <v>110.3259018078045</v>
       </c>
       <c r="F41">
-        <v>205.82904579473271</v>
+        <v>219.58073580374361</v>
       </c>
       <c r="G41">
-        <v>96.176782015020819</v>
+        <v>102.4974746830583</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B42" t="s">
         <v>47</v>
       </c>
       <c r="C42">
-        <v>26.142135623730951</v>
+        <v>26.055199887160551</v>
       </c>
       <c r="D42">
-        <v>51.698484809834987</v>
+        <v>51.454459478380492</v>
       </c>
       <c r="E42">
-        <v>103.9827560572969</v>
+        <v>103.32715348193069</v>
       </c>
       <c r="F42">
-        <v>208.55129855222069</v>
+        <v>207.42488285544599</v>
       </c>
       <c r="G42">
-        <v>97.593668760770868</v>
+        <v>97.065423925729448</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B43" t="s">
         <v>48</v>
       </c>
       <c r="C43">
-        <v>25.061772596780042</v>
+        <v>24.65008380450606</v>
       </c>
       <c r="D43">
-        <v>50.784817904249259</v>
+        <v>49.547812689146618</v>
       </c>
       <c r="E43">
-        <v>102.44570532669439</v>
+        <v>104.63568079173621</v>
       </c>
       <c r="F43">
-        <v>205.82904579473271</v>
+        <v>209.67674266387999</v>
       </c>
       <c r="G43">
-        <v>96.030335405614096</v>
+        <v>97.127579987317219</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -6135,19 +5351,19 @@
         <v>49</v>
       </c>
       <c r="C44">
-        <v>24.883627011906739</v>
+        <v>25.061772596780042</v>
       </c>
       <c r="D44">
-        <v>51.003693057838348</v>
+        <v>52.28288660312667</v>
       </c>
       <c r="E44">
-        <v>102.0330616688867</v>
+        <v>105.108348609036</v>
       </c>
       <c r="F44">
-        <v>205.15588556365569</v>
+        <v>211.04304927991731</v>
       </c>
       <c r="G44">
-        <v>95.769066825571869</v>
+        <v>98.374014272215007</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -6158,19 +5374,19 @@
         <v>50</v>
       </c>
       <c r="C45">
-        <v>26.414373490277999</v>
+        <v>26.727922061357859</v>
       </c>
       <c r="D45">
-        <v>49.693773510102133</v>
+        <v>54.041630560342618</v>
       </c>
       <c r="E45">
-        <v>104.569998812953</v>
+        <v>108.6690475583121</v>
       </c>
       <c r="F45">
-        <v>209.36663344984279</v>
+        <v>217.92388155425121</v>
       </c>
       <c r="G45">
-        <v>97.511194815793985</v>
+        <v>101.8406204335659</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -6181,19 +5397,19 @@
         <v>51</v>
       </c>
       <c r="C46">
-        <v>27.55634918610405</v>
+        <v>26.055199887160551</v>
       </c>
       <c r="D46">
-        <v>51.698484809834987</v>
+        <v>52.28288660312667</v>
       </c>
       <c r="E46">
-        <v>110.3259018078045</v>
+        <v>105.108348609036</v>
       </c>
       <c r="F46">
-        <v>219.58073580374361</v>
+        <v>211.04304927991731</v>
       </c>
       <c r="G46">
-        <v>102.2903679018718</v>
+        <v>98.622371094810134</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -6204,53 +5420,53 @@
         <v>52</v>
       </c>
       <c r="C47">
-        <v>26.055199887160551</v>
+        <v>25.877054302287249</v>
       </c>
       <c r="D47">
-        <v>51.454459478380492</v>
+        <v>52.850016554111697</v>
       </c>
       <c r="E47">
-        <v>103.32715348193069</v>
+        <v>106.5761026264193</v>
       </c>
       <c r="F47">
-        <v>207.42488285544599</v>
+        <v>214.08984039418249</v>
       </c>
       <c r="G47">
-        <v>97.065423925729448</v>
+        <v>99.848253469250182</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B48" t="s">
         <v>53</v>
       </c>
       <c r="C48">
-        <v>24.65008380450606</v>
+        <v>26.414373490277999</v>
       </c>
       <c r="D48">
-        <v>49.547812689146618</v>
+        <v>49.693773510102133</v>
       </c>
       <c r="E48">
-        <v>104.63568079173621</v>
+        <v>104.569998812953</v>
       </c>
       <c r="F48">
-        <v>209.67674266387999</v>
+        <v>209.36663344984279</v>
       </c>
       <c r="G48">
-        <v>97.127579987317219</v>
+        <v>97.511194815793985</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B49" t="s">
         <v>54</v>
       </c>
       <c r="C49">
-        <v>25.061772596780042</v>
+        <v>26.055199887160551</v>
       </c>
       <c r="D49">
         <v>52.28288660312667</v>
@@ -6262,375 +5478,7 @@
         <v>211.04304927991731</v>
       </c>
       <c r="G49">
-        <v>98.374014272215007</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50">
-        <v>4</v>
-      </c>
-      <c r="B50" t="s">
-        <v>55</v>
-      </c>
-      <c r="C50">
-        <v>25.55634918610405</v>
-      </c>
-      <c r="D50">
-        <v>51.698484809834987</v>
-      </c>
-      <c r="E50">
-        <v>107.1543289325507</v>
-      </c>
-      <c r="F50">
-        <v>214.0660171779821</v>
-      </c>
-      <c r="G50">
-        <v>99.618795026617974</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51">
-        <v>4</v>
-      </c>
-      <c r="B51" t="s">
-        <v>56</v>
-      </c>
-      <c r="C51">
-        <v>26.727922061357859</v>
-      </c>
-      <c r="D51">
-        <v>54.041630560342618</v>
-      </c>
-      <c r="E51">
-        <v>108.6690475583121</v>
-      </c>
-      <c r="F51">
-        <v>217.92388155425121</v>
-      </c>
-      <c r="G51">
-        <v>101.8406204335659</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52">
-        <v>4</v>
-      </c>
-      <c r="B52" t="s">
-        <v>57</v>
-      </c>
-      <c r="C52">
-        <v>26.055199887160551</v>
-      </c>
-      <c r="D52">
-        <v>52.28288660312667</v>
-      </c>
-      <c r="E52">
-        <v>105.108348609036</v>
-      </c>
-      <c r="F52">
-        <v>211.04304927991731</v>
-      </c>
-      <c r="G52">
         <v>98.622371094810134</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53">
-        <v>4</v>
-      </c>
-      <c r="B53" t="s">
-        <v>58</v>
-      </c>
-      <c r="C53">
-        <v>26.727922061357859</v>
-      </c>
-      <c r="D53">
-        <v>54.041630560342618</v>
-      </c>
-      <c r="E53">
-        <v>119.39696961967</v>
-      </c>
-      <c r="F53">
-        <v>239.96551211459379</v>
-      </c>
-      <c r="G53">
-        <v>110.03300858899109</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54">
-        <v>4</v>
-      </c>
-      <c r="B54" t="s">
-        <v>59</v>
-      </c>
-      <c r="C54">
-        <v>25.061772596780042</v>
-      </c>
-      <c r="D54">
-        <v>50.217687953264218</v>
-      </c>
-      <c r="E54">
-        <v>105.2369118846929</v>
-      </c>
-      <c r="F54">
-        <v>227.85829715105589</v>
-      </c>
-      <c r="G54">
-        <v>102.0936673964483</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55">
-        <v>4</v>
-      </c>
-      <c r="B55" t="s">
-        <v>60</v>
-      </c>
-      <c r="C55">
-        <v>26.297840574279839</v>
-      </c>
-      <c r="D55">
-        <v>52.850016554111697</v>
-      </c>
-      <c r="E55">
-        <v>111.1160456359106</v>
-      </c>
-      <c r="F55">
-        <v>214.08984039418249</v>
-      </c>
-      <c r="G55">
-        <v>101.0884357896212</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56">
-        <v>4</v>
-      </c>
-      <c r="B56" t="s">
-        <v>61</v>
-      </c>
-      <c r="C56">
-        <v>25.877054302287249</v>
-      </c>
-      <c r="D56">
-        <v>52.850016554111697</v>
-      </c>
-      <c r="E56">
-        <v>106.5761026264193</v>
-      </c>
-      <c r="F56">
-        <v>214.08984039418249</v>
-      </c>
-      <c r="G56">
-        <v>99.848253469250182</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57">
-        <v>4</v>
-      </c>
-      <c r="B57" t="s">
-        <v>62</v>
-      </c>
-      <c r="C57">
-        <v>26.727922061357859</v>
-      </c>
-      <c r="D57">
-        <v>54.041630560342618</v>
-      </c>
-      <c r="E57">
-        <v>108.6690475583121</v>
-      </c>
-      <c r="F57">
-        <v>217.92388155425121</v>
-      </c>
-      <c r="G57">
-        <v>101.8406204335659</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58">
-        <v>4</v>
-      </c>
-      <c r="B58" t="s">
-        <v>63</v>
-      </c>
-      <c r="C58">
-        <v>25.64755903440695</v>
-      </c>
-      <c r="D58">
-        <v>50.784817904249259</v>
-      </c>
-      <c r="E58">
-        <v>102.44570532669439</v>
-      </c>
-      <c r="F58">
-        <v>205.82904579473271</v>
-      </c>
-      <c r="G58">
-        <v>96.176782015020819</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59">
-        <v>5</v>
-      </c>
-      <c r="B59" t="s">
-        <v>64</v>
-      </c>
-      <c r="C59">
-        <v>26.414373490277999</v>
-      </c>
-      <c r="D59">
-        <v>49.416292002980207</v>
-      </c>
-      <c r="E59">
-        <v>104.569998812953</v>
-      </c>
-      <c r="F59">
-        <v>209.36663344984279</v>
-      </c>
-      <c r="G59">
-        <v>97.441824439013502</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>5</v>
-      </c>
-      <c r="B60" t="s">
-        <v>65</v>
-      </c>
-      <c r="C60">
-        <v>25.061772596780042</v>
-      </c>
-      <c r="D60">
-        <v>50.217687953264218</v>
-      </c>
-      <c r="E60">
-        <v>105.2369118846929</v>
-      </c>
-      <c r="F60">
-        <v>211.04877549728519</v>
-      </c>
-      <c r="G60">
-        <v>97.891286983005614</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61">
-        <v>5</v>
-      </c>
-      <c r="B61" t="s">
-        <v>66</v>
-      </c>
-      <c r="C61">
-        <v>26.055199887160551</v>
-      </c>
-      <c r="D61">
-        <v>52.28288660312667</v>
-      </c>
-      <c r="E61">
-        <v>105.108348609036</v>
-      </c>
-      <c r="F61">
-        <v>211.04304927991731</v>
-      </c>
-      <c r="G61">
-        <v>98.622371094810134</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62">
-        <v>5</v>
-      </c>
-      <c r="B62" t="s">
-        <v>67</v>
-      </c>
-      <c r="C62">
-        <v>25.55634918610405</v>
-      </c>
-      <c r="D62">
-        <v>54.041630560342618</v>
-      </c>
-      <c r="E62">
-        <v>103.9827560572969</v>
-      </c>
-      <c r="F62">
-        <v>214.0660171779821</v>
-      </c>
-      <c r="G62">
-        <v>99.411688245431421</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63">
-        <v>5</v>
-      </c>
-      <c r="B63" t="s">
-        <v>68</v>
-      </c>
-      <c r="C63">
-        <v>26.055199887160551</v>
-      </c>
-      <c r="D63">
-        <v>52.28288660312667</v>
-      </c>
-      <c r="E63">
-        <v>103.3028666066464</v>
-      </c>
-      <c r="F63">
-        <v>209.604943347925</v>
-      </c>
-      <c r="G63">
-        <v>97.811474111214665</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64">
-        <v>5</v>
-      </c>
-      <c r="B64" t="s">
-        <v>69</v>
-      </c>
-      <c r="C64">
-        <v>25.877054302287249</v>
-      </c>
-      <c r="D64">
-        <v>52.850016554111697</v>
-      </c>
-      <c r="E64">
-        <v>106.5761026264193</v>
-      </c>
-      <c r="F64">
-        <v>214.08984039418249</v>
-      </c>
-      <c r="G64">
-        <v>99.848253469250182</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65">
-        <v>6</v>
-      </c>
-      <c r="B65" t="s">
-        <v>70</v>
-      </c>
-      <c r="C65">
-        <v>25.061772596780042</v>
-      </c>
-      <c r="D65">
-        <v>52.28288660312667</v>
-      </c>
-      <c r="E65">
-        <v>100.97795130931109</v>
-      </c>
-      <c r="F65">
-        <v>211.04877549728519</v>
-      </c>
-      <c r="G65">
-        <v>97.342846501625758</v>
       </c>
     </row>
   </sheetData>
@@ -6640,7 +5488,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -6812,19 +5660,19 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D8">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E8">
         <v>138</v>
       </c>
       <c r="F8">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="G8">
-        <v>139.25</v>
+        <v>134.25</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -6907,16 +5755,16 @@
         <v>31</v>
       </c>
       <c r="D12">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E12">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F12">
-        <v>690</v>
+        <v>674</v>
       </c>
       <c r="G12">
-        <v>269.25</v>
+        <v>264.5</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -6950,19 +5798,19 @@
         <v>19</v>
       </c>
       <c r="C14">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D14">
         <v>102</v>
       </c>
       <c r="E14">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F14">
-        <v>696</v>
+        <v>673</v>
       </c>
       <c r="G14">
-        <v>279.75</v>
+        <v>272.25</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -7019,19 +5867,19 @@
         <v>22</v>
       </c>
       <c r="C17">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D17">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E17">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="F17">
-        <v>648</v>
+        <v>617</v>
       </c>
       <c r="G17">
-        <v>264.25</v>
+        <v>252.5</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -7134,42 +5982,42 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="D22">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="E22">
-        <v>14</v>
+        <v>138</v>
       </c>
       <c r="F22">
-        <v>15</v>
+        <v>322</v>
       </c>
       <c r="G22">
-        <v>13.25</v>
+        <v>134.25</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="s">
         <v>28</v>
       </c>
       <c r="C23">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="D23">
-        <v>56</v>
+        <v>110</v>
       </c>
       <c r="E23">
-        <v>138</v>
+        <v>278</v>
       </c>
       <c r="F23">
-        <v>336</v>
+        <v>631</v>
       </c>
       <c r="G23">
-        <v>139.25</v>
+        <v>264</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -7180,19 +6028,19 @@
         <v>29</v>
       </c>
       <c r="C24">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D24">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="E24">
-        <v>278</v>
+        <v>240</v>
       </c>
       <c r="F24">
-        <v>631</v>
+        <v>581</v>
       </c>
       <c r="G24">
-        <v>264</v>
+        <v>237</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -7203,19 +6051,19 @@
         <v>30</v>
       </c>
       <c r="C25">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D25">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="E25">
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="F25">
-        <v>594</v>
+        <v>452</v>
       </c>
       <c r="G25">
-        <v>243.75</v>
+        <v>207.75</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -7226,19 +6074,19 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D26">
-        <v>115</v>
+        <v>68</v>
       </c>
       <c r="E26">
-        <v>229</v>
+        <v>172</v>
       </c>
       <c r="F26">
-        <v>452</v>
+        <v>419</v>
       </c>
       <c r="G26">
-        <v>207.75</v>
+        <v>171.25</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -7249,19 +6097,19 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D27">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E27">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F27">
-        <v>419</v>
+        <v>364</v>
       </c>
       <c r="G27">
-        <v>171.25</v>
+        <v>157.5</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -7272,19 +6120,19 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D28">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="E28">
-        <v>174</v>
+        <v>261</v>
       </c>
       <c r="F28">
-        <v>376</v>
+        <v>674</v>
       </c>
       <c r="G28">
-        <v>161.25</v>
+        <v>264.5</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -7298,16 +6146,16 @@
         <v>31</v>
       </c>
       <c r="D29">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E29">
-        <v>262</v>
+        <v>283</v>
       </c>
       <c r="F29">
-        <v>690</v>
+        <v>673</v>
       </c>
       <c r="G29">
-        <v>269.25</v>
+        <v>272.25</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -7318,19 +6166,19 @@
         <v>35</v>
       </c>
       <c r="C30">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D30">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="E30">
-        <v>289</v>
+        <v>225</v>
       </c>
       <c r="F30">
-        <v>696</v>
+        <v>497</v>
       </c>
       <c r="G30">
-        <v>279.75</v>
+        <v>210.75</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -7341,19 +6189,19 @@
         <v>36</v>
       </c>
       <c r="C31">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D31">
         <v>90</v>
       </c>
       <c r="E31">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="F31">
-        <v>497</v>
+        <v>533</v>
       </c>
       <c r="G31">
-        <v>210.75</v>
+        <v>223.75</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -7367,16 +6215,16 @@
         <v>30</v>
       </c>
       <c r="D32">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E32">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="F32">
-        <v>542</v>
+        <v>617</v>
       </c>
       <c r="G32">
-        <v>227.25</v>
+        <v>252.5</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -7387,19 +6235,19 @@
         <v>38</v>
       </c>
       <c r="C33">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="D33">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="E33">
-        <v>286</v>
+        <v>17</v>
       </c>
       <c r="F33">
-        <v>648</v>
+        <v>17</v>
       </c>
       <c r="G33">
-        <v>264.25</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -7410,19 +6258,19 @@
         <v>39</v>
       </c>
       <c r="C34">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D34">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E34">
         <v>17</v>
       </c>
       <c r="F34">
+        <v>19</v>
+      </c>
+      <c r="G34">
         <v>17</v>
-      </c>
-      <c r="G34">
-        <v>16.25</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -7433,19 +6281,19 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D35">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E35">
+        <v>16</v>
+      </c>
+      <c r="F35">
         <v>17</v>
       </c>
-      <c r="F35">
-        <v>19</v>
-      </c>
       <c r="G35">
-        <v>17</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -7456,19 +6304,19 @@
         <v>41</v>
       </c>
       <c r="C36">
+        <v>10</v>
+      </c>
+      <c r="D36">
+        <v>13</v>
+      </c>
+      <c r="E36">
         <v>15</v>
       </c>
-      <c r="D36">
-        <v>18</v>
-      </c>
-      <c r="E36">
+      <c r="F36">
         <v>16</v>
       </c>
-      <c r="F36">
-        <v>17</v>
-      </c>
       <c r="G36">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -7479,19 +6327,19 @@
         <v>42</v>
       </c>
       <c r="C37">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D37">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E37">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F37">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G37">
-        <v>17.75</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -7502,134 +6350,134 @@
         <v>43</v>
       </c>
       <c r="C38">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D38">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E38">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F38">
         <v>16</v>
       </c>
       <c r="G38">
-        <v>13.5</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B39" t="s">
         <v>44</v>
       </c>
       <c r="C39">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="D39">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="E39">
-        <v>15</v>
+        <v>240</v>
       </c>
       <c r="F39">
-        <v>16</v>
+        <v>581</v>
       </c>
       <c r="G39">
-        <v>13.5</v>
+        <v>237</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B40" t="s">
         <v>45</v>
       </c>
       <c r="C40">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="D40">
-        <v>13</v>
+        <v>115</v>
       </c>
       <c r="E40">
-        <v>12</v>
+        <v>229</v>
       </c>
       <c r="F40">
-        <v>13</v>
+        <v>452</v>
       </c>
       <c r="G40">
-        <v>12.5</v>
+        <v>207.75</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B41" t="s">
         <v>46</v>
       </c>
       <c r="C41">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D41">
-        <v>16</v>
+        <v>114</v>
       </c>
       <c r="E41">
-        <v>16</v>
+        <v>260</v>
       </c>
       <c r="F41">
-        <v>16</v>
+        <v>518</v>
       </c>
       <c r="G41">
-        <v>15.25</v>
+        <v>231</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B42" t="s">
         <v>47</v>
       </c>
       <c r="C42">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D42">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="E42">
-        <v>16</v>
+        <v>174</v>
       </c>
       <c r="F42">
-        <v>16</v>
+        <v>364</v>
       </c>
       <c r="G42">
-        <v>15.25</v>
+        <v>157.5</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B43" t="s">
         <v>48</v>
       </c>
       <c r="C43">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="D43">
-        <v>13</v>
+        <v>90</v>
       </c>
       <c r="E43">
-        <v>14</v>
+        <v>242</v>
       </c>
       <c r="F43">
-        <v>15</v>
+        <v>533</v>
       </c>
       <c r="G43">
-        <v>13.25</v>
+        <v>223.75</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -7640,19 +6488,19 @@
         <v>49</v>
       </c>
       <c r="C44">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D44">
-        <v>95</v>
+        <v>17</v>
       </c>
       <c r="E44">
-        <v>249</v>
+        <v>17</v>
       </c>
       <c r="F44">
-        <v>594</v>
+        <v>17</v>
       </c>
       <c r="G44">
-        <v>243.75</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -7663,19 +6511,19 @@
         <v>50</v>
       </c>
       <c r="C45">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="D45">
-        <v>115</v>
+        <v>20</v>
       </c>
       <c r="E45">
-        <v>229</v>
+        <v>19</v>
       </c>
       <c r="F45">
-        <v>452</v>
+        <v>18</v>
       </c>
       <c r="G45">
-        <v>207.75</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -7686,19 +6534,19 @@
         <v>51</v>
       </c>
       <c r="C46">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D46">
-        <v>115</v>
+        <v>19</v>
       </c>
       <c r="E46">
-        <v>262</v>
+        <v>17</v>
       </c>
       <c r="F46">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="G46">
-        <v>231.25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -7709,432 +6557,64 @@
         <v>52</v>
       </c>
       <c r="C47">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D47">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="E47">
-        <v>174</v>
+        <v>12</v>
       </c>
       <c r="F47">
-        <v>376</v>
+        <v>13</v>
       </c>
       <c r="G47">
-        <v>161.25</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B48" t="s">
         <v>53</v>
       </c>
       <c r="C48">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D48">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="E48">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="F48">
-        <v>542</v>
+        <v>518</v>
       </c>
       <c r="G48">
-        <v>227.25</v>
+        <v>231</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B49" t="s">
         <v>54</v>
       </c>
       <c r="C49">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D49">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E49">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F49">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G49">
-        <v>16.25</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50">
-        <v>4</v>
-      </c>
-      <c r="B50" t="s">
-        <v>55</v>
-      </c>
-      <c r="C50">
-        <v>13</v>
-      </c>
-      <c r="D50">
-        <v>21</v>
-      </c>
-      <c r="E50">
-        <v>15</v>
-      </c>
-      <c r="F50">
-        <v>22</v>
-      </c>
-      <c r="G50">
-        <v>17.75</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51">
-        <v>4</v>
-      </c>
-      <c r="B51" t="s">
-        <v>56</v>
-      </c>
-      <c r="C51">
-        <v>13</v>
-      </c>
-      <c r="D51">
-        <v>20</v>
-      </c>
-      <c r="E51">
-        <v>19</v>
-      </c>
-      <c r="F51">
-        <v>18</v>
-      </c>
-      <c r="G51">
-        <v>17.5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52">
-        <v>4</v>
-      </c>
-      <c r="B52" t="s">
-        <v>57</v>
-      </c>
-      <c r="C52">
-        <v>13</v>
-      </c>
-      <c r="D52">
-        <v>19</v>
-      </c>
-      <c r="E52">
-        <v>17</v>
-      </c>
-      <c r="F52">
-        <v>19</v>
-      </c>
-      <c r="G52">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53">
-        <v>4</v>
-      </c>
-      <c r="B53" t="s">
-        <v>58</v>
-      </c>
-      <c r="C53">
-        <v>13</v>
-      </c>
-      <c r="D53">
-        <v>18</v>
-      </c>
-      <c r="E53">
-        <v>22</v>
-      </c>
-      <c r="F53">
-        <v>20</v>
-      </c>
-      <c r="G53">
-        <v>18.25</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54">
-        <v>4</v>
-      </c>
-      <c r="B54" t="s">
-        <v>59</v>
-      </c>
-      <c r="C54">
-        <v>15</v>
-      </c>
-      <c r="D54">
-        <v>21</v>
-      </c>
-      <c r="E54">
-        <v>14</v>
-      </c>
-      <c r="F54">
-        <v>21</v>
-      </c>
-      <c r="G54">
-        <v>17.75</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55">
-        <v>4</v>
-      </c>
-      <c r="B55" t="s">
-        <v>60</v>
-      </c>
-      <c r="C55">
-        <v>10</v>
-      </c>
-      <c r="D55">
-        <v>13</v>
-      </c>
-      <c r="E55">
-        <v>15</v>
-      </c>
-      <c r="F55">
-        <v>16</v>
-      </c>
-      <c r="G55">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56">
-        <v>4</v>
-      </c>
-      <c r="B56" t="s">
-        <v>61</v>
-      </c>
-      <c r="C56">
-        <v>12</v>
-      </c>
-      <c r="D56">
-        <v>13</v>
-      </c>
-      <c r="E56">
-        <v>12</v>
-      </c>
-      <c r="F56">
-        <v>13</v>
-      </c>
-      <c r="G56">
-        <v>12.5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57">
-        <v>4</v>
-      </c>
-      <c r="B57" t="s">
-        <v>62</v>
-      </c>
-      <c r="C57">
-        <v>12</v>
-      </c>
-      <c r="D57">
-        <v>13</v>
-      </c>
-      <c r="E57">
-        <v>12</v>
-      </c>
-      <c r="F57">
-        <v>13</v>
-      </c>
-      <c r="G57">
-        <v>12.5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58">
-        <v>4</v>
-      </c>
-      <c r="B58" t="s">
-        <v>63</v>
-      </c>
-      <c r="C58">
-        <v>13</v>
-      </c>
-      <c r="D58">
-        <v>16</v>
-      </c>
-      <c r="E58">
-        <v>16</v>
-      </c>
-      <c r="F58">
-        <v>16</v>
-      </c>
-      <c r="G58">
-        <v>15.25</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59">
-        <v>5</v>
-      </c>
-      <c r="B59" t="s">
-        <v>64</v>
-      </c>
-      <c r="C59">
-        <v>30</v>
-      </c>
-      <c r="D59">
-        <v>115</v>
-      </c>
-      <c r="E59">
-        <v>262</v>
-      </c>
-      <c r="F59">
-        <v>518</v>
-      </c>
-      <c r="G59">
-        <v>231.25</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>5</v>
-      </c>
-      <c r="B60" t="s">
-        <v>65</v>
-      </c>
-      <c r="C60">
-        <v>13</v>
-      </c>
-      <c r="D60">
-        <v>21</v>
-      </c>
-      <c r="E60">
-        <v>15</v>
-      </c>
-      <c r="F60">
-        <v>22</v>
-      </c>
-      <c r="G60">
-        <v>17.75</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61">
-        <v>5</v>
-      </c>
-      <c r="B61" t="s">
-        <v>66</v>
-      </c>
-      <c r="C61">
-        <v>13</v>
-      </c>
-      <c r="D61">
-        <v>20</v>
-      </c>
-      <c r="E61">
-        <v>19</v>
-      </c>
-      <c r="F61">
-        <v>18</v>
-      </c>
-      <c r="G61">
-        <v>17.5</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62">
-        <v>5</v>
-      </c>
-      <c r="B62" t="s">
-        <v>67</v>
-      </c>
-      <c r="C62">
-        <v>13</v>
-      </c>
-      <c r="D62">
-        <v>21</v>
-      </c>
-      <c r="E62">
-        <v>20</v>
-      </c>
-      <c r="F62">
-        <v>16</v>
-      </c>
-      <c r="G62">
-        <v>17.5</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63">
-        <v>5</v>
-      </c>
-      <c r="B63" t="s">
-        <v>68</v>
-      </c>
-      <c r="C63">
-        <v>13</v>
-      </c>
-      <c r="D63">
-        <v>18</v>
-      </c>
-      <c r="E63">
-        <v>22</v>
-      </c>
-      <c r="F63">
-        <v>20</v>
-      </c>
-      <c r="G63">
-        <v>18.25</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64">
-        <v>5</v>
-      </c>
-      <c r="B64" t="s">
-        <v>69</v>
-      </c>
-      <c r="C64">
-        <v>12</v>
-      </c>
-      <c r="D64">
-        <v>13</v>
-      </c>
-      <c r="E64">
-        <v>12</v>
-      </c>
-      <c r="F64">
-        <v>13</v>
-      </c>
-      <c r="G64">
-        <v>12.5</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65">
-        <v>6</v>
-      </c>
-      <c r="B65" t="s">
-        <v>70</v>
-      </c>
-      <c r="C65">
-        <v>13</v>
-      </c>
-      <c r="D65">
-        <v>21</v>
-      </c>
-      <c r="E65">
-        <v>20</v>
-      </c>
-      <c r="F65">
-        <v>16</v>
-      </c>
-      <c r="G65">
         <v>17.5</v>
       </c>
     </row>
@@ -8145,7 +6625,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -8409,19 +6889,19 @@
         <v>17</v>
       </c>
       <c r="C12">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D12">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E12">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="F12">
-        <v>3493</v>
+        <v>3486</v>
       </c>
       <c r="G12">
-        <v>1164.75</v>
+        <v>1162.25</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -8455,19 +6935,19 @@
         <v>19</v>
       </c>
       <c r="C14">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D14">
         <v>92</v>
       </c>
       <c r="E14">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F14">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="G14">
-        <v>694.5</v>
+        <v>694</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -8639,42 +7119,42 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="D22">
-        <v>41</v>
+        <v>266</v>
       </c>
       <c r="E22">
-        <v>39</v>
+        <v>1058</v>
       </c>
       <c r="F22">
-        <v>38</v>
+        <v>4201</v>
       </c>
       <c r="G22">
-        <v>37.25</v>
+        <v>1398.5</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="s">
         <v>28</v>
       </c>
       <c r="C23">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="D23">
-        <v>266</v>
+        <v>130</v>
       </c>
       <c r="E23">
-        <v>1058</v>
+        <v>496</v>
       </c>
       <c r="F23">
-        <v>4201</v>
+        <v>1909</v>
       </c>
       <c r="G23">
-        <v>1398.5</v>
+        <v>644</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -8685,19 +7165,19 @@
         <v>29</v>
       </c>
       <c r="C24">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D24">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="E24">
-        <v>496</v>
+        <v>526</v>
       </c>
       <c r="F24">
-        <v>1909</v>
+        <v>2111</v>
       </c>
       <c r="G24">
-        <v>644</v>
+        <v>703.25</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -8708,19 +7188,19 @@
         <v>30</v>
       </c>
       <c r="C25">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D25">
-        <v>140</v>
+        <v>186</v>
       </c>
       <c r="E25">
-        <v>524</v>
+        <v>645</v>
       </c>
       <c r="F25">
-        <v>2107</v>
+        <v>2471</v>
       </c>
       <c r="G25">
-        <v>703.25</v>
+        <v>836.75</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -8731,19 +7211,19 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="D26">
-        <v>186</v>
+        <v>212</v>
       </c>
       <c r="E26">
-        <v>645</v>
+        <v>753</v>
       </c>
       <c r="F26">
-        <v>2471</v>
+        <v>2897</v>
       </c>
       <c r="G26">
-        <v>836.75</v>
+        <v>979.75</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -8757,16 +7237,16 @@
         <v>57</v>
       </c>
       <c r="D27">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E27">
-        <v>753</v>
+        <v>789</v>
       </c>
       <c r="F27">
-        <v>2897</v>
+        <v>2954</v>
       </c>
       <c r="G27">
-        <v>979.75</v>
+        <v>1003.75</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -8777,19 +7257,19 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D28">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="E28">
-        <v>789</v>
+        <v>876</v>
       </c>
       <c r="F28">
-        <v>2960</v>
+        <v>3486</v>
       </c>
       <c r="G28">
-        <v>1006</v>
+        <v>1162.25</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -8800,19 +7280,19 @@
         <v>34</v>
       </c>
       <c r="C29">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="D29">
-        <v>233</v>
+        <v>92</v>
       </c>
       <c r="E29">
-        <v>875</v>
+        <v>410</v>
       </c>
       <c r="F29">
-        <v>3493</v>
+        <v>2242</v>
       </c>
       <c r="G29">
-        <v>1164.75</v>
+        <v>694</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -8823,19 +7303,19 @@
         <v>35</v>
       </c>
       <c r="C30">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D30">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="E30">
-        <v>409</v>
+        <v>525</v>
       </c>
       <c r="F30">
-        <v>2243</v>
+        <v>2852</v>
       </c>
       <c r="G30">
-        <v>694.5</v>
+        <v>881.5</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -8846,19 +7326,19 @@
         <v>36</v>
       </c>
       <c r="C31">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D31">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E31">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="F31">
-        <v>2852</v>
+        <v>2864</v>
       </c>
       <c r="G31">
-        <v>881.5</v>
+        <v>886.25</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -8869,19 +7349,19 @@
         <v>37</v>
       </c>
       <c r="C32">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="D32">
-        <v>117</v>
+        <v>243</v>
       </c>
       <c r="E32">
-        <v>529</v>
+        <v>776</v>
       </c>
       <c r="F32">
-        <v>2864</v>
+        <v>3037</v>
       </c>
       <c r="G32">
-        <v>886.75</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -8892,19 +7372,19 @@
         <v>38</v>
       </c>
       <c r="C33">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="D33">
-        <v>243</v>
+        <v>38</v>
       </c>
       <c r="E33">
-        <v>776</v>
+        <v>39</v>
       </c>
       <c r="F33">
-        <v>3037</v>
+        <v>39</v>
       </c>
       <c r="G33">
-        <v>1030</v>
+        <v>36.25</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -8915,19 +7395,19 @@
         <v>39</v>
       </c>
       <c r="C34">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D34">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E34">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F34">
         <v>39</v>
       </c>
       <c r="G34">
-        <v>36.25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -8938,19 +7418,19 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D35">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E35">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F35">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G35">
-        <v>35</v>
+        <v>33.75</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -8961,19 +7441,19 @@
         <v>41</v>
       </c>
       <c r="C36">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D36">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E36">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="F36">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G36">
-        <v>33.75</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -8984,19 +7464,19 @@
         <v>42</v>
       </c>
       <c r="C37">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D37">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="E37">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="F37">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="G37">
-        <v>50</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -9007,134 +7487,134 @@
         <v>43</v>
       </c>
       <c r="C38">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D38">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="E38">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F38">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G38">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B39" t="s">
         <v>44</v>
       </c>
       <c r="C39">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D39">
-        <v>33</v>
+        <v>138</v>
       </c>
       <c r="E39">
-        <v>40</v>
+        <v>526</v>
       </c>
       <c r="F39">
-        <v>42</v>
+        <v>2111</v>
       </c>
       <c r="G39">
-        <v>34</v>
+        <v>703.25</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B40" t="s">
         <v>45</v>
       </c>
       <c r="C40">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="D40">
-        <v>38</v>
+        <v>186</v>
       </c>
       <c r="E40">
-        <v>37</v>
+        <v>645</v>
       </c>
       <c r="F40">
-        <v>45</v>
+        <v>2471</v>
       </c>
       <c r="G40">
-        <v>35</v>
+        <v>836.75</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B41" t="s">
         <v>46</v>
       </c>
       <c r="C41">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="D41">
-        <v>45</v>
+        <v>194</v>
       </c>
       <c r="E41">
-        <v>44</v>
+        <v>697</v>
       </c>
       <c r="F41">
-        <v>44</v>
+        <v>2585</v>
       </c>
       <c r="G41">
-        <v>41</v>
+        <v>881.5</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B42" t="s">
         <v>47</v>
       </c>
       <c r="C42">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="D42">
-        <v>45</v>
+        <v>215</v>
       </c>
       <c r="E42">
-        <v>44</v>
+        <v>789</v>
       </c>
       <c r="F42">
-        <v>44</v>
+        <v>2954</v>
       </c>
       <c r="G42">
-        <v>41</v>
+        <v>1003.75</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B43" t="s">
         <v>48</v>
       </c>
       <c r="C43">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D43">
-        <v>41</v>
+        <v>117</v>
       </c>
       <c r="E43">
-        <v>39</v>
+        <v>529</v>
       </c>
       <c r="F43">
-        <v>38</v>
+        <v>2864</v>
       </c>
       <c r="G43">
-        <v>37.25</v>
+        <v>886.25</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -9145,19 +7625,19 @@
         <v>49</v>
       </c>
       <c r="C44">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D44">
-        <v>140</v>
+        <v>38</v>
       </c>
       <c r="E44">
-        <v>524</v>
+        <v>39</v>
       </c>
       <c r="F44">
-        <v>2107</v>
+        <v>39</v>
       </c>
       <c r="G44">
-        <v>703.25</v>
+        <v>36.25</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -9168,19 +7648,19 @@
         <v>50</v>
       </c>
       <c r="C45">
+        <v>23</v>
+      </c>
+      <c r="D45">
         <v>45</v>
       </c>
-      <c r="D45">
-        <v>186</v>
-      </c>
       <c r="E45">
-        <v>645</v>
+        <v>43</v>
       </c>
       <c r="F45">
-        <v>2471</v>
+        <v>42</v>
       </c>
       <c r="G45">
-        <v>836.75</v>
+        <v>38.25</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -9191,19 +7671,19 @@
         <v>51</v>
       </c>
       <c r="C46">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="D46">
-        <v>195</v>
+        <v>41</v>
       </c>
       <c r="E46">
-        <v>697</v>
+        <v>37</v>
       </c>
       <c r="F46">
-        <v>2583</v>
+        <v>39</v>
       </c>
       <c r="G46">
-        <v>882</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -9214,433 +7694,65 @@
         <v>52</v>
       </c>
       <c r="C47">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="D47">
-        <v>216</v>
+        <v>38</v>
       </c>
       <c r="E47">
-        <v>789</v>
+        <v>37</v>
       </c>
       <c r="F47">
-        <v>2960</v>
+        <v>45</v>
       </c>
       <c r="G47">
-        <v>1006</v>
+        <v>35</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B48" t="s">
         <v>53</v>
       </c>
       <c r="C48">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D48">
-        <v>117</v>
+        <v>194</v>
       </c>
       <c r="E48">
-        <v>529</v>
+        <v>697</v>
       </c>
       <c r="F48">
-        <v>2864</v>
+        <v>2585</v>
       </c>
       <c r="G48">
-        <v>886.75</v>
+        <v>881.5</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B49" t="s">
         <v>54</v>
       </c>
       <c r="C49">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D49">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E49">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F49">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G49">
-        <v>36.25</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50">
-        <v>4</v>
-      </c>
-      <c r="B50" t="s">
-        <v>55</v>
-      </c>
-      <c r="C50">
-        <v>27</v>
-      </c>
-      <c r="D50">
-        <v>45</v>
-      </c>
-      <c r="E50">
-        <v>37</v>
-      </c>
-      <c r="F50">
-        <v>43</v>
-      </c>
-      <c r="G50">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51">
-        <v>4</v>
-      </c>
-      <c r="B51" t="s">
-        <v>56</v>
-      </c>
-      <c r="C51">
-        <v>23</v>
-      </c>
-      <c r="D51">
-        <v>45</v>
-      </c>
-      <c r="E51">
-        <v>43</v>
-      </c>
-      <c r="F51">
-        <v>42</v>
-      </c>
-      <c r="G51">
         <v>38.25</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52">
-        <v>4</v>
-      </c>
-      <c r="B52" t="s">
-        <v>57</v>
-      </c>
-      <c r="C52">
-        <v>23</v>
-      </c>
-      <c r="D52">
-        <v>41</v>
-      </c>
-      <c r="E52">
-        <v>37</v>
-      </c>
-      <c r="F52">
-        <v>39</v>
-      </c>
-      <c r="G52">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53">
-        <v>4</v>
-      </c>
-      <c r="B53" t="s">
-        <v>58</v>
-      </c>
-      <c r="C53">
-        <v>24</v>
-      </c>
-      <c r="D53">
-        <v>39</v>
-      </c>
-      <c r="E53">
-        <v>53</v>
-      </c>
-      <c r="F53">
-        <v>67</v>
-      </c>
-      <c r="G53">
-        <v>45.75</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54">
-        <v>4</v>
-      </c>
-      <c r="B54" t="s">
-        <v>59</v>
-      </c>
-      <c r="C54">
-        <v>30</v>
-      </c>
-      <c r="D54">
-        <v>47</v>
-      </c>
-      <c r="E54">
-        <v>59</v>
-      </c>
-      <c r="F54">
-        <v>64</v>
-      </c>
-      <c r="G54">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55">
-        <v>4</v>
-      </c>
-      <c r="B55" t="s">
-        <v>60</v>
-      </c>
-      <c r="C55">
-        <v>21</v>
-      </c>
-      <c r="D55">
-        <v>33</v>
-      </c>
-      <c r="E55">
-        <v>40</v>
-      </c>
-      <c r="F55">
-        <v>42</v>
-      </c>
-      <c r="G55">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56">
-        <v>4</v>
-      </c>
-      <c r="B56" t="s">
-        <v>61</v>
-      </c>
-      <c r="C56">
-        <v>20</v>
-      </c>
-      <c r="D56">
-        <v>38</v>
-      </c>
-      <c r="E56">
-        <v>37</v>
-      </c>
-      <c r="F56">
-        <v>45</v>
-      </c>
-      <c r="G56">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57">
-        <v>4</v>
-      </c>
-      <c r="B57" t="s">
-        <v>62</v>
-      </c>
-      <c r="C57">
-        <v>20</v>
-      </c>
-      <c r="D57">
-        <v>38</v>
-      </c>
-      <c r="E57">
-        <v>37</v>
-      </c>
-      <c r="F57">
-        <v>45</v>
-      </c>
-      <c r="G57">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58">
-        <v>4</v>
-      </c>
-      <c r="B58" t="s">
-        <v>63</v>
-      </c>
-      <c r="C58">
-        <v>31</v>
-      </c>
-      <c r="D58">
-        <v>45</v>
-      </c>
-      <c r="E58">
-        <v>44</v>
-      </c>
-      <c r="F58">
-        <v>44</v>
-      </c>
-      <c r="G58">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59">
-        <v>5</v>
-      </c>
-      <c r="B59" t="s">
-        <v>64</v>
-      </c>
-      <c r="C59">
-        <v>53</v>
-      </c>
-      <c r="D59">
-        <v>195</v>
-      </c>
-      <c r="E59">
-        <v>697</v>
-      </c>
-      <c r="F59">
-        <v>2583</v>
-      </c>
-      <c r="G59">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>5</v>
-      </c>
-      <c r="B60" t="s">
-        <v>65</v>
-      </c>
-      <c r="C60">
-        <v>27</v>
-      </c>
-      <c r="D60">
-        <v>45</v>
-      </c>
-      <c r="E60">
-        <v>37</v>
-      </c>
-      <c r="F60">
-        <v>43</v>
-      </c>
-      <c r="G60">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61">
-        <v>5</v>
-      </c>
-      <c r="B61" t="s">
-        <v>66</v>
-      </c>
-      <c r="C61">
-        <v>23</v>
-      </c>
-      <c r="D61">
-        <v>45</v>
-      </c>
-      <c r="E61">
-        <v>43</v>
-      </c>
-      <c r="F61">
-        <v>42</v>
-      </c>
-      <c r="G61">
-        <v>38.25</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62">
-        <v>5</v>
-      </c>
-      <c r="B62" t="s">
-        <v>67</v>
-      </c>
-      <c r="C62">
-        <v>27</v>
-      </c>
-      <c r="D62">
-        <v>47</v>
-      </c>
-      <c r="E62">
-        <v>45</v>
-      </c>
-      <c r="F62">
-        <v>45</v>
-      </c>
-      <c r="G62">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63">
-        <v>5</v>
-      </c>
-      <c r="B63" t="s">
-        <v>68</v>
-      </c>
-      <c r="C63">
-        <v>24</v>
-      </c>
-      <c r="D63">
-        <v>39</v>
-      </c>
-      <c r="E63">
-        <v>53</v>
-      </c>
-      <c r="F63">
-        <v>67</v>
-      </c>
-      <c r="G63">
-        <v>45.75</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64">
-        <v>5</v>
-      </c>
-      <c r="B64" t="s">
-        <v>69</v>
-      </c>
-      <c r="C64">
-        <v>20</v>
-      </c>
-      <c r="D64">
-        <v>38</v>
-      </c>
-      <c r="E64">
-        <v>37</v>
-      </c>
-      <c r="F64">
-        <v>45</v>
-      </c>
-      <c r="G64">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65">
-        <v>6</v>
-      </c>
-      <c r="B65" t="s">
-        <v>70</v>
-      </c>
-      <c r="C65">
-        <v>27</v>
-      </c>
-      <c r="D65">
-        <v>47</v>
-      </c>
-      <c r="E65">
-        <v>45</v>
-      </c>
-      <c r="F65">
-        <v>45</v>
-      </c>
-      <c r="G65">
-        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -9650,7 +7762,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -9920,13 +8032,13 @@
         <v>13</v>
       </c>
       <c r="E12">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F12">
         <v>18</v>
       </c>
       <c r="G12">
-        <v>15.5</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -10144,24 +8256,24 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D22">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E22">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F22">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G22">
-        <v>11</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="s">
         <v>28</v>
@@ -10170,16 +8282,16 @@
         <v>9</v>
       </c>
       <c r="D23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G23">
-        <v>8.25</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -10190,19 +8302,19 @@
         <v>29</v>
       </c>
       <c r="C24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E24">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F24">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G24">
-        <v>9.25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -10213,19 +8325,19 @@
         <v>30</v>
       </c>
       <c r="C25">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D25">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E25">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F25">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G25">
-        <v>12.25</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -10236,19 +8348,19 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D26">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E26">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F26">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G26">
-        <v>16.75</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -10259,19 +8371,19 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D27">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E27">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F27">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G27">
-        <v>9.75</v>
+        <v>17.75</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -10282,19 +8394,19 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D28">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E28">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F28">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G28">
-        <v>17.75</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -10305,19 +8417,19 @@
         <v>34</v>
       </c>
       <c r="C29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G29">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -10328,10 +8440,10 @@
         <v>35</v>
       </c>
       <c r="C30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E30">
         <v>9</v>
@@ -10340,7 +8452,7 @@
         <v>9</v>
       </c>
       <c r="G30">
-        <v>9</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -10351,19 +8463,19 @@
         <v>36</v>
       </c>
       <c r="C31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D31">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E31">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F31">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G31">
-        <v>8.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -10377,16 +8489,16 @@
         <v>10</v>
       </c>
       <c r="D32">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E32">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F32">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G32">
-        <v>13.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -10397,19 +8509,19 @@
         <v>38</v>
       </c>
       <c r="C33">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D33">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E33">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F33">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G33">
-        <v>8.5</v>
+        <v>13.25</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -10420,7 +8532,7 @@
         <v>39</v>
       </c>
       <c r="C34">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D34">
         <v>14</v>
@@ -10432,7 +8544,7 @@
         <v>14</v>
       </c>
       <c r="G34">
-        <v>13.25</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -10443,19 +8555,19 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D35">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E35">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F35">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G35">
-        <v>13.75</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -10469,16 +8581,16 @@
         <v>9</v>
       </c>
       <c r="D36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E36">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G36">
-        <v>9</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -10489,19 +8601,19 @@
         <v>42</v>
       </c>
       <c r="C37">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D37">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E37">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F37">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G37">
-        <v>13.25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -10512,93 +8624,93 @@
         <v>43</v>
       </c>
       <c r="C38">
+        <v>7</v>
+      </c>
+      <c r="D38">
         <v>9</v>
       </c>
-      <c r="D38">
-        <v>10</v>
-      </c>
       <c r="E38">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G38">
-        <v>10.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B39" t="s">
         <v>44</v>
       </c>
       <c r="C39">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D39">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E39">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F39">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G39">
-        <v>13.25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B40" t="s">
         <v>45</v>
       </c>
       <c r="C40">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D40">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E40">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F40">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G40">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B41" t="s">
         <v>46</v>
       </c>
       <c r="C41">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D41">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E41">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="F41">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G41">
-        <v>8.5</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B42" t="s">
         <v>47</v>
@@ -10607,30 +8719,30 @@
         <v>9</v>
       </c>
       <c r="D42">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E42">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F42">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G42">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B43" t="s">
         <v>48</v>
       </c>
       <c r="C43">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D43">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E43">
         <v>9</v>
@@ -10639,7 +8751,7 @@
         <v>9</v>
       </c>
       <c r="G43">
-        <v>9</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -10656,13 +8768,13 @@
         <v>9</v>
       </c>
       <c r="E44">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F44">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G44">
-        <v>9</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -10673,19 +8785,19 @@
         <v>50</v>
       </c>
       <c r="C45">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D45">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E45">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F45">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G45">
-        <v>9</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -10696,19 +8808,19 @@
         <v>51</v>
       </c>
       <c r="C46">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D46">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E46">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F46">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G46">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -10719,10 +8831,10 @@
         <v>52</v>
       </c>
       <c r="C47">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D47">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E47">
         <v>10</v>
@@ -10731,18 +8843,18 @@
         <v>10</v>
       </c>
       <c r="G47">
-        <v>9.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B48" t="s">
         <v>53</v>
       </c>
       <c r="C48">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D48">
         <v>8</v>
@@ -10754,18 +8866,18 @@
         <v>9</v>
       </c>
       <c r="G48">
-        <v>8.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B49" t="s">
         <v>54</v>
       </c>
       <c r="C49">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D49">
         <v>9</v>
@@ -10777,375 +8889,7 @@
         <v>11</v>
       </c>
       <c r="G49">
-        <v>9.75</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50">
-        <v>4</v>
-      </c>
-      <c r="B50" t="s">
-        <v>55</v>
-      </c>
-      <c r="C50">
-        <v>11</v>
-      </c>
-      <c r="D50">
-        <v>12</v>
-      </c>
-      <c r="E50">
-        <v>14</v>
-      </c>
-      <c r="F50">
-        <v>14</v>
-      </c>
-      <c r="G50">
-        <v>12.75</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51">
-        <v>4</v>
-      </c>
-      <c r="B51" t="s">
-        <v>56</v>
-      </c>
-      <c r="C51">
-        <v>13</v>
-      </c>
-      <c r="D51">
-        <v>14</v>
-      </c>
-      <c r="E51">
-        <v>14</v>
-      </c>
-      <c r="F51">
-        <v>14</v>
-      </c>
-      <c r="G51">
-        <v>13.75</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52">
-        <v>4</v>
-      </c>
-      <c r="B52" t="s">
-        <v>57</v>
-      </c>
-      <c r="C52">
         <v>10</v>
-      </c>
-      <c r="D52">
-        <v>9</v>
-      </c>
-      <c r="E52">
-        <v>10</v>
-      </c>
-      <c r="F52">
-        <v>11</v>
-      </c>
-      <c r="G52">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53">
-        <v>4</v>
-      </c>
-      <c r="B53" t="s">
-        <v>58</v>
-      </c>
-      <c r="C53">
-        <v>13</v>
-      </c>
-      <c r="D53">
-        <v>14</v>
-      </c>
-      <c r="E53">
-        <v>15</v>
-      </c>
-      <c r="F53">
-        <v>15</v>
-      </c>
-      <c r="G53">
-        <v>14.25</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54">
-        <v>4</v>
-      </c>
-      <c r="B54" t="s">
-        <v>59</v>
-      </c>
-      <c r="C54">
-        <v>9</v>
-      </c>
-      <c r="D54">
-        <v>9</v>
-      </c>
-      <c r="E54">
-        <v>10</v>
-      </c>
-      <c r="F54">
-        <v>11</v>
-      </c>
-      <c r="G54">
-        <v>9.75</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55">
-        <v>4</v>
-      </c>
-      <c r="B55" t="s">
-        <v>60</v>
-      </c>
-      <c r="C55">
-        <v>9</v>
-      </c>
-      <c r="D55">
-        <v>10</v>
-      </c>
-      <c r="E55">
-        <v>13</v>
-      </c>
-      <c r="F55">
-        <v>10</v>
-      </c>
-      <c r="G55">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56">
-        <v>4</v>
-      </c>
-      <c r="B56" t="s">
-        <v>61</v>
-      </c>
-      <c r="C56">
-        <v>10</v>
-      </c>
-      <c r="D56">
-        <v>10</v>
-      </c>
-      <c r="E56">
-        <v>10</v>
-      </c>
-      <c r="F56">
-        <v>10</v>
-      </c>
-      <c r="G56">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57">
-        <v>4</v>
-      </c>
-      <c r="B57" t="s">
-        <v>62</v>
-      </c>
-      <c r="C57">
-        <v>13</v>
-      </c>
-      <c r="D57">
-        <v>13</v>
-      </c>
-      <c r="E57">
-        <v>13</v>
-      </c>
-      <c r="F57">
-        <v>13</v>
-      </c>
-      <c r="G57">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58">
-        <v>4</v>
-      </c>
-      <c r="B58" t="s">
-        <v>63</v>
-      </c>
-      <c r="C58">
-        <v>7</v>
-      </c>
-      <c r="D58">
-        <v>9</v>
-      </c>
-      <c r="E58">
-        <v>9</v>
-      </c>
-      <c r="F58">
-        <v>9</v>
-      </c>
-      <c r="G58">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59">
-        <v>5</v>
-      </c>
-      <c r="B59" t="s">
-        <v>64</v>
-      </c>
-      <c r="C59">
-        <v>10</v>
-      </c>
-      <c r="D59">
-        <v>8</v>
-      </c>
-      <c r="E59">
-        <v>9</v>
-      </c>
-      <c r="F59">
-        <v>9</v>
-      </c>
-      <c r="G59">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>5</v>
-      </c>
-      <c r="B60" t="s">
-        <v>65</v>
-      </c>
-      <c r="C60">
-        <v>9</v>
-      </c>
-      <c r="D60">
-        <v>9</v>
-      </c>
-      <c r="E60">
-        <v>10</v>
-      </c>
-      <c r="F60">
-        <v>10</v>
-      </c>
-      <c r="G60">
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61">
-        <v>5</v>
-      </c>
-      <c r="B61" t="s">
-        <v>66</v>
-      </c>
-      <c r="C61">
-        <v>10</v>
-      </c>
-      <c r="D61">
-        <v>9</v>
-      </c>
-      <c r="E61">
-        <v>10</v>
-      </c>
-      <c r="F61">
-        <v>11</v>
-      </c>
-      <c r="G61">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62">
-        <v>5</v>
-      </c>
-      <c r="B62" t="s">
-        <v>67</v>
-      </c>
-      <c r="C62">
-        <v>11</v>
-      </c>
-      <c r="D62">
-        <v>14</v>
-      </c>
-      <c r="E62">
-        <v>12</v>
-      </c>
-      <c r="F62">
-        <v>14</v>
-      </c>
-      <c r="G62">
-        <v>12.75</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63">
-        <v>5</v>
-      </c>
-      <c r="B63" t="s">
-        <v>68</v>
-      </c>
-      <c r="C63">
-        <v>10</v>
-      </c>
-      <c r="D63">
-        <v>9</v>
-      </c>
-      <c r="E63">
-        <v>11</v>
-      </c>
-      <c r="F63">
-        <v>11</v>
-      </c>
-      <c r="G63">
-        <v>10.25</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64">
-        <v>5</v>
-      </c>
-      <c r="B64" t="s">
-        <v>69</v>
-      </c>
-      <c r="C64">
-        <v>10</v>
-      </c>
-      <c r="D64">
-        <v>10</v>
-      </c>
-      <c r="E64">
-        <v>10</v>
-      </c>
-      <c r="F64">
-        <v>10</v>
-      </c>
-      <c r="G64">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65">
-        <v>6</v>
-      </c>
-      <c r="B65" t="s">
-        <v>70</v>
-      </c>
-      <c r="C65">
-        <v>9</v>
-      </c>
-      <c r="D65">
-        <v>9</v>
-      </c>
-      <c r="E65">
-        <v>9</v>
-      </c>
-      <c r="F65">
-        <v>10</v>
-      </c>
-      <c r="G65">
-        <v>9.25</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Validasi/Hasil_Pengujian_Map_1_128_avg_length.xlsx
+++ b/Excel/Validasi/Hasil_Pengujian_Map_1_128_avg_length.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEMHAS\TA_Python_Server\Excel\Validasi\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9968E71-DC3B-478B-B47F-8ED2D38AF7E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Waktu Pencarian" sheetId="1" r:id="rId1"/>
@@ -20,7 +14,7 @@
     <sheet name="Jumlah Close" sheetId="5" r:id="rId5"/>
     <sheet name="Jumlah Belok" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -195,8 +189,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -259,1540 +253,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="id-ID"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$B$2</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>A*</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>128</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Waktu Pencarian'!$C$2:$F$2</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>4.9379999999999997E-4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2.8850999999999998E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.8933499999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.12529689999999999</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4C9B-4881-8EED-80B5538409C7}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$B$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>BDS</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>128</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Waktu Pencarian'!$C$3:$F$3</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>2.7970000000000002E-4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.2294000000000001E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4.9227000000000003E-3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2.0550700000000002E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-4C9B-4881-8EED-80B5538409C7}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$B$4</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>BRC</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent3"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>128</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Waktu Pencarian'!$C$4:$F$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>4.5229999999999988E-4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2.020399999999999E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.6072300000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.18012449999999999</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-4C9B-4881-8EED-80B5538409C7}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$B$5</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>GL</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent4"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>128</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Waktu Pencarian'!$C$5:$F$5</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>4.0739999999999987E-4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2.2921E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.5739400000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.1123504</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-4C9B-4881-8EED-80B5538409C7}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$B$6</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>JPS</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent5"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>128</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Waktu Pencarian'!$C$6:$F$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>3.5849999999999999E-4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.0181000000000001E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3.5002000000000002E-3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.2126899999999999E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-4C9B-4881-8EED-80B5538409C7}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="5"/>
-          <c:order val="5"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$B$7</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>PPO</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent6"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>128</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Waktu Pencarian'!$C$7:$F$7</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>5.6109999999999992E-4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2.9761000000000002E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.9082100000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.1257644</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-4C9B-4881-8EED-80B5538409C7}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="6"/>
-          <c:order val="6"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$B$8</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>TPF</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="60000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>128</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Waktu Pencarian'!$C$8:$F$8</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>5.2979999999999998E-4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2.8898000000000001E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.7512699999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.1189119</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-4C9B-4881-8EED-80B5538409C7}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:hiLowLines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="75000"/>
-                  <a:lumOff val="25000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:hiLowLines>
-        <c:marker val="1"/>
-        <c:smooth val="0"/>
-        <c:axId val="693613583"/>
-        <c:axId val="693570863"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="693613583"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="id-ID"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="id-ID"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="693570863"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="693570863"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="id-ID"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="id-ID"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="693613583"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="id-ID"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="id-ID"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>34290</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>34290</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80C790E0-5C57-54A4-2B28-4435CFB00C3F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Red Orange">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1800,37 +267,37 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="505046"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
         <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="E84C22"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="FFBD47"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="B64926"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FF8427"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="CC9900"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="B22600"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="CC9900"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="666699"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1864,7 +331,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1899,10 +365,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2075,11 +540,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2102,7 +567,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2110,22 +575,22 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>4.9379999999999997E-4</v>
+        <v>0.0004671</v>
       </c>
       <c r="D2">
-        <v>2.8850999999999998E-3</v>
+        <v>0.0028731</v>
       </c>
       <c r="E2">
-        <v>1.8933499999999999E-2</v>
+        <v>0.018852</v>
       </c>
       <c r="F2">
-        <v>0.12529689999999999</v>
+        <v>0.1263417</v>
       </c>
       <c r="G2">
-        <v>3.6902325E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.037133475</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2133,22 +598,22 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>2.7970000000000002E-4</v>
+        <v>0.0003097</v>
       </c>
       <c r="D3">
-        <v>1.2294000000000001E-3</v>
+        <v>0.0012374</v>
       </c>
       <c r="E3">
-        <v>4.9227000000000003E-3</v>
+        <v>0.005019</v>
       </c>
       <c r="F3">
-        <v>2.0550700000000002E-2</v>
+        <v>0.0212998</v>
       </c>
       <c r="G3">
-        <v>6.7456250000000008E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.006966475</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>1</v>
       </c>
@@ -2156,22 +621,22 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>4.5229999999999988E-4</v>
+        <v>0.0004344999999999999</v>
       </c>
       <c r="D4">
-        <v>2.020399999999999E-3</v>
+        <v>0.002075</v>
       </c>
       <c r="E4">
-        <v>1.6072300000000001E-2</v>
+        <v>0.0164053</v>
       </c>
       <c r="F4">
-        <v>0.18012449999999999</v>
+        <v>0.1825708</v>
       </c>
       <c r="G4">
-        <v>4.9667374999999993E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0503714</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>1</v>
       </c>
@@ -2179,22 +644,22 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>4.0739999999999987E-4</v>
+        <v>0.0003937</v>
       </c>
       <c r="D5">
-        <v>2.2921E-3</v>
+        <v>0.0023428</v>
       </c>
       <c r="E5">
-        <v>1.5739400000000001E-2</v>
+        <v>0.0158304</v>
       </c>
       <c r="F5">
-        <v>0.1123504</v>
+        <v>0.1102341</v>
       </c>
       <c r="G5">
-        <v>3.2697324999999999E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.03220025</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>1</v>
       </c>
@@ -2202,22 +667,22 @@
         <v>11</v>
       </c>
       <c r="C6">
-        <v>3.5849999999999999E-4</v>
+        <v>0.0003599000000000001</v>
       </c>
       <c r="D6">
-        <v>1.0181000000000001E-3</v>
+        <v>0.0010078</v>
       </c>
       <c r="E6">
-        <v>3.5002000000000002E-3</v>
+        <v>0.003384</v>
       </c>
       <c r="F6">
-        <v>1.2126899999999999E-2</v>
+        <v>0.0123414</v>
       </c>
       <c r="G6">
-        <v>4.250925E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.004273275</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -2225,22 +690,22 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>5.6109999999999992E-4</v>
+        <v>0.0005657999999999999</v>
       </c>
       <c r="D7">
-        <v>2.9761000000000002E-3</v>
+        <v>0.0029561</v>
       </c>
       <c r="E7">
-        <v>1.9082100000000001E-2</v>
+        <v>0.0190359</v>
       </c>
       <c r="F7">
-        <v>0.1257644</v>
+        <v>0.1278414</v>
       </c>
       <c r="G7">
-        <v>3.7095925000000002E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0375998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>1</v>
       </c>
@@ -2248,22 +713,22 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>5.2979999999999998E-4</v>
+        <v>0.0005416999999999999</v>
       </c>
       <c r="D8">
-        <v>2.8898000000000001E-3</v>
+        <v>0.0028076</v>
       </c>
       <c r="E8">
-        <v>1.7512699999999999E-2</v>
+        <v>0.0174677</v>
       </c>
       <c r="F8">
-        <v>0.1189119</v>
+        <v>0.1210942</v>
       </c>
       <c r="G8">
-        <v>3.4961049999999987E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0354778</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>2</v>
       </c>
@@ -2271,22 +736,22 @@
         <v>14</v>
       </c>
       <c r="C9">
-        <v>4.6579999999999999E-4</v>
+        <v>0.000453</v>
       </c>
       <c r="D9">
-        <v>1.7442E-3</v>
+        <v>0.0017509</v>
       </c>
       <c r="E9">
-        <v>8.5352000000000015E-3</v>
+        <v>0.008597499999999999</v>
       </c>
       <c r="F9">
-        <v>5.1208799999999999E-2</v>
+        <v>0.05295890000000001</v>
       </c>
       <c r="G9">
-        <v>1.5488500000000001E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.015940075</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>2</v>
       </c>
@@ -2294,22 +759,22 @@
         <v>15</v>
       </c>
       <c r="C10">
-        <v>3.4220000000000002E-4</v>
+        <v>0.0003246</v>
       </c>
       <c r="D10">
-        <v>1.3734000000000001E-3</v>
+        <v>0.001424</v>
       </c>
       <c r="E10">
-        <v>5.916600000000001E-3</v>
+        <v>0.0059972</v>
       </c>
       <c r="F10">
-        <v>2.4535499999999998E-2</v>
+        <v>0.0254855</v>
       </c>
       <c r="G10">
-        <v>8.0419250000000001E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.008307825000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>2</v>
       </c>
@@ -2317,22 +782,22 @@
         <v>16</v>
       </c>
       <c r="C11">
-        <v>3.1639999999999999E-4</v>
+        <v>0.0003357</v>
       </c>
       <c r="D11">
-        <v>1.3039E-3</v>
+        <v>0.0013621</v>
       </c>
       <c r="E11">
-        <v>5.0924999999999998E-3</v>
+        <v>0.0052069</v>
       </c>
       <c r="F11">
-        <v>2.12602E-2</v>
+        <v>0.0219035</v>
       </c>
       <c r="G11">
-        <v>6.9932499999999986E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.00720205</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>2</v>
       </c>
@@ -2340,22 +805,22 @@
         <v>17</v>
       </c>
       <c r="C12">
-        <v>3.4200000000000002E-4</v>
+        <v>0.0003564</v>
       </c>
       <c r="D12">
-        <v>1.4683000000000001E-3</v>
+        <v>0.0014683</v>
       </c>
       <c r="E12">
-        <v>5.4098999999999996E-3</v>
+        <v>0.0054437</v>
       </c>
       <c r="F12">
-        <v>2.1597700000000001E-2</v>
+        <v>0.0223129</v>
       </c>
       <c r="G12">
-        <v>7.204475000000001E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.007395325</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>2</v>
       </c>
@@ -2363,22 +828,22 @@
         <v>18</v>
       </c>
       <c r="C13">
-        <v>4.6440000000000001E-4</v>
+        <v>0.0005072</v>
       </c>
       <c r="D13">
-        <v>2.2074E-3</v>
+        <v>0.0021937</v>
       </c>
       <c r="E13">
-        <v>1.6632299999999999E-2</v>
+        <v>0.0167864</v>
       </c>
       <c r="F13">
-        <v>0.17948030000000001</v>
+        <v>0.1828421</v>
       </c>
       <c r="G13">
-        <v>4.9696099999999993E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.05058235</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>2</v>
       </c>
@@ -2386,22 +851,22 @@
         <v>19</v>
       </c>
       <c r="C14">
-        <v>4.9330000000000001E-4</v>
+        <v>0.0005087</v>
       </c>
       <c r="D14">
-        <v>2.2282000000000001E-3</v>
+        <v>0.0021151</v>
       </c>
       <c r="E14">
-        <v>1.61285E-2</v>
+        <v>0.0163585</v>
       </c>
       <c r="F14">
-        <v>0.17113900000000001</v>
+        <v>0.1723085</v>
       </c>
       <c r="G14">
-        <v>4.7497249999999998E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.04782270000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>2</v>
       </c>
@@ -2409,22 +874,22 @@
         <v>20</v>
       </c>
       <c r="C15">
-        <v>5.107E-4</v>
+        <v>0.0005158999999999999</v>
       </c>
       <c r="D15">
-        <v>2.7369999999999998E-3</v>
+        <v>0.002686</v>
       </c>
       <c r="E15">
-        <v>2.0884699999999999E-2</v>
+        <v>0.020967</v>
       </c>
       <c r="F15">
-        <v>0.21187819999999999</v>
+        <v>0.2153625</v>
       </c>
       <c r="G15">
-        <v>5.9002649999999997E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.05988284999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>2</v>
       </c>
@@ -2432,22 +897,22 @@
         <v>21</v>
       </c>
       <c r="C16">
-        <v>4.5580000000000002E-4</v>
+        <v>0.0004625000000000001</v>
       </c>
       <c r="D16">
-        <v>2.4453000000000001E-3</v>
+        <v>0.0024338</v>
       </c>
       <c r="E16">
-        <v>1.6251600000000001E-2</v>
+        <v>0.0160007</v>
       </c>
       <c r="F16">
-        <v>0.11184620000000001</v>
+        <v>0.1113366</v>
       </c>
       <c r="G16">
-        <v>3.2749725E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0325584</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>2</v>
       </c>
@@ -2455,22 +920,22 @@
         <v>22</v>
       </c>
       <c r="C17">
-        <v>5.5910000000000009E-4</v>
+        <v>0.0005591999999999999</v>
       </c>
       <c r="D17">
-        <v>3.4920000000000012E-3</v>
+        <v>0.0034476</v>
       </c>
       <c r="E17">
-        <v>1.6085700000000001E-2</v>
+        <v>0.0157666</v>
       </c>
       <c r="F17">
-        <v>0.106137</v>
+        <v>0.1055624</v>
       </c>
       <c r="G17">
-        <v>3.1568449999999998E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.03133395</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>2</v>
       </c>
@@ -2478,22 +943,22 @@
         <v>23</v>
       </c>
       <c r="C18">
-        <v>3.7500000000000001E-4</v>
+        <v>0.0003774000000000001</v>
       </c>
       <c r="D18">
-        <v>9.4190000000000007E-4</v>
+        <v>0.0009888</v>
       </c>
       <c r="E18">
-        <v>2.9147999999999999E-3</v>
+        <v>0.002965</v>
       </c>
       <c r="F18">
-        <v>1.06172E-2</v>
+        <v>0.011029</v>
       </c>
       <c r="G18">
-        <v>3.712225E-3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.00384005</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>2</v>
       </c>
@@ -2501,22 +966,22 @@
         <v>24</v>
       </c>
       <c r="C19">
-        <v>3.212E-4</v>
+        <v>0.0003128</v>
       </c>
       <c r="D19">
-        <v>9.323999999999999E-4</v>
+        <v>0.0009300000000000001</v>
       </c>
       <c r="E19">
-        <v>3.1335E-3</v>
+        <v>0.0032116</v>
       </c>
       <c r="F19">
-        <v>1.15268E-2</v>
+        <v>0.0118351</v>
       </c>
       <c r="G19">
-        <v>3.9784750000000004E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.004072375</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>2</v>
       </c>
@@ -2524,22 +989,22 @@
         <v>25</v>
       </c>
       <c r="C20">
-        <v>4.7649999999999993E-4</v>
+        <v>0.0003769</v>
       </c>
       <c r="D20">
-        <v>1.1236E-3</v>
+        <v>0.001184</v>
       </c>
       <c r="E20">
-        <v>3.5431999999999998E-3</v>
+        <v>0.0035621</v>
       </c>
       <c r="F20">
-        <v>1.3403200000000001E-2</v>
+        <v>0.0132511</v>
       </c>
       <c r="G20">
-        <v>4.6366250000000001E-3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.004593524999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>2</v>
       </c>
@@ -2547,22 +1012,22 @@
         <v>26</v>
       </c>
       <c r="C21">
-        <v>3.926E-4</v>
+        <v>0.0004033</v>
       </c>
       <c r="D21">
-        <v>1.0494E-3</v>
+        <v>0.0010434</v>
       </c>
       <c r="E21">
-        <v>3.3776000000000001E-3</v>
+        <v>0.0034384</v>
       </c>
       <c r="F21">
-        <v>1.1986200000000001E-2</v>
+        <v>0.0120888</v>
       </c>
       <c r="G21">
-        <v>4.2014499999999998E-3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.004243475</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>2</v>
       </c>
@@ -2570,22 +1035,22 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>5.6949999999999991E-4</v>
+        <v>0.0005602000000000001</v>
       </c>
       <c r="D22">
-        <v>2.9991000000000002E-3</v>
+        <v>0.0028968</v>
       </c>
       <c r="E22">
-        <v>1.7790400000000001E-2</v>
+        <v>0.017527</v>
       </c>
       <c r="F22">
-        <v>0.1218943</v>
+        <v>0.1224394</v>
       </c>
       <c r="G22">
-        <v>3.5813325000000007E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.03585585</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>3</v>
       </c>
@@ -2593,22 +1058,22 @@
         <v>28</v>
       </c>
       <c r="C23">
-        <v>4.9589999999999996E-4</v>
+        <v>0.0005103000000000001</v>
       </c>
       <c r="D23">
-        <v>1.7639999999999999E-3</v>
+        <v>0.0018861</v>
       </c>
       <c r="E23">
-        <v>8.8319000000000002E-3</v>
+        <v>0.008874499999999999</v>
       </c>
       <c r="F23">
-        <v>5.2588099999999992E-2</v>
+        <v>0.05422140000000001</v>
       </c>
       <c r="G23">
-        <v>1.5919974999999999E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.016373075</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>3</v>
       </c>
@@ -2616,22 +1081,22 @@
         <v>29</v>
       </c>
       <c r="C24">
-        <v>4.3619999999999998E-4</v>
+        <v>0.0004831</v>
       </c>
       <c r="D24">
-        <v>1.9517E-3</v>
+        <v>0.001943</v>
       </c>
       <c r="E24">
-        <v>9.2374000000000015E-3</v>
+        <v>0.009243099999999999</v>
       </c>
       <c r="F24">
-        <v>5.3368100000000009E-2</v>
+        <v>0.0550246</v>
       </c>
       <c r="G24">
-        <v>1.6248350000000002E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.01667345</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>3</v>
       </c>
@@ -2639,22 +1104,22 @@
         <v>30</v>
       </c>
       <c r="C25">
-        <v>5.1239999999999999E-4</v>
+        <v>0.0005296999999999999</v>
       </c>
       <c r="D25">
-        <v>2.7553999999999999E-3</v>
+        <v>0.0028292</v>
       </c>
       <c r="E25">
-        <v>1.35646E-2</v>
+        <v>0.0138794</v>
       </c>
       <c r="F25">
-        <v>8.7090799999999996E-2</v>
+        <v>0.0910108</v>
       </c>
       <c r="G25">
-        <v>2.5980799999999998E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.027062275</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>3</v>
       </c>
@@ -2662,22 +1127,22 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>3.5090000000000002E-4</v>
+        <v>0.0004126999999999999</v>
       </c>
       <c r="D26">
-        <v>1.4966000000000001E-3</v>
+        <v>0.0016067</v>
       </c>
       <c r="E26">
-        <v>6.0125999999999999E-3</v>
+        <v>0.0061584</v>
       </c>
       <c r="F26">
-        <v>2.53899E-2</v>
+        <v>0.026432</v>
       </c>
       <c r="G26">
-        <v>8.3125000000000004E-3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.008652449999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>3</v>
       </c>
@@ -2685,22 +1150,22 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>3.7240000000000011E-4</v>
+        <v>0.0003757</v>
       </c>
       <c r="D27">
-        <v>1.6012999999999999E-3</v>
+        <v>0.0017975</v>
       </c>
       <c r="E27">
-        <v>6.2833999999999997E-3</v>
+        <v>0.006503699999999999</v>
       </c>
       <c r="F27">
-        <v>2.7113999999999999E-2</v>
+        <v>0.0268676</v>
       </c>
       <c r="G27">
-        <v>8.8427750000000006E-3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.008886125</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>3</v>
       </c>
@@ -2708,22 +1173,22 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>3.9300000000000001E-4</v>
+        <v>0.0003857</v>
       </c>
       <c r="D28">
-        <v>1.555E-3</v>
+        <v>0.0016218</v>
       </c>
       <c r="E28">
-        <v>5.8628999999999999E-3</v>
+        <v>0.005859099999999999</v>
       </c>
       <c r="F28">
-        <v>2.26804E-2</v>
+        <v>0.023247</v>
       </c>
       <c r="G28">
-        <v>7.6228249999999997E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0077784</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>3</v>
       </c>
@@ -2731,22 +1196,22 @@
         <v>34</v>
       </c>
       <c r="C29">
-        <v>5.3459999999999988E-4</v>
+        <v>0.0005701</v>
       </c>
       <c r="D29">
-        <v>2.2845999999999999E-3</v>
+        <v>0.0023477</v>
       </c>
       <c r="E29">
-        <v>1.6494499999999999E-2</v>
+        <v>0.0166029</v>
       </c>
       <c r="F29">
-        <v>0.17120179999999999</v>
+        <v>0.1731427</v>
       </c>
       <c r="G29">
-        <v>4.7628875000000001E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.04816585</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>3</v>
       </c>
@@ -2754,22 +1219,22 @@
         <v>35</v>
       </c>
       <c r="C30">
-        <v>5.5150000000000002E-4</v>
+        <v>0.0005375</v>
       </c>
       <c r="D30">
-        <v>2.8059000000000001E-3</v>
+        <v>0.0028914</v>
       </c>
       <c r="E30">
-        <v>2.11451E-2</v>
+        <v>0.0214981</v>
       </c>
       <c r="F30">
-        <v>0.21209259999999999</v>
+        <v>0.2163032</v>
       </c>
       <c r="G30">
-        <v>5.9148775000000001E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.06030754999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>3</v>
       </c>
@@ -2777,22 +1242,22 @@
         <v>36</v>
       </c>
       <c r="C31">
-        <v>5.5210000000000003E-4</v>
+        <v>0.0005589999999999999</v>
       </c>
       <c r="D31">
-        <v>2.9053E-3</v>
+        <v>0.0029506</v>
       </c>
       <c r="E31">
-        <v>2.1082099999999999E-2</v>
+        <v>0.0213484</v>
       </c>
       <c r="F31">
-        <v>0.20836560000000001</v>
+        <v>0.2143728</v>
       </c>
       <c r="G31">
-        <v>5.8226274999999987E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.05980769999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>3</v>
       </c>
@@ -2800,22 +1265,22 @@
         <v>37</v>
       </c>
       <c r="C32">
-        <v>5.824999999999999E-4</v>
+        <v>0.0006119999999999999</v>
       </c>
       <c r="D32">
-        <v>3.4924999999999999E-3</v>
+        <v>0.0035919</v>
       </c>
       <c r="E32">
-        <v>1.6322199999999999E-2</v>
+        <v>0.0164576</v>
       </c>
       <c r="F32">
-        <v>0.106556</v>
+        <v>0.1075917</v>
       </c>
       <c r="G32">
-        <v>3.1738299999999997E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0320633</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>3</v>
       </c>
@@ -2823,22 +1288,22 @@
         <v>38</v>
       </c>
       <c r="C33">
-        <v>4.2739999999999998E-4</v>
+        <v>0.0004611</v>
       </c>
       <c r="D33">
-        <v>1.1126E-3</v>
+        <v>0.0011149</v>
       </c>
       <c r="E33">
-        <v>3.1419999999999998E-3</v>
+        <v>0.0032558</v>
       </c>
       <c r="F33">
-        <v>1.14371E-2</v>
+        <v>0.0114823</v>
       </c>
       <c r="G33">
-        <v>4.0297750000000002E-3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.004078525</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>3</v>
       </c>
@@ -2846,22 +1311,22 @@
         <v>39</v>
       </c>
       <c r="C34">
-        <v>2.8130000000000012E-4</v>
+        <v>0.0003025</v>
       </c>
       <c r="D34">
-        <v>1.0296999999999999E-3</v>
+        <v>0.0014499</v>
       </c>
       <c r="E34">
-        <v>2.9332E-3</v>
+        <v>0.0029033</v>
       </c>
       <c r="F34">
-        <v>1.1029300000000001E-2</v>
+        <v>0.0114197</v>
       </c>
       <c r="G34">
-        <v>3.8183750000000002E-3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.00401885</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>3</v>
       </c>
@@ -2869,22 +1334,22 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>4.4049999999999997E-4</v>
+        <v>0.0004103</v>
       </c>
       <c r="D35">
-        <v>1.0322E-3</v>
+        <v>0.0010353</v>
       </c>
       <c r="E35">
-        <v>2.9897999999999999E-3</v>
+        <v>0.0029478</v>
       </c>
       <c r="F35">
-        <v>1.09438E-2</v>
+        <v>0.0111202</v>
       </c>
       <c r="G35">
-        <v>3.851574999999999E-3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0038784</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>3</v>
       </c>
@@ -2892,22 +1357,22 @@
         <v>41</v>
       </c>
       <c r="C36">
-        <v>3.3839999999999999E-4</v>
+        <v>0.0003829</v>
       </c>
       <c r="D36">
-        <v>9.8380000000000017E-4</v>
+        <v>0.0009647</v>
       </c>
       <c r="E36">
-        <v>3.2701000000000002E-3</v>
+        <v>0.0031609</v>
       </c>
       <c r="F36">
-        <v>1.19174E-2</v>
+        <v>0.0119732</v>
       </c>
       <c r="G36">
-        <v>4.1274249999999997E-3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.004120425</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>3</v>
       </c>
@@ -2915,22 +1380,22 @@
         <v>42</v>
       </c>
       <c r="C37">
-        <v>3.5070000000000001E-4</v>
+        <v>0.0003242</v>
       </c>
       <c r="D37">
-        <v>1.0594000000000001E-3</v>
+        <v>0.001045</v>
       </c>
       <c r="E37">
-        <v>2.8119999999999998E-3</v>
+        <v>0.0029875</v>
       </c>
       <c r="F37">
-        <v>1.2728700000000001E-2</v>
+        <v>0.012668</v>
       </c>
       <c r="G37">
-        <v>4.2376999999999996E-3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.004256175000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>3</v>
       </c>
@@ -2938,22 +1403,22 @@
         <v>43</v>
       </c>
       <c r="C38">
-        <v>3.882E-4</v>
+        <v>0.0004173</v>
       </c>
       <c r="D38">
-        <v>1.1693000000000001E-3</v>
+        <v>0.0011838</v>
       </c>
       <c r="E38">
-        <v>3.6083E-3</v>
+        <v>0.003676099999999999</v>
       </c>
       <c r="F38">
-        <v>1.34076E-2</v>
+        <v>0.0136793</v>
       </c>
       <c r="G38">
-        <v>4.6433500000000001E-3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.004739125</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>4</v>
       </c>
@@ -2961,22 +1426,22 @@
         <v>44</v>
       </c>
       <c r="C39">
-        <v>5.1539999999999995E-4</v>
+        <v>0.0005191000000000001</v>
       </c>
       <c r="D39">
-        <v>2.0387000000000001E-3</v>
+        <v>0.0020792</v>
       </c>
       <c r="E39">
-        <v>9.5207999999999994E-3</v>
+        <v>0.009789599999999999</v>
       </c>
       <c r="F39">
-        <v>5.3929099999999987E-2</v>
+        <v>0.055882</v>
       </c>
       <c r="G39">
-        <v>1.6500999999999998E-2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.017067475</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>4</v>
       </c>
@@ -2984,22 +1449,22 @@
         <v>45</v>
       </c>
       <c r="C40">
-        <v>5.6050000000000002E-4</v>
+        <v>0.0005931000000000001</v>
       </c>
       <c r="D40">
-        <v>2.7542000000000001E-3</v>
+        <v>0.0028551</v>
       </c>
       <c r="E40">
-        <v>1.3998E-2</v>
+        <v>0.0142147</v>
       </c>
       <c r="F40">
-        <v>8.8623900000000005E-2</v>
+        <v>0.0914111</v>
       </c>
       <c r="G40">
-        <v>2.6484150000000001E-2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0272685</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>4</v>
       </c>
@@ -3007,22 +1472,22 @@
         <v>46</v>
       </c>
       <c r="C41">
-        <v>6.2229999999999989E-4</v>
+        <v>0.0005943000000000001</v>
       </c>
       <c r="D41">
-        <v>3.0252999999999999E-3</v>
+        <v>0.0030247</v>
       </c>
       <c r="E41">
-        <v>1.47192E-2</v>
+        <v>0.0148698</v>
       </c>
       <c r="F41">
-        <v>8.6871300000000012E-2</v>
+        <v>0.09069920000000001</v>
       </c>
       <c r="G41">
-        <v>2.6309525E-2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.027297</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>4</v>
       </c>
@@ -3030,22 +1495,22 @@
         <v>47</v>
       </c>
       <c r="C42">
-        <v>4.035000000000001E-4</v>
+        <v>0.0004463</v>
       </c>
       <c r="D42">
-        <v>1.6724000000000001E-3</v>
+        <v>0.0017463</v>
       </c>
       <c r="E42">
-        <v>6.5813E-3</v>
+        <v>0.0067222</v>
       </c>
       <c r="F42">
-        <v>2.6708699999999998E-2</v>
+        <v>0.0281102</v>
       </c>
       <c r="G42">
-        <v>8.8414750000000014E-3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.009256250000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>4</v>
       </c>
@@ -3053,22 +1518,22 @@
         <v>48</v>
       </c>
       <c r="C43">
-        <v>5.9009999999999998E-4</v>
+        <v>0.0006337</v>
       </c>
       <c r="D43">
-        <v>2.9277999999999999E-3</v>
+        <v>0.0029755</v>
       </c>
       <c r="E43">
-        <v>2.1913200000000001E-2</v>
+        <v>0.0220362</v>
       </c>
       <c r="F43">
-        <v>0.2078333</v>
+        <v>0.2139558</v>
       </c>
       <c r="G43">
-        <v>5.831610000000001E-2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0599003</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>4</v>
       </c>
@@ -3076,22 +1541,22 @@
         <v>49</v>
       </c>
       <c r="C44">
-        <v>4.6260000000000002E-4</v>
+        <v>0.0004681</v>
       </c>
       <c r="D44">
-        <v>1.1374E-3</v>
+        <v>0.0014037</v>
       </c>
       <c r="E44">
-        <v>3.2699000000000001E-3</v>
+        <v>0.003271</v>
       </c>
       <c r="F44">
-        <v>1.1563199999999999E-2</v>
+        <v>0.011631</v>
       </c>
       <c r="G44">
-        <v>4.1082749999999998E-3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.00419345</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>4</v>
       </c>
@@ -3099,22 +1564,22 @@
         <v>50</v>
       </c>
       <c r="C45">
-        <v>3.6360000000000011E-4</v>
+        <v>0.0004222</v>
       </c>
       <c r="D45">
-        <v>1.4534000000000001E-3</v>
+        <v>0.0013458</v>
       </c>
       <c r="E45">
-        <v>3.6001000000000002E-3</v>
+        <v>0.0036118</v>
       </c>
       <c r="F45">
-        <v>1.23131E-2</v>
+        <v>0.0125145</v>
       </c>
       <c r="G45">
-        <v>4.4325500000000004E-3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.004473575</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>4</v>
       </c>
@@ -3122,22 +1587,22 @@
         <v>51</v>
       </c>
       <c r="C46">
-        <v>3.191E-4</v>
+        <v>0.000358</v>
       </c>
       <c r="D46">
-        <v>1.1915999999999999E-3</v>
+        <v>0.0015141</v>
       </c>
       <c r="E46">
-        <v>2.9635999999999998E-3</v>
+        <v>0.0030484</v>
       </c>
       <c r="F46">
-        <v>1.1420700000000001E-2</v>
+        <v>0.0114328</v>
       </c>
       <c r="G46">
-        <v>3.9737499999999999E-3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.004088325</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>4</v>
       </c>
@@ -3145,22 +1610,22 @@
         <v>52</v>
       </c>
       <c r="C47">
-        <v>3.9239999999999989E-4</v>
+        <v>0.0003885</v>
       </c>
       <c r="D47">
-        <v>1.1172000000000001E-3</v>
+        <v>0.0011271</v>
       </c>
       <c r="E47">
-        <v>3.7997999999999999E-3</v>
+        <v>0.0030063</v>
       </c>
       <c r="F47">
-        <v>1.23894E-2</v>
+        <v>0.0130265</v>
       </c>
       <c r="G47">
-        <v>4.4247000000000002E-3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0043871</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>5</v>
       </c>
@@ -3168,22 +1633,22 @@
         <v>53</v>
       </c>
       <c r="C48">
-        <v>6.1689999999999998E-4</v>
+        <v>0.0006716999999999999</v>
       </c>
       <c r="D48">
-        <v>3.0723999999999999E-3</v>
+        <v>0.003192700000000001</v>
       </c>
       <c r="E48">
-        <v>1.49134E-2</v>
+        <v>0.0151282</v>
       </c>
       <c r="F48">
-        <v>8.7208699999999986E-2</v>
+        <v>0.09127890000000001</v>
       </c>
       <c r="G48">
-        <v>2.645285E-2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.027567875</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>5</v>
       </c>
@@ -3191,33 +1656,32 @@
         <v>54</v>
       </c>
       <c r="C49">
-        <v>4.3169999999999998E-4</v>
+        <v>0.0004466</v>
       </c>
       <c r="D49">
-        <v>1.5219999999999999E-3</v>
+        <v>0.0014707</v>
       </c>
       <c r="E49">
-        <v>3.754700000000001E-3</v>
+        <v>0.003644700000000001</v>
       </c>
       <c r="F49">
-        <v>1.2436300000000001E-2</v>
+        <v>0.0128153</v>
       </c>
       <c r="G49">
-        <v>4.5361749999999999E-3</v>
+        <v>0.004594325</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3240,7 +1704,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
@@ -3263,7 +1727,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1</v>
       </c>
@@ -3286,7 +1750,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>1</v>
       </c>
@@ -3309,7 +1773,7 @@
         <v>82.75</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>1</v>
       </c>
@@ -3332,7 +1796,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>1</v>
       </c>
@@ -3355,7 +1819,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -3378,7 +1842,7 @@
         <v>10.25</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>1</v>
       </c>
@@ -3401,7 +1865,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>2</v>
       </c>
@@ -3424,7 +1888,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>2</v>
       </c>
@@ -3447,7 +1911,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>2</v>
       </c>
@@ -3470,7 +1934,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>2</v>
       </c>
@@ -3493,7 +1957,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>2</v>
       </c>
@@ -3516,7 +1980,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>2</v>
       </c>
@@ -3539,7 +2003,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>2</v>
       </c>
@@ -3562,7 +2026,7 @@
         <v>88.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>2</v>
       </c>
@@ -3585,7 +2049,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>2</v>
       </c>
@@ -3608,7 +2072,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>2</v>
       </c>
@@ -3631,7 +2095,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>2</v>
       </c>
@@ -3654,7 +2118,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>2</v>
       </c>
@@ -3677,7 +2141,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>2</v>
       </c>
@@ -3700,7 +2164,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>2</v>
       </c>
@@ -3723,7 +2187,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>3</v>
       </c>
@@ -3746,7 +2210,7 @@
         <v>11.25</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>3</v>
       </c>
@@ -3769,7 +2233,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>3</v>
       </c>
@@ -3792,7 +2256,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>3</v>
       </c>
@@ -3815,7 +2279,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>3</v>
       </c>
@@ -3838,7 +2302,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>3</v>
       </c>
@@ -3861,7 +2325,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>3</v>
       </c>
@@ -3884,7 +2348,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>3</v>
       </c>
@@ -3907,7 +2371,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>3</v>
       </c>
@@ -3930,7 +2394,7 @@
         <v>88.5</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>3</v>
       </c>
@@ -3953,7 +2417,7 @@
         <v>10.75</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>3</v>
       </c>
@@ -3976,7 +2440,7 @@
         <v>19.25</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>3</v>
       </c>
@@ -3999,7 +2463,7 @@
         <v>19.25</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>3</v>
       </c>
@@ -4022,7 +2486,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>3</v>
       </c>
@@ -4045,7 +2509,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>3</v>
       </c>
@@ -4068,7 +2532,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>3</v>
       </c>
@@ -4091,7 +2555,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>4</v>
       </c>
@@ -4114,7 +2578,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>4</v>
       </c>
@@ -4137,7 +2601,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>4</v>
       </c>
@@ -4160,7 +2624,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>4</v>
       </c>
@@ -4183,7 +2647,7 @@
         <v>11.75</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>4</v>
       </c>
@@ -4206,7 +2670,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>4</v>
       </c>
@@ -4229,7 +2693,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>4</v>
       </c>
@@ -4252,7 +2716,7 @@
         <v>19.25</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>4</v>
       </c>
@@ -4275,7 +2739,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>4</v>
       </c>
@@ -4298,7 +2762,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>5</v>
       </c>
@@ -4321,7 +2785,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>5</v>
       </c>
@@ -4350,11 +2814,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4377,7 +2841,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
@@ -4388,19 +2852,19 @@
         <v>25.55634918610405</v>
       </c>
       <c r="D2">
-        <v>51.698484809834987</v>
+        <v>51.69848480983499</v>
       </c>
       <c r="E2">
         <v>103.9827560572969</v>
       </c>
       <c r="F2">
-        <v>208.55129855222069</v>
+        <v>208.5512985522207</v>
       </c>
       <c r="G2">
-        <v>97.447222151364159</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>97.44722215136416</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1</v>
       </c>
@@ -4408,10 +2872,10 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>26.384776310850231</v>
+        <v>26.38477631085023</v>
       </c>
       <c r="D3">
-        <v>52.526911934581193</v>
+        <v>52.52691193458119</v>
       </c>
       <c r="E3">
         <v>104.8111831820431</v>
@@ -4420,10 +2884,10 @@
         <v>209.3797256769669</v>
       </c>
       <c r="G3">
-        <v>98.275649276110343</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>98.27564927611034</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>1</v>
       </c>
@@ -4431,22 +2895,22 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>26.970562748477139</v>
+        <v>26.97056274847714</v>
       </c>
       <c r="D4">
-        <v>52.526911934581193</v>
+        <v>52.52691193458119</v>
       </c>
       <c r="E4">
-        <v>106.46803743153551</v>
+        <v>106.4680374315355</v>
       </c>
       <c r="F4">
-        <v>214.35028842544401</v>
+        <v>214.350288425444</v>
       </c>
       <c r="G4">
-        <v>100.07895013500951</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>100.0789501350095</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>1</v>
       </c>
@@ -4457,19 +2921,19 @@
         <v>25.55634918610405</v>
       </c>
       <c r="D5">
-        <v>51.698484809834987</v>
+        <v>51.69848480983499</v>
       </c>
       <c r="E5">
         <v>103.9827560572969</v>
       </c>
       <c r="F5">
-        <v>208.55129855222069</v>
+        <v>208.5512985522207</v>
       </c>
       <c r="G5">
-        <v>97.447222151364159</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>97.44722215136416</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>1</v>
       </c>
@@ -4480,19 +2944,19 @@
         <v>25.55634918610405</v>
       </c>
       <c r="D6">
-        <v>51.698484809834987</v>
+        <v>51.69848480983499</v>
       </c>
       <c r="E6">
         <v>103.9827560572969</v>
       </c>
       <c r="F6">
-        <v>208.55129855222069</v>
+        <v>208.5512985522207</v>
       </c>
       <c r="G6">
-        <v>97.447222151364144</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>97.44722215136414</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -4500,10 +2964,10 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>24.883627011906739</v>
+        <v>24.88362701190674</v>
       </c>
       <c r="D7">
-        <v>49.972647762797628</v>
+        <v>49.97264776279763</v>
       </c>
       <c r="E7">
         <v>100.6259579416699</v>
@@ -4512,10 +2976,10 @@
         <v>201.6665280368868</v>
       </c>
       <c r="G7">
-        <v>94.287190188315265</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>94.28719018831526</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>1</v>
       </c>
@@ -4526,19 +2990,19 @@
         <v>25.55634918610405</v>
       </c>
       <c r="D8">
-        <v>51.698484809834987</v>
+        <v>51.69848480983499</v>
       </c>
       <c r="E8">
         <v>103.9827560572969</v>
       </c>
       <c r="F8">
-        <v>208.55129855222069</v>
+        <v>208.5512985522207</v>
       </c>
       <c r="G8">
-        <v>97.447222151364159</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+        <v>97.44722215136416</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>2</v>
       </c>
@@ -4549,19 +3013,19 @@
         <v>25.55634918610405</v>
       </c>
       <c r="D9">
-        <v>53.355339059327378</v>
+        <v>53.35533905932738</v>
       </c>
       <c r="E9">
-        <v>107.29646455628171</v>
+        <v>107.2964645562817</v>
       </c>
       <c r="F9">
-        <v>215.17871555019019</v>
+        <v>215.1787155501902</v>
       </c>
       <c r="G9">
         <v>100.3467170879758</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>2</v>
       </c>
@@ -4578,13 +3042,13 @@
         <v>109.4974746830583</v>
       </c>
       <c r="F10">
-        <v>218.75230867899739</v>
+        <v>218.7523086789974</v>
       </c>
       <c r="G10">
         <v>102.6690475583121</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>2</v>
       </c>
@@ -4595,19 +3059,19 @@
         <v>24.65008380450606</v>
       </c>
       <c r="D11">
-        <v>49.275151345830253</v>
+        <v>49.27515134583025</v>
       </c>
       <c r="E11">
-        <v>98.568492671203913</v>
+        <v>98.56849267120391</v>
       </c>
       <c r="F11">
-        <v>197.61193860700311</v>
+        <v>197.6119386070031</v>
       </c>
       <c r="G11">
-        <v>92.526416607135829</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+        <v>92.52641660713583</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>2</v>
       </c>
@@ -4615,10 +3079,10 @@
         <v>17</v>
       </c>
       <c r="C12">
-        <v>26.384776310850231</v>
+        <v>26.38477631085023</v>
       </c>
       <c r="D12">
-        <v>51.698484809834987</v>
+        <v>51.69848480983499</v>
       </c>
       <c r="E12">
         <v>104.8111831820431</v>
@@ -4627,10 +3091,10 @@
         <v>209.3797256769669</v>
       </c>
       <c r="G12">
-        <v>98.068542494923804</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+        <v>98.0685424949238</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>2</v>
       </c>
@@ -4638,22 +3102,22 @@
         <v>18</v>
       </c>
       <c r="C13">
-        <v>25.896819140124329</v>
+        <v>25.89681914012433</v>
       </c>
       <c r="D13">
-        <v>50.219756464235182</v>
+        <v>50.21975646423518</v>
       </c>
       <c r="E13">
         <v>101.5994483836505</v>
       </c>
       <c r="F13">
-        <v>204.51616349626769</v>
+        <v>204.5161634962677</v>
       </c>
       <c r="G13">
-        <v>95.558046871069408</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+        <v>95.55804687106941</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>2</v>
       </c>
@@ -4664,19 +3128,19 @@
         <v>25.55634918610405</v>
       </c>
       <c r="D14">
-        <v>52.526911934581193</v>
+        <v>52.52691193458119</v>
       </c>
       <c r="E14">
-        <v>106.46803743153551</v>
+        <v>106.4680374315355</v>
       </c>
       <c r="F14">
-        <v>214.35028842544401</v>
+        <v>214.350288425444</v>
       </c>
       <c r="G14">
-        <v>99.725396744416187</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+        <v>99.72539674441619</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>2</v>
       </c>
@@ -4687,19 +3151,19 @@
         <v>25.55634918610405</v>
       </c>
       <c r="D15">
-        <v>51.698484809834987</v>
+        <v>51.69848480983499</v>
       </c>
       <c r="E15">
         <v>109.4974746830583</v>
       </c>
       <c r="F15">
-        <v>218.75230867899739</v>
+        <v>218.7523086789974</v>
       </c>
       <c r="G15">
         <v>101.3761543394987</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>2</v>
       </c>
@@ -4707,22 +3171,22 @@
         <v>21</v>
       </c>
       <c r="C16">
-        <v>24.616020898215641</v>
+        <v>24.61602089821564</v>
       </c>
       <c r="D16">
         <v>49.34816619039939</v>
       </c>
       <c r="E16">
-        <v>99.166496458306156</v>
+        <v>99.16649645830616</v>
       </c>
       <c r="F16">
-        <v>198.93034199038169</v>
+        <v>198.9303419903817</v>
       </c>
       <c r="G16">
-        <v>93.015256384325724</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+        <v>93.01525638432572</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>2</v>
       </c>
@@ -4730,22 +3194,22 @@
         <v>22</v>
       </c>
       <c r="C17">
-        <v>26.727922061357859</v>
+        <v>26.72792206135786</v>
       </c>
       <c r="D17">
-        <v>54.041630560342618</v>
+        <v>54.04163056034262</v>
       </c>
       <c r="E17">
         <v>103.9827560572969</v>
       </c>
       <c r="F17">
-        <v>208.55129855222069</v>
+        <v>208.5512985522207</v>
       </c>
       <c r="G17">
-        <v>98.325901807804513</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+        <v>98.32590180780451</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>2</v>
       </c>
@@ -4756,19 +3220,19 @@
         <v>25.55634918610405</v>
       </c>
       <c r="D18">
-        <v>51.698484809834987</v>
+        <v>51.69848480983499</v>
       </c>
       <c r="E18">
         <v>103.9827560572969</v>
       </c>
       <c r="F18">
-        <v>208.55129855222069</v>
+        <v>208.5512985522207</v>
       </c>
       <c r="G18">
-        <v>97.447222151364144</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+        <v>97.44722215136414</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>2</v>
       </c>
@@ -4776,22 +3240,22 @@
         <v>24</v>
       </c>
       <c r="C19">
-        <v>26.970562748477139</v>
+        <v>26.97056274847714</v>
       </c>
       <c r="D19">
-        <v>54.041630560342618</v>
+        <v>54.04163056034262</v>
       </c>
       <c r="E19">
         <v>111.8406204335659</v>
       </c>
       <c r="F19">
-        <v>217.92388155425121</v>
+        <v>217.9238815542512</v>
       </c>
       <c r="G19">
-        <v>102.69417382415919</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+        <v>102.6941738241592</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>2</v>
       </c>
@@ -4799,22 +3263,22 @@
         <v>25</v>
       </c>
       <c r="C20">
-        <v>26.142135623730951</v>
+        <v>26.14213562373095</v>
       </c>
       <c r="D20">
-        <v>51.698484809834987</v>
+        <v>51.69848480983499</v>
       </c>
       <c r="E20">
         <v>103.9827560572969</v>
       </c>
       <c r="F20">
-        <v>208.55129855222069</v>
+        <v>208.5512985522207</v>
       </c>
       <c r="G20">
-        <v>97.593668760770868</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+        <v>97.59366876077087</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>2</v>
       </c>
@@ -4822,22 +3286,22 @@
         <v>26</v>
       </c>
       <c r="C21">
-        <v>25.061772596780042</v>
+        <v>25.06177259678004</v>
       </c>
       <c r="D21">
-        <v>50.784817904249259</v>
+        <v>50.78481790424926</v>
       </c>
       <c r="E21">
-        <v>102.44570532669439</v>
+        <v>102.4457053266944</v>
       </c>
       <c r="F21">
-        <v>205.82904579473271</v>
+        <v>205.8290457947327</v>
       </c>
       <c r="G21">
-        <v>96.030335405614096</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+        <v>96.0303354056141</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>2</v>
       </c>
@@ -4845,22 +3309,22 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>24.883627011906739</v>
+        <v>24.88362701190674</v>
       </c>
       <c r="D22">
-        <v>49.468775958388193</v>
+        <v>49.46877595838819</v>
       </c>
       <c r="E22">
-        <v>99.995569844109326</v>
+        <v>99.99556984410933</v>
       </c>
       <c r="F22">
-        <v>201.30769961265111</v>
+        <v>201.3076996126511</v>
       </c>
       <c r="G22">
-        <v>93.913918106763845</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+        <v>93.91391810676384</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>3</v>
       </c>
@@ -4868,22 +3332,22 @@
         <v>28</v>
       </c>
       <c r="C23">
-        <v>24.660751162624539</v>
+        <v>24.66075116262454</v>
       </c>
       <c r="D23">
-        <v>50.193745265794732</v>
+        <v>50.19374526579473</v>
       </c>
       <c r="E23">
         <v>100.9725808023951</v>
       </c>
       <c r="F23">
-        <v>203.16961391690279</v>
+        <v>203.1696139169028</v>
       </c>
       <c r="G23">
-        <v>94.749172786929307</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+        <v>94.74917278692931</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>3</v>
       </c>
@@ -4894,19 +3358,19 @@
         <v>25.55634918610405</v>
       </c>
       <c r="D24">
-        <v>52.526911934581193</v>
+        <v>52.52691193458119</v>
       </c>
       <c r="E24">
-        <v>106.46803743153551</v>
+        <v>106.4680374315355</v>
       </c>
       <c r="F24">
-        <v>214.35028842544401</v>
+        <v>214.350288425444</v>
       </c>
       <c r="G24">
-        <v>99.725396744416187</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+        <v>99.72539674441619</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>3</v>
       </c>
@@ -4917,19 +3381,19 @@
         <v>27.55634918610405</v>
       </c>
       <c r="D25">
-        <v>52.526911934581193</v>
+        <v>52.52691193458119</v>
       </c>
       <c r="E25">
         <v>110.3259018078045</v>
       </c>
       <c r="F25">
-        <v>219.58073580374361</v>
+        <v>219.5807358037436</v>
       </c>
       <c r="G25">
         <v>102.4974746830583</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>3</v>
       </c>
@@ -4937,22 +3401,22 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>25.877054302287249</v>
+        <v>25.87705430228725</v>
       </c>
       <c r="D26">
-        <v>51.454459478380492</v>
+        <v>51.45445947838049</v>
       </c>
       <c r="E26">
         <v>103.3736799535253</v>
       </c>
       <c r="F26">
-        <v>207.42488285544599</v>
+        <v>207.424882855446</v>
       </c>
       <c r="G26">
-        <v>97.032519147409758</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+        <v>97.03251914740976</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>3</v>
       </c>
@@ -4960,7 +3424,7 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>26.727922061357859</v>
+        <v>26.72792206135786</v>
       </c>
       <c r="D27">
         <v>54.87005768508881</v>
@@ -4969,13 +3433,13 @@
         <v>109.4974746830583</v>
       </c>
       <c r="F27">
-        <v>218.75230867899739</v>
+        <v>218.7523086789974</v>
       </c>
       <c r="G27">
         <v>102.4619407771256</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>3</v>
       </c>
@@ -4986,19 +3450,19 @@
         <v>24.65008380450606</v>
       </c>
       <c r="D28">
-        <v>49.953523924572849</v>
+        <v>49.95352392457285</v>
       </c>
       <c r="E28">
-        <v>98.901986786617144</v>
+        <v>98.90198678661714</v>
       </c>
       <c r="F28">
-        <v>197.88084452787041</v>
+        <v>197.8808445278704</v>
       </c>
       <c r="G28">
-        <v>92.846609760891596</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+        <v>92.8466097608916</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>3</v>
       </c>
@@ -5006,22 +3470,22 @@
         <v>34</v>
       </c>
       <c r="C29">
-        <v>24.883627011906739</v>
+        <v>24.88362701190674</v>
       </c>
       <c r="D29">
-        <v>50.688499009058027</v>
+        <v>50.68849900905803</v>
       </c>
       <c r="E29">
         <v>102.5369334732962</v>
       </c>
       <c r="F29">
-        <v>206.40962072616639</v>
+        <v>206.4096207261664</v>
       </c>
       <c r="G29">
-        <v>96.129670055106828</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+        <v>96.12967005510683</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>3</v>
       </c>
@@ -5032,19 +3496,19 @@
         <v>24.65008380450606</v>
       </c>
       <c r="D30">
-        <v>49.547812689146618</v>
+        <v>49.54781268914662</v>
       </c>
       <c r="E30">
-        <v>104.63568079173621</v>
+        <v>104.6356807917362</v>
       </c>
       <c r="F30">
-        <v>209.67674266387999</v>
+        <v>209.67674266388</v>
       </c>
       <c r="G30">
-        <v>97.127579987317219</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+        <v>97.12757998731722</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>3</v>
       </c>
@@ -5055,19 +3519,19 @@
         <v>25.55634918610405</v>
       </c>
       <c r="D31">
-        <v>51.698484809834987</v>
+        <v>51.69848480983499</v>
       </c>
       <c r="E31">
         <v>109.4974746830583</v>
       </c>
       <c r="F31">
-        <v>218.75230867899739</v>
+        <v>218.7523086789974</v>
       </c>
       <c r="G31">
         <v>101.3761543394987</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>3</v>
       </c>
@@ -5075,22 +3539,22 @@
         <v>37</v>
       </c>
       <c r="C32">
-        <v>25.877054302287249</v>
+        <v>25.87705430228725</v>
       </c>
       <c r="D32">
-        <v>51.417057965269542</v>
+        <v>51.41705796526954</v>
       </c>
       <c r="E32">
-        <v>99.166496458306156</v>
+        <v>99.16649645830616</v>
       </c>
       <c r="F32">
-        <v>198.93034199038169</v>
+        <v>198.9303419903817</v>
       </c>
       <c r="G32">
-        <v>93.847737679061154</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+        <v>93.84773767906115</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>3</v>
       </c>
@@ -5101,19 +3565,19 @@
         <v>25.55634918610405</v>
       </c>
       <c r="D33">
-        <v>54.041630560342618</v>
+        <v>54.04163056034262</v>
       </c>
       <c r="E33">
         <v>108.6690475583121</v>
       </c>
       <c r="F33">
-        <v>217.92388155425121</v>
+        <v>217.9238815542512</v>
       </c>
       <c r="G33">
         <v>101.5477272147525</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>3</v>
       </c>
@@ -5121,22 +3585,22 @@
         <v>39</v>
       </c>
       <c r="C34">
-        <v>26.727922061357859</v>
+        <v>26.72792206135786</v>
       </c>
       <c r="D34">
-        <v>54.041630560342618</v>
+        <v>54.04163056034262</v>
       </c>
       <c r="E34">
         <v>108.6690475583121</v>
       </c>
       <c r="F34">
-        <v>217.92388155425121</v>
+        <v>217.9238815542512</v>
       </c>
       <c r="G34">
         <v>101.8406204335659</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>3</v>
       </c>
@@ -5144,22 +3608,22 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>25.061772596780042</v>
+        <v>25.06177259678004</v>
       </c>
       <c r="D35">
-        <v>50.217687953264218</v>
+        <v>50.21768795326422</v>
       </c>
       <c r="E35">
-        <v>100.97795130931109</v>
+        <v>100.9779513093111</v>
       </c>
       <c r="F35">
         <v>202.6246318390989</v>
       </c>
       <c r="G35">
-        <v>94.720510924613549</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+        <v>94.72051092461355</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>3</v>
       </c>
@@ -5167,22 +3631,22 @@
         <v>41</v>
       </c>
       <c r="C36">
-        <v>26.297840574279839</v>
+        <v>26.29784057427984</v>
       </c>
       <c r="D36">
-        <v>52.850016554111697</v>
+        <v>52.8500165541117</v>
       </c>
       <c r="E36">
         <v>111.1160456359106</v>
       </c>
       <c r="F36">
-        <v>214.08984039418249</v>
+        <v>214.0898403941825</v>
       </c>
       <c r="G36">
         <v>101.0884357896212</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>3</v>
       </c>
@@ -5190,22 +3654,22 @@
         <v>42</v>
       </c>
       <c r="C37">
-        <v>26.727922061357859</v>
+        <v>26.72792206135786</v>
       </c>
       <c r="D37">
-        <v>54.041630560342618</v>
+        <v>54.04163056034262</v>
       </c>
       <c r="E37">
         <v>108.6690475583121</v>
       </c>
       <c r="F37">
-        <v>217.92388155425121</v>
+        <v>217.9238815542512</v>
       </c>
       <c r="G37">
         <v>101.8406204335659</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>3</v>
       </c>
@@ -5216,19 +3680,19 @@
         <v>25.64755903440695</v>
       </c>
       <c r="D38">
-        <v>50.784817904249259</v>
+        <v>50.78481790424926</v>
       </c>
       <c r="E38">
-        <v>102.44570532669439</v>
+        <v>102.4457053266944</v>
       </c>
       <c r="F38">
-        <v>205.82904579473271</v>
+        <v>205.8290457947327</v>
       </c>
       <c r="G38">
-        <v>96.176782015020819</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+        <v>96.17678201502082</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>4</v>
       </c>
@@ -5236,22 +3700,22 @@
         <v>44</v>
       </c>
       <c r="C39">
-        <v>24.883627011906739</v>
+        <v>24.88362701190674</v>
       </c>
       <c r="D39">
-        <v>51.003693057838348</v>
+        <v>51.00369305783835</v>
       </c>
       <c r="E39">
         <v>102.0330616688867</v>
       </c>
       <c r="F39">
-        <v>205.15588556365569</v>
+        <v>205.1558855636557</v>
       </c>
       <c r="G39">
-        <v>95.769066825571869</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+        <v>95.76906682557187</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>4</v>
       </c>
@@ -5259,22 +3723,22 @@
         <v>45</v>
       </c>
       <c r="C40">
-        <v>26.414373490277999</v>
+        <v>26.414373490278</v>
       </c>
       <c r="D40">
-        <v>49.693773510102133</v>
+        <v>49.69377351010213</v>
       </c>
       <c r="E40">
         <v>104.569998812953</v>
       </c>
       <c r="F40">
-        <v>209.36663344984279</v>
+        <v>209.3666334498428</v>
       </c>
       <c r="G40">
-        <v>97.511194815793985</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+        <v>97.51119481579398</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>4</v>
       </c>
@@ -5285,19 +3749,19 @@
         <v>27.55634918610405</v>
       </c>
       <c r="D41">
-        <v>52.526911934581193</v>
+        <v>52.52691193458119</v>
       </c>
       <c r="E41">
         <v>110.3259018078045</v>
       </c>
       <c r="F41">
-        <v>219.58073580374361</v>
+        <v>219.5807358037436</v>
       </c>
       <c r="G41">
         <v>102.4974746830583</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>4</v>
       </c>
@@ -5305,22 +3769,22 @@
         <v>47</v>
       </c>
       <c r="C42">
-        <v>26.055199887160551</v>
+        <v>26.05519988716055</v>
       </c>
       <c r="D42">
-        <v>51.454459478380492</v>
+        <v>51.45445947838049</v>
       </c>
       <c r="E42">
-        <v>103.32715348193069</v>
+        <v>103.3271534819307</v>
       </c>
       <c r="F42">
-        <v>207.42488285544599</v>
+        <v>207.424882855446</v>
       </c>
       <c r="G42">
-        <v>97.065423925729448</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+        <v>97.06542392572945</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>4</v>
       </c>
@@ -5331,19 +3795,19 @@
         <v>24.65008380450606</v>
       </c>
       <c r="D43">
-        <v>49.547812689146618</v>
+        <v>49.54781268914662</v>
       </c>
       <c r="E43">
-        <v>104.63568079173621</v>
+        <v>104.6356807917362</v>
       </c>
       <c r="F43">
-        <v>209.67674266387999</v>
+        <v>209.67674266388</v>
       </c>
       <c r="G43">
-        <v>97.127579987317219</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+        <v>97.12757998731722</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>4</v>
       </c>
@@ -5351,7 +3815,7 @@
         <v>49</v>
       </c>
       <c r="C44">
-        <v>25.061772596780042</v>
+        <v>25.06177259678004</v>
       </c>
       <c r="D44">
         <v>52.28288660312667</v>
@@ -5360,13 +3824,13 @@
         <v>105.108348609036</v>
       </c>
       <c r="F44">
-        <v>211.04304927991731</v>
+        <v>211.0430492799173</v>
       </c>
       <c r="G44">
-        <v>98.374014272215007</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+        <v>98.37401427221501</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>4</v>
       </c>
@@ -5374,22 +3838,22 @@
         <v>50</v>
       </c>
       <c r="C45">
-        <v>26.727922061357859</v>
+        <v>26.72792206135786</v>
       </c>
       <c r="D45">
-        <v>54.041630560342618</v>
+        <v>54.04163056034262</v>
       </c>
       <c r="E45">
         <v>108.6690475583121</v>
       </c>
       <c r="F45">
-        <v>217.92388155425121</v>
+        <v>217.9238815542512</v>
       </c>
       <c r="G45">
         <v>101.8406204335659</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>4</v>
       </c>
@@ -5397,7 +3861,7 @@
         <v>51</v>
       </c>
       <c r="C46">
-        <v>26.055199887160551</v>
+        <v>26.05519988716055</v>
       </c>
       <c r="D46">
         <v>52.28288660312667</v>
@@ -5406,13 +3870,13 @@
         <v>105.108348609036</v>
       </c>
       <c r="F46">
-        <v>211.04304927991731</v>
+        <v>211.0430492799173</v>
       </c>
       <c r="G46">
-        <v>98.622371094810134</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+        <v>98.62237109481013</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>4</v>
       </c>
@@ -5420,22 +3884,22 @@
         <v>52</v>
       </c>
       <c r="C47">
-        <v>25.877054302287249</v>
+        <v>25.87705430228725</v>
       </c>
       <c r="D47">
-        <v>52.850016554111697</v>
+        <v>52.8500165541117</v>
       </c>
       <c r="E47">
         <v>106.5761026264193</v>
       </c>
       <c r="F47">
-        <v>214.08984039418249</v>
+        <v>214.0898403941825</v>
       </c>
       <c r="G47">
-        <v>99.848253469250182</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+        <v>99.84825346925018</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>5</v>
       </c>
@@ -5443,22 +3907,22 @@
         <v>53</v>
       </c>
       <c r="C48">
-        <v>26.414373490277999</v>
+        <v>26.414373490278</v>
       </c>
       <c r="D48">
-        <v>49.693773510102133</v>
+        <v>49.69377351010213</v>
       </c>
       <c r="E48">
         <v>104.569998812953</v>
       </c>
       <c r="F48">
-        <v>209.36663344984279</v>
+        <v>209.3666334498428</v>
       </c>
       <c r="G48">
-        <v>97.511194815793985</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+        <v>97.51119481579398</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>5</v>
       </c>
@@ -5466,7 +3930,7 @@
         <v>54</v>
       </c>
       <c r="C49">
-        <v>26.055199887160551</v>
+        <v>26.05519988716055</v>
       </c>
       <c r="D49">
         <v>52.28288660312667</v>
@@ -5475,10 +3939,10 @@
         <v>105.108348609036</v>
       </c>
       <c r="F49">
-        <v>211.04304927991731</v>
+        <v>211.0430492799173</v>
       </c>
       <c r="G49">
-        <v>98.622371094810134</v>
+        <v>98.62237109481013</v>
       </c>
     </row>
   </sheetData>
@@ -5487,11 +3951,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5514,7 +3978,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
@@ -5537,7 +4001,7 @@
         <v>152.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5560,7 +4024,7 @@
         <v>338.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>1</v>
       </c>
@@ -5583,7 +4047,7 @@
         <v>268.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>1</v>
       </c>
@@ -5606,7 +4070,7 @@
         <v>237.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>1</v>
       </c>
@@ -5629,7 +4093,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -5652,7 +4116,7 @@
         <v>152.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>1</v>
       </c>
@@ -5675,7 +4139,7 @@
         <v>134.25</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>2</v>
       </c>
@@ -5698,7 +4162,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>2</v>
       </c>
@@ -5721,7 +4185,7 @@
         <v>171.25</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>2</v>
       </c>
@@ -5744,7 +4208,7 @@
         <v>338.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>2</v>
       </c>
@@ -5767,7 +4231,7 @@
         <v>264.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>2</v>
       </c>
@@ -5790,7 +4254,7 @@
         <v>268.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>2</v>
       </c>
@@ -5813,7 +4277,7 @@
         <v>272.25</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>2</v>
       </c>
@@ -5836,7 +4300,7 @@
         <v>210.75</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>2</v>
       </c>
@@ -5859,7 +4323,7 @@
         <v>237.5</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>2</v>
       </c>
@@ -5882,7 +4346,7 @@
         <v>252.5</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>2</v>
       </c>
@@ -5905,7 +4369,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>2</v>
       </c>
@@ -5928,7 +4392,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>2</v>
       </c>
@@ -5951,7 +4415,7 @@
         <v>15.25</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>2</v>
       </c>
@@ -5974,7 +4438,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>2</v>
       </c>
@@ -5997,7 +4461,7 @@
         <v>134.25</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>3</v>
       </c>
@@ -6020,7 +4484,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>3</v>
       </c>
@@ -6043,7 +4507,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>3</v>
       </c>
@@ -6066,7 +4530,7 @@
         <v>207.75</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>3</v>
       </c>
@@ -6089,7 +4553,7 @@
         <v>171.25</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>3</v>
       </c>
@@ -6112,7 +4576,7 @@
         <v>157.5</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>3</v>
       </c>
@@ -6135,7 +4599,7 @@
         <v>264.5</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>3</v>
       </c>
@@ -6158,7 +4622,7 @@
         <v>272.25</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>3</v>
       </c>
@@ -6181,7 +4645,7 @@
         <v>210.75</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>3</v>
       </c>
@@ -6204,7 +4668,7 @@
         <v>223.75</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>3</v>
       </c>
@@ -6227,7 +4691,7 @@
         <v>252.5</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>3</v>
       </c>
@@ -6250,7 +4714,7 @@
         <v>16.25</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>3</v>
       </c>
@@ -6273,7 +4737,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>3</v>
       </c>
@@ -6296,7 +4760,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>3</v>
       </c>
@@ -6319,7 +4783,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>3</v>
       </c>
@@ -6342,7 +4806,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>3</v>
       </c>
@@ -6365,7 +4829,7 @@
         <v>15.25</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>4</v>
       </c>
@@ -6388,7 +4852,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>4</v>
       </c>
@@ -6411,7 +4875,7 @@
         <v>207.75</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>4</v>
       </c>
@@ -6434,7 +4898,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>4</v>
       </c>
@@ -6457,7 +4921,7 @@
         <v>157.5</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>4</v>
       </c>
@@ -6480,7 +4944,7 @@
         <v>223.75</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>4</v>
       </c>
@@ -6503,7 +4967,7 @@
         <v>16.25</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>4</v>
       </c>
@@ -6526,7 +4990,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>4</v>
       </c>
@@ -6549,7 +5013,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>4</v>
       </c>
@@ -6572,7 +5036,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>5</v>
       </c>
@@ -6595,7 +5059,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>5</v>
       </c>
@@ -6624,11 +5088,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6651,7 +5115,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
@@ -6674,7 +5138,7 @@
         <v>1378.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1</v>
       </c>
@@ -6697,7 +5161,7 @@
         <v>1201.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>1</v>
       </c>
@@ -6720,7 +5184,7 @@
         <v>703.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>1</v>
       </c>
@@ -6743,7 +5207,7 @@
         <v>998.75</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>1</v>
       </c>
@@ -6766,7 +5230,7 @@
         <v>40.75</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -6789,7 +5253,7 @@
         <v>1378.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>1</v>
       </c>
@@ -6812,7 +5276,7 @@
         <v>1398.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>2</v>
       </c>
@@ -6835,7 +5299,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>2</v>
       </c>
@@ -6858,7 +5322,7 @@
         <v>979.75</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>2</v>
       </c>
@@ -6881,7 +5345,7 @@
         <v>1201.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>2</v>
       </c>
@@ -6904,7 +5368,7 @@
         <v>1162.25</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>2</v>
       </c>
@@ -6927,7 +5391,7 @@
         <v>703.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>2</v>
       </c>
@@ -6950,7 +5414,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>2</v>
       </c>
@@ -6973,7 +5437,7 @@
         <v>881.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>2</v>
       </c>
@@ -6996,7 +5460,7 @@
         <v>998.75</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>2</v>
       </c>
@@ -7019,7 +5483,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>2</v>
       </c>
@@ -7042,7 +5506,7 @@
         <v>33.75</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>2</v>
       </c>
@@ -7065,7 +5529,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>2</v>
       </c>
@@ -7088,7 +5552,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>2</v>
       </c>
@@ -7111,7 +5575,7 @@
         <v>40.75</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>2</v>
       </c>
@@ -7134,7 +5598,7 @@
         <v>1398.5</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>3</v>
       </c>
@@ -7157,7 +5621,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>3</v>
       </c>
@@ -7180,7 +5644,7 @@
         <v>703.25</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>3</v>
       </c>
@@ -7203,7 +5667,7 @@
         <v>836.75</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>3</v>
       </c>
@@ -7226,7 +5690,7 @@
         <v>979.75</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>3</v>
       </c>
@@ -7249,7 +5713,7 @@
         <v>1003.75</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>3</v>
       </c>
@@ -7272,7 +5736,7 @@
         <v>1162.25</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>3</v>
       </c>
@@ -7295,7 +5759,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>3</v>
       </c>
@@ -7318,7 +5782,7 @@
         <v>881.5</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>3</v>
       </c>
@@ -7341,7 +5805,7 @@
         <v>886.25</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>3</v>
       </c>
@@ -7364,7 +5828,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>3</v>
       </c>
@@ -7387,7 +5851,7 @@
         <v>36.25</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>3</v>
       </c>
@@ -7410,7 +5874,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>3</v>
       </c>
@@ -7433,7 +5897,7 @@
         <v>33.75</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>3</v>
       </c>
@@ -7456,7 +5920,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>3</v>
       </c>
@@ -7479,7 +5943,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>3</v>
       </c>
@@ -7502,7 +5966,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>4</v>
       </c>
@@ -7525,7 +5989,7 @@
         <v>703.25</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>4</v>
       </c>
@@ -7548,7 +6012,7 @@
         <v>836.75</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>4</v>
       </c>
@@ -7571,7 +6035,7 @@
         <v>881.5</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>4</v>
       </c>
@@ -7594,7 +6058,7 @@
         <v>1003.75</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>4</v>
       </c>
@@ -7617,7 +6081,7 @@
         <v>886.25</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>4</v>
       </c>
@@ -7640,7 +6104,7 @@
         <v>36.25</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>4</v>
       </c>
@@ -7663,7 +6127,7 @@
         <v>38.25</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>4</v>
       </c>
@@ -7686,7 +6150,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>4</v>
       </c>
@@ -7709,7 +6173,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>5</v>
       </c>
@@ -7732,7 +6196,7 @@
         <v>881.5</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>5</v>
       </c>
@@ -7761,11 +6225,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7788,7 +6252,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
@@ -7811,7 +6275,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1</v>
       </c>
@@ -7834,7 +6298,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>1</v>
       </c>
@@ -7857,7 +6321,7 @@
         <v>16.75</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>1</v>
       </c>
@@ -7880,7 +6344,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>1</v>
       </c>
@@ -7903,7 +6367,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -7926,7 +6390,7 @@
         <v>8.25</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>1</v>
       </c>
@@ -7949,7 +6413,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>2</v>
       </c>
@@ -7972,7 +6436,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>2</v>
       </c>
@@ -7995,7 +6459,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>2</v>
       </c>
@@ -8018,7 +6482,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>2</v>
       </c>
@@ -8041,7 +6505,7 @@
         <v>15.25</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>2</v>
       </c>
@@ -8064,7 +6528,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>2</v>
       </c>
@@ -8087,7 +6551,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>2</v>
       </c>
@@ -8110,7 +6574,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>2</v>
       </c>
@@ -8133,7 +6597,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>2</v>
       </c>
@@ -8156,7 +6620,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>2</v>
       </c>
@@ -8179,7 +6643,7 @@
         <v>11.75</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>2</v>
       </c>
@@ -8202,7 +6666,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>2</v>
       </c>
@@ -8225,7 +6689,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>2</v>
       </c>
@@ -8248,7 +6712,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>2</v>
       </c>
@@ -8271,7 +6735,7 @@
         <v>8.25</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>3</v>
       </c>
@@ -8294,7 +6758,7 @@
         <v>9.25</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>3</v>
       </c>
@@ -8317,7 +6781,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>3</v>
       </c>
@@ -8340,7 +6804,7 @@
         <v>16.75</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>3</v>
       </c>
@@ -8363,7 +6827,7 @@
         <v>9.75</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>3</v>
       </c>
@@ -8386,7 +6850,7 @@
         <v>17.75</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>3</v>
       </c>
@@ -8409,7 +6873,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>3</v>
       </c>
@@ -8432,7 +6896,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>3</v>
       </c>
@@ -8455,7 +6919,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>3</v>
       </c>
@@ -8478,7 +6942,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>3</v>
       </c>
@@ -8501,7 +6965,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>3</v>
       </c>
@@ -8524,7 +6988,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>3</v>
       </c>
@@ -8547,7 +7011,7 @@
         <v>13.75</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>3</v>
       </c>
@@ -8570,7 +7034,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>3</v>
       </c>
@@ -8593,7 +7057,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>3</v>
       </c>
@@ -8616,7 +7080,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>3</v>
       </c>
@@ -8639,7 +7103,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>4</v>
       </c>
@@ -8662,7 +7126,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>4</v>
       </c>
@@ -8685,7 +7149,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>4</v>
       </c>
@@ -8708,7 +7172,7 @@
         <v>16.25</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>4</v>
       </c>
@@ -8731,7 +7195,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>4</v>
       </c>
@@ -8754,7 +7218,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>4</v>
       </c>
@@ -8777,7 +7241,7 @@
         <v>9.75</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>4</v>
       </c>
@@ -8800,7 +7264,7 @@
         <v>13.75</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>4</v>
       </c>
@@ -8823,7 +7287,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>4</v>
       </c>
@@ -8846,7 +7310,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>5</v>
       </c>
@@ -8869,7 +7333,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>5</v>
       </c>

--- a/Excel/Validasi/Hasil_Pengujian_Map_1_128_avg_length.xlsx
+++ b/Excel/Validasi/Hasil_Pengujian_Map_1_128_avg_length.xlsx
@@ -506,19 +506,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.0004756999999999999</v>
+        <v>0.000488</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0028988</v>
+        <v>0.002934</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0186209</v>
+        <v>0.0191111</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1221172</v>
+        <v>0.1264418</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03602815</v>
+        <v>0.037243725</v>
       </c>
     </row>
     <row r="3">
@@ -531,19 +531,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.0003067</v>
+        <v>0.0003022</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0012662</v>
+        <v>0.0011951</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0048661</v>
+        <v>0.0049929</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0206463</v>
+        <v>0.0208262</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006771325000000001</v>
+        <v>0.006829100000000001</v>
       </c>
     </row>
     <row r="4">
@@ -556,19 +556,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0004619</v>
+        <v>0.0004053</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0020094</v>
+        <v>0.0018053</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0158992</v>
+        <v>0.0142213</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1740273</v>
+        <v>0.1646243</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04809945</v>
+        <v>0.04526405</v>
       </c>
     </row>
     <row r="5">
@@ -581,19 +581,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.0003941</v>
+        <v>0.0003970999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002353</v>
+        <v>0.0023637</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0155628</v>
+        <v>0.0155513</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1056073</v>
+        <v>0.1113312</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0309793</v>
+        <v>0.032410825</v>
       </c>
     </row>
     <row r="6">
@@ -606,19 +606,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0003715</v>
+        <v>0.0003778</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0010265</v>
+        <v>0.0009717</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0033432</v>
+        <v>0.0033759</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0119062</v>
+        <v>0.012292</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00416185</v>
+        <v>0.00425435</v>
       </c>
     </row>
     <row r="7">
@@ -631,19 +631,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0005382000000000001</v>
+        <v>0.0006016000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002879800000000001</v>
+        <v>0.003082</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0186637</v>
+        <v>0.0195018</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1220557</v>
+        <v>0.127873</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03603435</v>
+        <v>0.0377646</v>
       </c>
     </row>
     <row r="8">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0005308</v>
+        <v>0.0005254999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0028147</v>
+        <v>0.0027902</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0176039</v>
+        <v>0.0178527</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1156211</v>
+        <v>0.1198106</v>
       </c>
       <c r="G8" t="n">
-        <v>0.034142625</v>
+        <v>0.03524475</v>
       </c>
     </row>
     <row r="9">
@@ -681,19 +681,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0004712</v>
+        <v>0.0004429</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0018196</v>
+        <v>0.0016992</v>
       </c>
       <c r="E9" t="n">
-        <v>0.008529600000000002</v>
+        <v>0.008820700000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.051552</v>
+        <v>0.0528004</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0155931</v>
+        <v>0.0159408</v>
       </c>
     </row>
     <row r="10">
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0003732</v>
+        <v>0.0003189</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0014352</v>
+        <v>0.0013871</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0058292</v>
+        <v>0.005935</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0246614</v>
+        <v>0.0249958</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00807475</v>
+        <v>0.0081592</v>
       </c>
     </row>
     <row r="11">
@@ -731,19 +731,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.000318</v>
+        <v>0.0003365</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0013445</v>
+        <v>0.0013536</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0061563</v>
+        <v>0.005054500000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0210556</v>
+        <v>0.0217027</v>
       </c>
       <c r="G11" t="n">
-        <v>0.007218599999999999</v>
+        <v>0.007111825</v>
       </c>
     </row>
     <row r="12">
@@ -756,19 +756,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0003443</v>
+        <v>0.0003193</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0015302</v>
+        <v>0.0014867</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0055171</v>
+        <v>0.0054447</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0218654</v>
+        <v>0.021916</v>
       </c>
       <c r="G12" t="n">
-        <v>0.00731425</v>
+        <v>0.007291674999999999</v>
       </c>
     </row>
     <row r="13">
@@ -781,19 +781,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0004921</v>
+        <v>0.0004682000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0021853</v>
+        <v>0.0019299</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0167967</v>
+        <v>0.0142374</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1759747</v>
+        <v>0.1669026</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0488622</v>
+        <v>0.045884525</v>
       </c>
     </row>
     <row r="14">
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0005229</v>
+        <v>0.0004872</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0021296</v>
+        <v>0.001915</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0162308</v>
+        <v>0.0138306</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1649628</v>
+        <v>0.1616847</v>
       </c>
       <c r="G14" t="n">
-        <v>0.04596152499999999</v>
+        <v>0.04447937499999999</v>
       </c>
     </row>
     <row r="15">
@@ -831,19 +831,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0005288</v>
+        <v>0.0005844</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0027433</v>
+        <v>0.0026095</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0204157</v>
+        <v>0.0183228</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2079127</v>
+        <v>0.1764387</v>
       </c>
       <c r="G15" t="n">
-        <v>0.057900125</v>
+        <v>0.04948885</v>
       </c>
     </row>
     <row r="16">
@@ -856,19 +856,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0004431</v>
+        <v>0.0004614</v>
       </c>
       <c r="D16" t="n">
-        <v>0.00235</v>
+        <v>0.00241</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0158109</v>
+        <v>0.0156817</v>
       </c>
       <c r="F16" t="n">
-        <v>0.106677</v>
+        <v>0.1132413</v>
       </c>
       <c r="G16" t="n">
-        <v>0.03132025</v>
+        <v>0.0329486</v>
       </c>
     </row>
     <row r="17">
@@ -881,19 +881,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0005802</v>
+        <v>0.0005739</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0034873</v>
+        <v>0.0035986</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0157301</v>
+        <v>0.0158411</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1034032</v>
+        <v>0.1056952</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0308002</v>
+        <v>0.0314272</v>
       </c>
     </row>
     <row r="18">
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0003467</v>
+        <v>0.0003591</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0009754000000000001</v>
+        <v>0.00098</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0028549</v>
+        <v>0.0028888</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0108609</v>
+        <v>0.0108466</v>
       </c>
       <c r="G18" t="n">
-        <v>0.003759475</v>
+        <v>0.003768625</v>
       </c>
     </row>
     <row r="19">
@@ -931,19 +931,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0003091</v>
+        <v>0.0003145</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0008983</v>
+        <v>0.0008716999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0032276</v>
+        <v>0.0025937</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0117835</v>
+        <v>0.0121766</v>
       </c>
       <c r="G19" t="n">
-        <v>0.004054625</v>
+        <v>0.003989125</v>
       </c>
     </row>
     <row r="20">
@@ -956,19 +956,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0003916999999999999</v>
+        <v>0.000361</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0011461</v>
+        <v>0.0011302</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0036688</v>
+        <v>0.0036276</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0132597</v>
+        <v>0.0133442</v>
       </c>
       <c r="G20" t="n">
-        <v>0.004616574999999999</v>
+        <v>0.00461575</v>
       </c>
     </row>
     <row r="21">
@@ -981,19 +981,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0003956</v>
+        <v>0.0003751</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0010646</v>
+        <v>0.0011003</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0033574</v>
+        <v>0.0034493</v>
       </c>
       <c r="F21" t="n">
-        <v>0.012179</v>
+        <v>0.0122192</v>
       </c>
       <c r="G21" t="n">
-        <v>0.00424915</v>
+        <v>0.004285975</v>
       </c>
     </row>
     <row r="22">
@@ -1006,19 +1006,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0005819</v>
+        <v>0.0005897000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0028</v>
+        <v>0.0029227</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0177781</v>
+        <v>0.0182536</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1173793</v>
+        <v>0.1212913</v>
       </c>
       <c r="G22" t="n">
-        <v>0.034634825</v>
+        <v>0.035764325</v>
       </c>
     </row>
     <row r="23">
@@ -1031,19 +1031,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.000505</v>
+        <v>0.0005002</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0019143</v>
+        <v>0.0017475</v>
       </c>
       <c r="E23" t="n">
-        <v>0.008947300000000002</v>
+        <v>0.008291099999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0540928</v>
+        <v>0.0530564</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01636485</v>
+        <v>0.0158988</v>
       </c>
     </row>
     <row r="24">
@@ -1056,19 +1056,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0004673</v>
+        <v>0.0005290999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0020009</v>
+        <v>0.0017723</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0093343</v>
+        <v>0.0085497</v>
       </c>
       <c r="F24" t="n">
-        <v>0.054073</v>
+        <v>0.0533539</v>
       </c>
       <c r="G24" t="n">
-        <v>0.016468875</v>
+        <v>0.01605125</v>
       </c>
     </row>
     <row r="25">
@@ -1081,19 +1081,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0005209</v>
+        <v>0.0005549</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0028063</v>
+        <v>0.0023584</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0136905</v>
+        <v>0.012572</v>
       </c>
       <c r="F25" t="n">
-        <v>0.08627009999999999</v>
+        <v>0.0846522</v>
       </c>
       <c r="G25" t="n">
-        <v>0.02582195</v>
+        <v>0.025034375</v>
       </c>
     </row>
     <row r="26">
@@ -1106,19 +1106,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0003688</v>
+        <v>0.0003788</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0015198</v>
+        <v>0.0015154</v>
       </c>
       <c r="E26" t="n">
-        <v>0.006096</v>
+        <v>0.006075</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0252678</v>
+        <v>0.0262154</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0083131</v>
+        <v>0.008546149999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1131,19 +1131,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0003525</v>
+        <v>0.0003761</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0016157</v>
+        <v>0.0016044</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0065068</v>
+        <v>0.0063856</v>
       </c>
       <c r="F27" t="n">
-        <v>0.02576230000000001</v>
+        <v>0.0264375</v>
       </c>
       <c r="G27" t="n">
-        <v>0.008559325000000001</v>
+        <v>0.008700899999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1156,19 +1156,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0003619</v>
+        <v>0.000369</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0015598</v>
+        <v>0.0015119</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0057539</v>
+        <v>0.005735599999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0223897</v>
+        <v>0.0228551</v>
       </c>
       <c r="G28" t="n">
-        <v>0.007516324999999999</v>
+        <v>0.007617899999999999</v>
       </c>
     </row>
     <row r="29">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0005151</v>
+        <v>0.0005112000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0023147</v>
+        <v>0.0020943</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0165782</v>
+        <v>0.0142882</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1687278</v>
+        <v>0.1643884</v>
       </c>
       <c r="G29" t="n">
-        <v>0.04703395</v>
+        <v>0.045320525</v>
       </c>
     </row>
     <row r="30">
@@ -1206,19 +1206,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0005317000000000001</v>
+        <v>0.0006200999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0028494</v>
+        <v>0.0025644</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0209271</v>
+        <v>0.0187376</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2072366</v>
+        <v>0.179151</v>
       </c>
       <c r="G30" t="n">
-        <v>0.05788620000000001</v>
+        <v>0.050268275</v>
       </c>
     </row>
     <row r="31">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0005666000000000001</v>
+        <v>0.0006041</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0028583</v>
+        <v>0.0027139</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0213642</v>
+        <v>0.0179335</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2053403</v>
+        <v>0.1518734</v>
       </c>
       <c r="G31" t="n">
-        <v>0.05753235</v>
+        <v>0.043281225</v>
       </c>
     </row>
     <row r="32">
@@ -1256,19 +1256,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0006046000000000001</v>
+        <v>0.0006119</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0035056</v>
+        <v>0.0035223</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0163175</v>
+        <v>0.0160673</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1051713</v>
+        <v>0.1078077</v>
       </c>
       <c r="G32" t="n">
-        <v>0.03139975</v>
+        <v>0.0320023</v>
       </c>
     </row>
     <row r="33">
@@ -1281,19 +1281,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0004681</v>
+        <v>0.0004094</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0011065</v>
+        <v>0.0011284</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0033254</v>
+        <v>0.0032717</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0117152</v>
+        <v>0.0107584</v>
       </c>
       <c r="G33" t="n">
-        <v>0.004153799999999999</v>
+        <v>0.003891975</v>
       </c>
     </row>
     <row r="34">
@@ -1306,19 +1306,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0003272</v>
+        <v>0.0003128000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0011511</v>
+        <v>0.0010323</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0029128</v>
+        <v>0.0029806</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0112634</v>
+        <v>0.0113632</v>
       </c>
       <c r="G34" t="n">
-        <v>0.003913625</v>
+        <v>0.003922225000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1331,19 +1331,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0003986000000000001</v>
+        <v>0.0004091</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0010193</v>
+        <v>0.0009947999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0030416</v>
+        <v>0.0029447</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0108127</v>
+        <v>0.0111221</v>
       </c>
       <c r="G35" t="n">
-        <v>0.00381805</v>
+        <v>0.003867675</v>
       </c>
     </row>
     <row r="36">
@@ -1356,19 +1356,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0003326</v>
+        <v>0.0003565</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0009556</v>
+        <v>0.0009288999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0032688</v>
+        <v>0.0025786</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0117226</v>
+        <v>0.0121538</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0040699</v>
+        <v>0.00400445</v>
       </c>
     </row>
     <row r="37">
@@ -1381,19 +1381,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.0003278</v>
+        <v>0.000322</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0010643</v>
+        <v>0.0009711000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>0.002871</v>
+        <v>0.0026808</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0125853</v>
+        <v>0.0114559</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0042121</v>
+        <v>0.00385745</v>
       </c>
     </row>
     <row r="38">
@@ -1406,19 +1406,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.0004063000000000001</v>
+        <v>0.0004107000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0011827</v>
+        <v>0.0012051</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0037134</v>
+        <v>0.0036779</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0132234</v>
+        <v>0.0133779</v>
       </c>
       <c r="G38" t="n">
-        <v>0.00463145</v>
+        <v>0.004667900000000001</v>
       </c>
     </row>
     <row r="39">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.0004917000000000001</v>
+        <v>0.0005093000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0020552</v>
+        <v>0.0019482</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0096069</v>
+        <v>0.0090095</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0543331</v>
+        <v>0.05484220000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>0.016621725</v>
+        <v>0.0165773</v>
       </c>
     </row>
     <row r="40">
@@ -1456,19 +1456,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0005229</v>
+        <v>0.0005922</v>
       </c>
       <c r="D40" t="n">
-        <v>0.00289</v>
+        <v>0.0023443</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0140074</v>
+        <v>0.0129631</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0875451</v>
+        <v>0.0861218</v>
       </c>
       <c r="G40" t="n">
-        <v>0.02624135</v>
+        <v>0.02550535</v>
       </c>
     </row>
     <row r="41">
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.000592</v>
+        <v>0.0006981</v>
       </c>
       <c r="D41" t="n">
-        <v>0.003019399999999999</v>
+        <v>0.002830099999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0147816</v>
+        <v>0.0139667</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0860274</v>
+        <v>0.085648</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0261051</v>
+        <v>0.025785725</v>
       </c>
     </row>
     <row r="42">
@@ -1506,19 +1506,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.0004217</v>
+        <v>0.000403</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0017371</v>
+        <v>0.001654</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0066523</v>
+        <v>0.0066898</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0264875</v>
+        <v>0.0271707</v>
       </c>
       <c r="G42" t="n">
-        <v>0.00882465</v>
+        <v>0.008979375</v>
       </c>
     </row>
     <row r="43">
@@ -1531,19 +1531,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.0006101</v>
+        <v>0.0006057</v>
       </c>
       <c r="D43" t="n">
-        <v>0.002870699999999999</v>
+        <v>0.0028399</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0220386</v>
+        <v>0.0179021</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2044078</v>
+        <v>0.1528052</v>
       </c>
       <c r="G43" t="n">
-        <v>0.05748179999999999</v>
+        <v>0.04353822500000001</v>
       </c>
     </row>
     <row r="44">
@@ -1556,19 +1556,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.0004442</v>
+        <v>0.0003966</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0012349</v>
+        <v>0.0011272</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0033418</v>
+        <v>0.0032949</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0113932</v>
+        <v>0.0106684</v>
       </c>
       <c r="G44" t="n">
-        <v>0.004103525</v>
+        <v>0.003871775</v>
       </c>
     </row>
     <row r="45">
@@ -1581,19 +1581,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.0003973</v>
+        <v>0.0004068</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0014864</v>
+        <v>0.0014149</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0036257</v>
+        <v>0.0033747</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0128792</v>
+        <v>0.0117605</v>
       </c>
       <c r="G45" t="n">
-        <v>0.00459715</v>
+        <v>0.004239224999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1606,19 +1606,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.0003356</v>
+        <v>0.0003226</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0011823</v>
+        <v>0.0010937</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0030179</v>
+        <v>0.0030327</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0115555</v>
+        <v>0.0113453</v>
       </c>
       <c r="G46" t="n">
-        <v>0.004022825</v>
+        <v>0.003948574999999999</v>
       </c>
     </row>
     <row r="47">
@@ -1631,19 +1631,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.0003649</v>
+        <v>0.0003851</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0010953</v>
+        <v>0.0010217</v>
       </c>
       <c r="E47" t="n">
-        <v>0.00299</v>
+        <v>0.0027238</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0123946</v>
+        <v>0.0114242</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0042112</v>
+        <v>0.0038887</v>
       </c>
     </row>
     <row r="48">
@@ -1656,19 +1656,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.0006339000000000001</v>
+        <v>0.0007373</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0032533</v>
+        <v>0.0029201</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0148296</v>
+        <v>0.0142106</v>
       </c>
       <c r="F48" t="n">
-        <v>0.08674019999999998</v>
+        <v>0.0864718</v>
       </c>
       <c r="G48" t="n">
-        <v>0.02636425</v>
+        <v>0.02608495</v>
       </c>
     </row>
     <row r="49">
@@ -1681,19 +1681,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.0004256</v>
+        <v>0.0004337</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0014189</v>
+        <v>0.001344</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0037633</v>
+        <v>0.003318</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0128954</v>
+        <v>0.0118754</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0046258</v>
+        <v>0.004242775</v>
       </c>
     </row>
   </sheetData>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
         <v>44</v>
@@ -1819,7 +1819,7 @@
         <v>176</v>
       </c>
       <c r="G4" t="n">
-        <v>82.75</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="5">
@@ -2032,7 +2032,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
         <v>8</v>
@@ -2044,7 +2044,7 @@
         <v>9</v>
       </c>
       <c r="G13" t="n">
-        <v>8.75</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="14">
@@ -2082,10 +2082,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E15" t="n">
         <v>96</v>
@@ -2094,7 +2094,7 @@
         <v>192</v>
       </c>
       <c r="G15" t="n">
-        <v>88.5</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -2182,19 +2182,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D19" t="n">
         <v>20</v>
       </c>
       <c r="E19" t="n">
+        <v>20</v>
+      </c>
+      <c r="F19" t="n">
         <v>21</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>20</v>
-      </c>
-      <c r="G19" t="n">
-        <v>19.75</v>
       </c>
     </row>
     <row r="20">
@@ -2232,19 +2232,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="22">
@@ -2335,7 +2335,7 @@
         <v>24</v>
       </c>
       <c r="D25" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E25" t="n">
         <v>96</v>
@@ -2344,7 +2344,7 @@
         <v>192</v>
       </c>
       <c r="G25" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26">
@@ -2457,10 +2457,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E30" t="n">
         <v>9</v>
@@ -2469,7 +2469,7 @@
         <v>9</v>
       </c>
       <c r="G30" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="31">
@@ -2488,13 +2488,13 @@
         <v>44</v>
       </c>
       <c r="E31" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F31" t="n">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="G31" t="n">
-        <v>88.5</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="32">
@@ -2582,19 +2582,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D35" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E35" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F35" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G35" t="n">
-        <v>7.75</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="36">
@@ -2607,19 +2607,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E36" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G36" t="n">
-        <v>10.5</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="37">
@@ -2657,19 +2657,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G38" t="n">
-        <v>8.25</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="39">
@@ -2707,10 +2707,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E40" t="n">
         <v>10</v>
@@ -2719,7 +2719,7 @@
         <v>10</v>
       </c>
       <c r="G40" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41">
@@ -2732,19 +2732,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D41" t="n">
         <v>44</v>
       </c>
       <c r="E41" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F41" t="n">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="G41" t="n">
-        <v>89</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="42">
@@ -2782,19 +2782,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D43" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E43" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F43" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G43" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44">
@@ -2807,19 +2807,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F44" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G44" t="n">
-        <v>8.75</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="45">
@@ -2857,19 +2857,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F46" t="n">
+        <v>11</v>
+      </c>
+      <c r="G46" t="n">
         <v>10</v>
-      </c>
-      <c r="G46" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="47">
@@ -2882,19 +2882,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D47" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E47" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F47" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G47" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="48">
@@ -2907,19 +2907,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D48" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E48" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F48" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G48" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49">
@@ -2932,19 +2932,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D49" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E49" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F49" t="n">
+        <v>11</v>
+      </c>
+      <c r="G49" t="n">
         <v>10</v>
-      </c>
-      <c r="G49" t="n">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26.97056274847714</v>
+        <v>25.55634918610405</v>
       </c>
       <c r="D4" t="n">
         <v>52.52691193458119</v>
@@ -3070,7 +3070,7 @@
         <v>214.350288425444</v>
       </c>
       <c r="G4" t="n">
-        <v>100.0789501350095</v>
+        <v>99.72539674441619</v>
       </c>
     </row>
     <row r="5">
@@ -3186,7 +3186,7 @@
         <v>25.55634918610405</v>
       </c>
       <c r="D9" t="n">
-        <v>53.35533905932738</v>
+        <v>52.52691193458119</v>
       </c>
       <c r="E9" t="n">
         <v>107.2964645562817</v>
@@ -3195,7 +3195,7 @@
         <v>215.1787155501902</v>
       </c>
       <c r="G9" t="n">
-        <v>100.3467170879758</v>
+        <v>100.1396103067893</v>
       </c>
     </row>
     <row r="10">
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>25.7850865361163</v>
+        <v>24.41488446708389</v>
       </c>
       <c r="D13" t="n">
         <v>49.56011556674471</v>
@@ -3295,7 +3295,7 @@
         <v>203.2348880049742</v>
       </c>
       <c r="G13" t="n">
-        <v>94.92412607931394</v>
+        <v>94.58157556205583</v>
       </c>
     </row>
     <row r="14">
@@ -3333,19 +3333,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>25.55634918610405</v>
+        <v>27.55634918610405</v>
       </c>
       <c r="D15" t="n">
-        <v>51.69848480983499</v>
+        <v>54.87005768508881</v>
       </c>
       <c r="E15" t="n">
-        <v>109.4974746830583</v>
+        <v>108.6690475583121</v>
       </c>
       <c r="F15" t="n">
-        <v>218.7523086789974</v>
+        <v>217.9238815542512</v>
       </c>
       <c r="G15" t="n">
-        <v>101.3761543394987</v>
+        <v>102.254833995939</v>
       </c>
     </row>
     <row r="16">
@@ -3433,19 +3433,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>26.97056274847714</v>
+        <v>27.55634918610405</v>
       </c>
       <c r="D19" t="n">
         <v>54.04163056034262</v>
       </c>
       <c r="E19" t="n">
-        <v>111.8406204335659</v>
+        <v>108.6690475583121</v>
       </c>
       <c r="F19" t="n">
-        <v>217.9238815542512</v>
+        <v>223.4386001800126</v>
       </c>
       <c r="G19" t="n">
-        <v>102.6941738241592</v>
+        <v>103.4264068711929</v>
       </c>
     </row>
     <row r="20">
@@ -3483,19 +3483,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.74064110506006</v>
+        <v>24.62280887594792</v>
       </c>
       <c r="D21" t="n">
-        <v>50.17676995799587</v>
+        <v>50.84539750584248</v>
       </c>
       <c r="E21" t="n">
-        <v>100.1430788450122</v>
+        <v>101.6414365392452</v>
       </c>
       <c r="F21" t="n">
-        <v>200.8525404962239</v>
+        <v>204.0006534257569</v>
       </c>
       <c r="G21" t="n">
-        <v>93.72825760107301</v>
+        <v>95.27757408669811</v>
       </c>
     </row>
     <row r="22">
@@ -3536,7 +3536,7 @@
         <v>24.41488446708389</v>
       </c>
       <c r="D23" t="n">
-        <v>49.78173998791892</v>
+        <v>49.60484583115361</v>
       </c>
       <c r="E23" t="n">
         <v>101.1765739559945</v>
@@ -3545,7 +3545,7 @@
         <v>203.3015774098458</v>
       </c>
       <c r="G23" t="n">
-        <v>94.66869395521077</v>
+        <v>94.62447041601945</v>
       </c>
     </row>
     <row r="24">
@@ -3586,16 +3586,16 @@
         <v>27.55634918610405</v>
       </c>
       <c r="D25" t="n">
-        <v>52.52691193458119</v>
+        <v>54.04163056034262</v>
       </c>
       <c r="E25" t="n">
-        <v>110.3259018078045</v>
+        <v>109.4974746830583</v>
       </c>
       <c r="F25" t="n">
-        <v>219.5807358037436</v>
+        <v>218.7523086789974</v>
       </c>
       <c r="G25" t="n">
-        <v>102.4974746830583</v>
+        <v>102.4619407771256</v>
       </c>
     </row>
     <row r="26">
@@ -3689,13 +3689,13 @@
         <v>49.56011556674471</v>
       </c>
       <c r="E29" t="n">
-        <v>101.1164142094206</v>
+        <v>100.6044505332257</v>
       </c>
       <c r="F29" t="n">
         <v>203.2348880049742</v>
       </c>
       <c r="G29" t="n">
-        <v>94.58157556205583</v>
+        <v>94.45358464300712</v>
       </c>
     </row>
     <row r="30">
@@ -3708,19 +3708,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.41811047550525</v>
+        <v>25.83232403787834</v>
       </c>
       <c r="D30" t="n">
-        <v>49.04921408900104</v>
+        <v>51.44598283082938</v>
       </c>
       <c r="E30" t="n">
-        <v>103.7222775834009</v>
+        <v>103.0023916359005</v>
       </c>
       <c r="F30" t="n">
-        <v>207.7440267546941</v>
+        <v>206.425148898921</v>
       </c>
       <c r="G30" t="n">
-        <v>96.23340722565031</v>
+        <v>96.6764618508823</v>
       </c>
     </row>
     <row r="31">
@@ -3739,13 +3739,13 @@
         <v>51.69848480983499</v>
       </c>
       <c r="E31" t="n">
-        <v>109.4974746830583</v>
+        <v>103.9827560572969</v>
       </c>
       <c r="F31" t="n">
-        <v>218.7523086789974</v>
+        <v>208.5512985522207</v>
       </c>
       <c r="G31" t="n">
-        <v>101.3761543394987</v>
+        <v>97.44722215136416</v>
       </c>
     </row>
     <row r="32">
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>25.55634918610405</v>
+        <v>27.55634918610405</v>
       </c>
       <c r="D33" t="n">
         <v>54.04163056034262</v>
@@ -3795,7 +3795,7 @@
         <v>217.9238815542512</v>
       </c>
       <c r="G33" t="n">
-        <v>101.5477272147525</v>
+        <v>102.0477272147525</v>
       </c>
     </row>
     <row r="34">
@@ -3833,19 +3833,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>23.53271669619603</v>
+        <v>24.41488446708389</v>
       </c>
       <c r="D35" t="n">
-        <v>49.50528473946896</v>
+        <v>50.17391228731556</v>
       </c>
       <c r="E35" t="n">
-        <v>98.58961006939111</v>
+        <v>100.087967763624</v>
       </c>
       <c r="F35" t="n">
-        <v>197.5695114409684</v>
+        <v>200.7176243705014</v>
       </c>
       <c r="G35" t="n">
-        <v>92.29928073650612</v>
+        <v>93.84859722213122</v>
       </c>
     </row>
     <row r="36">
@@ -3858,19 +3858,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>24.90291876522843</v>
+        <v>26.59251907515131</v>
       </c>
       <c r="D36" t="n">
-        <v>51.95837796962023</v>
+        <v>52.62700551746683</v>
       </c>
       <c r="E36" t="n">
-        <v>109.6176879416777</v>
+        <v>105.9675221282317</v>
       </c>
       <c r="F36" t="n">
-        <v>209.6068123063317</v>
+        <v>222.6622168960765</v>
       </c>
       <c r="G36" t="n">
-        <v>99.02144924571451</v>
+        <v>101.9623159042316</v>
       </c>
     </row>
     <row r="37">
@@ -3908,19 +3908,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>24.50457312756027</v>
+        <v>25.38674089844813</v>
       </c>
       <c r="D38" t="n">
-        <v>50.17676995799587</v>
+        <v>50.84539750584248</v>
       </c>
       <c r="E38" t="n">
-        <v>100.1430788450122</v>
+        <v>101.6414365392452</v>
       </c>
       <c r="F38" t="n">
-        <v>200.8525404962239</v>
+        <v>204.0006534257569</v>
       </c>
       <c r="G38" t="n">
-        <v>93.91924060669805</v>
+        <v>95.46855709232315</v>
       </c>
     </row>
     <row r="39">
@@ -3939,13 +3939,13 @@
         <v>49.56011556674471</v>
       </c>
       <c r="E39" t="n">
-        <v>101.1318436915856</v>
+        <v>100.6198800153907</v>
       </c>
       <c r="F39" t="n">
         <v>203.2568471454369</v>
       </c>
       <c r="G39" t="n">
-        <v>94.59092271771277</v>
+        <v>94.46293179866406</v>
       </c>
     </row>
     <row r="40">
@@ -3958,19 +3958,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>26.07297705925549</v>
+        <v>25.71936168599622</v>
       </c>
       <c r="D40" t="n">
-        <v>49.24441272425872</v>
+        <v>51.44598283082938</v>
       </c>
       <c r="E40" t="n">
-        <v>103.8198470130748</v>
+        <v>103.0999610655744</v>
       </c>
       <c r="F40" t="n">
-        <v>207.8890363034826</v>
+        <v>206.5701584477096</v>
       </c>
       <c r="G40" t="n">
-        <v>96.75656827501791</v>
+        <v>96.7088660075274</v>
       </c>
     </row>
     <row r="41">
@@ -3983,19 +3983,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>27.55634918610405</v>
+        <v>25.55634918610405</v>
       </c>
       <c r="D41" t="n">
         <v>52.52691193458119</v>
       </c>
       <c r="E41" t="n">
-        <v>110.3259018078045</v>
+        <v>104.8111831820431</v>
       </c>
       <c r="F41" t="n">
-        <v>219.5807358037436</v>
+        <v>209.3797256769669</v>
       </c>
       <c r="G41" t="n">
-        <v>102.4974746830583</v>
+        <v>98.0685424949238</v>
       </c>
     </row>
     <row r="42">
@@ -4033,19 +4033,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>24.41811047550525</v>
+        <v>24.41488446708389</v>
       </c>
       <c r="D43" t="n">
-        <v>49.04921408900104</v>
+        <v>49.03946295574199</v>
       </c>
       <c r="E43" t="n">
-        <v>103.7222775834009</v>
+        <v>98.78888910980251</v>
       </c>
       <c r="F43" t="n">
-        <v>207.7440267546941</v>
+        <v>198.4048488856638</v>
       </c>
       <c r="G43" t="n">
-        <v>96.23340722565031</v>
+        <v>92.66202135457306</v>
       </c>
     </row>
     <row r="44">
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>23.74064110506006</v>
+        <v>26.59251907515131</v>
       </c>
       <c r="D44" t="n">
-        <v>51.45450616521079</v>
+        <v>52.12313371305741</v>
       </c>
       <c r="E44" t="n">
-        <v>103.46142082518</v>
+        <v>104.9597785194129</v>
       </c>
       <c r="F44" t="n">
-        <v>207.7489479300626</v>
+        <v>210.8970608595957</v>
       </c>
       <c r="G44" t="n">
-        <v>96.60137900637835</v>
+        <v>98.6431230418043</v>
       </c>
     </row>
     <row r="45">
@@ -4108,19 +4108,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>24.83719391510835</v>
+        <v>25.71936168599622</v>
       </c>
       <c r="D46" t="n">
-        <v>51.45450616521079</v>
+        <v>52.12313371305741</v>
       </c>
       <c r="E46" t="n">
-        <v>103.46142082518</v>
+        <v>104.9597785194129</v>
       </c>
       <c r="F46" t="n">
-        <v>207.7489479300626</v>
+        <v>210.8970608595957</v>
       </c>
       <c r="G46" t="n">
-        <v>96.87551720889043</v>
+        <v>98.42483369451554</v>
       </c>
     </row>
     <row r="47">
@@ -4133,19 +4133,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>24.83719391510835</v>
+        <v>25.71936168599622</v>
       </c>
       <c r="D47" t="n">
-        <v>51.95837796962023</v>
+        <v>52.62700551746683</v>
       </c>
       <c r="E47" t="n">
-        <v>104.4691644339988</v>
+        <v>105.9675221282317</v>
       </c>
       <c r="F47" t="n">
-        <v>209.6068123063317</v>
+        <v>212.7549252358647</v>
       </c>
       <c r="G47" t="n">
-        <v>97.71788715626477</v>
+        <v>99.26720364188988</v>
       </c>
     </row>
     <row r="48">
@@ -4158,19 +4158,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>26.07297705925549</v>
+        <v>24.41488446708389</v>
       </c>
       <c r="D48" t="n">
-        <v>49.24441272425872</v>
+        <v>49.21635711250729</v>
       </c>
       <c r="E48" t="n">
-        <v>103.8198470130748</v>
+        <v>98.78888910980251</v>
       </c>
       <c r="F48" t="n">
-        <v>207.8890363034826</v>
+        <v>198.4048488856638</v>
       </c>
       <c r="G48" t="n">
-        <v>96.75656827501791</v>
+        <v>92.70624489376438</v>
       </c>
     </row>
     <row r="49">
@@ -4183,19 +4183,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>24.83719391510835</v>
+        <v>25.71936168599622</v>
       </c>
       <c r="D49" t="n">
-        <v>51.45450616521079</v>
+        <v>52.12313371305741</v>
       </c>
       <c r="E49" t="n">
-        <v>103.46142082518</v>
+        <v>104.9597785194129</v>
       </c>
       <c r="F49" t="n">
-        <v>207.7489479300626</v>
+        <v>210.8970608595957</v>
       </c>
       <c r="G49" t="n">
-        <v>96.87551720889043</v>
+        <v>98.42483369451554</v>
       </c>
     </row>
   </sheetData>
@@ -4309,19 +4309,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E4" t="n">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F4" t="n">
-        <v>671</v>
+        <v>606</v>
       </c>
       <c r="G4" t="n">
-        <v>268.5</v>
+        <v>252.75</v>
       </c>
     </row>
     <row r="5">
@@ -4434,19 +4434,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D9" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E9" t="n">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="F9" t="n">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="G9" t="n">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10">
@@ -4534,19 +4534,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E13" t="n">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F13" t="n">
-        <v>671</v>
+        <v>606</v>
       </c>
       <c r="G13" t="n">
-        <v>268.5</v>
+        <v>252.75</v>
       </c>
     </row>
     <row r="14">
@@ -4559,19 +4559,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E14" t="n">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="F14" t="n">
-        <v>673</v>
+        <v>628</v>
       </c>
       <c r="G14" t="n">
-        <v>272.25</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15">
@@ -4584,19 +4584,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D15" t="n">
         <v>90</v>
       </c>
       <c r="E15" t="n">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F15" t="n">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="G15" t="n">
-        <v>210.75</v>
+        <v>196.25</v>
       </c>
     </row>
     <row r="16">
@@ -4684,19 +4684,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
+        <v>12</v>
+      </c>
+      <c r="E19" t="n">
         <v>13</v>
       </c>
-      <c r="E19" t="n">
-        <v>15</v>
-      </c>
       <c r="F19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G19" t="n">
-        <v>13.5</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="20">
@@ -4784,19 +4784,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D23" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E23" t="n">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="F23" t="n">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="G23" t="n">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24">
@@ -4812,16 +4812,16 @@
         <v>34</v>
       </c>
       <c r="D24" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E24" t="n">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="F24" t="n">
-        <v>581</v>
+        <v>508</v>
       </c>
       <c r="G24" t="n">
-        <v>237</v>
+        <v>220.75</v>
       </c>
     </row>
     <row r="25">
@@ -4834,19 +4834,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D25" t="n">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="E25" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F25" t="n">
-        <v>452</v>
+        <v>475</v>
       </c>
       <c r="G25" t="n">
-        <v>207.75</v>
+        <v>207.25</v>
       </c>
     </row>
     <row r="26">
@@ -4934,19 +4934,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D29" t="n">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E29" t="n">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="F29" t="n">
-        <v>673</v>
+        <v>628</v>
       </c>
       <c r="G29" t="n">
-        <v>272.25</v>
+        <v>253</v>
       </c>
     </row>
     <row r="30">
@@ -4959,19 +4959,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D30" t="n">
         <v>90</v>
       </c>
       <c r="E30" t="n">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F30" t="n">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="G30" t="n">
-        <v>210.75</v>
+        <v>196.25</v>
       </c>
     </row>
     <row r="31">
@@ -4984,19 +4984,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D31" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E31" t="n">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="F31" t="n">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="G31" t="n">
-        <v>223.75</v>
+        <v>221.5</v>
       </c>
     </row>
     <row r="32">
@@ -5043,10 +5043,10 @@
         <v>17</v>
       </c>
       <c r="F33" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G33" t="n">
-        <v>16.25</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="34">
@@ -5109,19 +5109,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D36" t="n">
+        <v>12</v>
+      </c>
+      <c r="E36" t="n">
         <v>13</v>
       </c>
-      <c r="E36" t="n">
-        <v>15</v>
-      </c>
       <c r="F36" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G36" t="n">
-        <v>13.5</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="37">
@@ -5140,13 +5140,13 @@
         <v>13</v>
       </c>
       <c r="E37" t="n">
+        <v>11</v>
+      </c>
+      <c r="F37" t="n">
         <v>12</v>
       </c>
-      <c r="F37" t="n">
-        <v>13</v>
-      </c>
       <c r="G37" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38">
@@ -5187,16 +5187,16 @@
         <v>34</v>
       </c>
       <c r="D39" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E39" t="n">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="F39" t="n">
-        <v>581</v>
+        <v>508</v>
       </c>
       <c r="G39" t="n">
-        <v>237</v>
+        <v>220.75</v>
       </c>
     </row>
     <row r="40">
@@ -5209,19 +5209,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D40" t="n">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="E40" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F40" t="n">
-        <v>452</v>
+        <v>475</v>
       </c>
       <c r="G40" t="n">
-        <v>207.75</v>
+        <v>207.25</v>
       </c>
     </row>
     <row r="41">
@@ -5234,19 +5234,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D41" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E41" t="n">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="F41" t="n">
-        <v>518</v>
+        <v>605</v>
       </c>
       <c r="G41" t="n">
-        <v>231</v>
+        <v>259.5</v>
       </c>
     </row>
     <row r="42">
@@ -5284,19 +5284,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D43" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E43" t="n">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="F43" t="n">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="G43" t="n">
-        <v>223.75</v>
+        <v>221.5</v>
       </c>
     </row>
     <row r="44">
@@ -5318,10 +5318,10 @@
         <v>17</v>
       </c>
       <c r="F44" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G44" t="n">
-        <v>16.25</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="45">
@@ -5340,13 +5340,13 @@
         <v>20</v>
       </c>
       <c r="E45" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F45" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G45" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46">
@@ -5390,13 +5390,13 @@
         <v>13</v>
       </c>
       <c r="E47" t="n">
+        <v>11</v>
+      </c>
+      <c r="F47" t="n">
         <v>12</v>
       </c>
-      <c r="F47" t="n">
-        <v>13</v>
-      </c>
       <c r="G47" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48">
@@ -5409,19 +5409,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D48" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E48" t="n">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="F48" t="n">
-        <v>518</v>
+        <v>605</v>
       </c>
       <c r="G48" t="n">
-        <v>231</v>
+        <v>259.5</v>
       </c>
     </row>
     <row r="49">
@@ -5440,13 +5440,13 @@
         <v>20</v>
       </c>
       <c r="E49" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F49" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G49" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -5560,19 +5560,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D4" t="n">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="E4" t="n">
-        <v>410</v>
+        <v>365</v>
       </c>
       <c r="F4" t="n">
-        <v>2280</v>
+        <v>2113</v>
       </c>
       <c r="G4" t="n">
-        <v>703.5</v>
+        <v>646.75</v>
       </c>
     </row>
     <row r="5">
@@ -5688,16 +5688,16 @@
         <v>41</v>
       </c>
       <c r="D9" t="n">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E9" t="n">
-        <v>496</v>
+        <v>463</v>
       </c>
       <c r="F9" t="n">
-        <v>1909</v>
+        <v>1824</v>
       </c>
       <c r="G9" t="n">
-        <v>644</v>
+        <v>613</v>
       </c>
     </row>
     <row r="10">
@@ -5785,19 +5785,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D13" t="n">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="E13" t="n">
-        <v>410</v>
+        <v>365</v>
       </c>
       <c r="F13" t="n">
-        <v>2280</v>
+        <v>2113</v>
       </c>
       <c r="G13" t="n">
-        <v>703.5</v>
+        <v>646.75</v>
       </c>
     </row>
     <row r="14">
@@ -5810,19 +5810,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D14" t="n">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E14" t="n">
-        <v>410</v>
+        <v>353</v>
       </c>
       <c r="F14" t="n">
-        <v>2242</v>
+        <v>2096</v>
       </c>
       <c r="G14" t="n">
-        <v>694</v>
+        <v>639.75</v>
       </c>
     </row>
     <row r="15">
@@ -5835,19 +5835,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E15" t="n">
-        <v>525</v>
+        <v>478</v>
       </c>
       <c r="F15" t="n">
-        <v>2852</v>
+        <v>2444</v>
       </c>
       <c r="G15" t="n">
-        <v>881.5</v>
+        <v>767.75</v>
       </c>
     </row>
     <row r="16">
@@ -5935,19 +5935,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D19" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E19" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F19" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G19" t="n">
-        <v>34</v>
+        <v>31.25</v>
       </c>
     </row>
     <row r="20">
@@ -6038,16 +6038,16 @@
         <v>41</v>
       </c>
       <c r="D23" t="n">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E23" t="n">
-        <v>496</v>
+        <v>463</v>
       </c>
       <c r="F23" t="n">
-        <v>1909</v>
+        <v>1824</v>
       </c>
       <c r="G23" t="n">
-        <v>644</v>
+        <v>613</v>
       </c>
     </row>
     <row r="24">
@@ -6060,19 +6060,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D24" t="n">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E24" t="n">
-        <v>526</v>
+        <v>478</v>
       </c>
       <c r="F24" t="n">
-        <v>2111</v>
+        <v>1954</v>
       </c>
       <c r="G24" t="n">
-        <v>703.25</v>
+        <v>650</v>
       </c>
     </row>
     <row r="25">
@@ -6085,19 +6085,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D25" t="n">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="E25" t="n">
-        <v>645</v>
+        <v>605</v>
       </c>
       <c r="F25" t="n">
-        <v>2471</v>
+        <v>2384</v>
       </c>
       <c r="G25" t="n">
-        <v>836.75</v>
+        <v>800</v>
       </c>
     </row>
     <row r="26">
@@ -6185,19 +6185,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D29" t="n">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E29" t="n">
-        <v>410</v>
+        <v>353</v>
       </c>
       <c r="F29" t="n">
-        <v>2242</v>
+        <v>2096</v>
       </c>
       <c r="G29" t="n">
-        <v>694</v>
+        <v>639.75</v>
       </c>
     </row>
     <row r="30">
@@ -6210,19 +6210,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D30" t="n">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E30" t="n">
-        <v>525</v>
+        <v>478</v>
       </c>
       <c r="F30" t="n">
-        <v>2852</v>
+        <v>2444</v>
       </c>
       <c r="G30" t="n">
-        <v>881.5</v>
+        <v>767.75</v>
       </c>
     </row>
     <row r="31">
@@ -6235,19 +6235,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D31" t="n">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="E31" t="n">
-        <v>529</v>
+        <v>454</v>
       </c>
       <c r="F31" t="n">
-        <v>2864</v>
+        <v>2132</v>
       </c>
       <c r="G31" t="n">
-        <v>886.25</v>
+        <v>683.25</v>
       </c>
     </row>
     <row r="32">
@@ -6285,19 +6285,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D33" t="n">
         <v>38</v>
       </c>
       <c r="E33" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F33" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G33" t="n">
-        <v>36.25</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="34">
@@ -6360,19 +6360,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D36" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E36" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F36" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G36" t="n">
-        <v>34</v>
+        <v>31.25</v>
       </c>
     </row>
     <row r="37">
@@ -6388,16 +6388,16 @@
         <v>20</v>
       </c>
       <c r="D37" t="n">
+        <v>33</v>
+      </c>
+      <c r="E37" t="n">
+        <v>33</v>
+      </c>
+      <c r="F37" t="n">
         <v>38</v>
       </c>
-      <c r="E37" t="n">
-        <v>37</v>
-      </c>
-      <c r="F37" t="n">
-        <v>45</v>
-      </c>
       <c r="G37" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38">
@@ -6435,19 +6435,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D39" t="n">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E39" t="n">
-        <v>526</v>
+        <v>478</v>
       </c>
       <c r="F39" t="n">
-        <v>2111</v>
+        <v>1954</v>
       </c>
       <c r="G39" t="n">
-        <v>703.25</v>
+        <v>650</v>
       </c>
     </row>
     <row r="40">
@@ -6460,19 +6460,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D40" t="n">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="E40" t="n">
-        <v>645</v>
+        <v>605</v>
       </c>
       <c r="F40" t="n">
-        <v>2471</v>
+        <v>2384</v>
       </c>
       <c r="G40" t="n">
-        <v>836.75</v>
+        <v>800</v>
       </c>
     </row>
     <row r="41">
@@ -6485,19 +6485,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D41" t="n">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="E41" t="n">
-        <v>697</v>
+        <v>657</v>
       </c>
       <c r="F41" t="n">
-        <v>2585</v>
+        <v>2515</v>
       </c>
       <c r="G41" t="n">
-        <v>881.5</v>
+        <v>851.75</v>
       </c>
     </row>
     <row r="42">
@@ -6535,19 +6535,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D43" t="n">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="E43" t="n">
-        <v>529</v>
+        <v>454</v>
       </c>
       <c r="F43" t="n">
-        <v>2864</v>
+        <v>2132</v>
       </c>
       <c r="G43" t="n">
-        <v>886.25</v>
+        <v>683.25</v>
       </c>
     </row>
     <row r="44">
@@ -6560,19 +6560,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D44" t="n">
         <v>38</v>
       </c>
       <c r="E44" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F44" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G44" t="n">
-        <v>36.25</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="45">
@@ -6588,16 +6588,16 @@
         <v>23</v>
       </c>
       <c r="D45" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E45" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F45" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G45" t="n">
-        <v>38.25</v>
+        <v>35.75</v>
       </c>
     </row>
     <row r="46">
@@ -6638,16 +6638,16 @@
         <v>20</v>
       </c>
       <c r="D47" t="n">
+        <v>33</v>
+      </c>
+      <c r="E47" t="n">
+        <v>33</v>
+      </c>
+      <c r="F47" t="n">
         <v>38</v>
       </c>
-      <c r="E47" t="n">
-        <v>37</v>
-      </c>
-      <c r="F47" t="n">
-        <v>45</v>
-      </c>
       <c r="G47" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48">
@@ -6660,19 +6660,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D48" t="n">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="E48" t="n">
-        <v>697</v>
+        <v>657</v>
       </c>
       <c r="F48" t="n">
-        <v>2585</v>
+        <v>2515</v>
       </c>
       <c r="G48" t="n">
-        <v>881.5</v>
+        <v>851.75</v>
       </c>
     </row>
     <row r="49">
@@ -6688,16 +6688,16 @@
         <v>23</v>
       </c>
       <c r="D49" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E49" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F49" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G49" t="n">
-        <v>38.25</v>
+        <v>35.75</v>
       </c>
     </row>
   </sheetData>
@@ -6814,16 +6814,16 @@
         <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G4" t="n">
-        <v>16.75</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="5">
@@ -6936,19 +6936,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
         <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G9" t="n">
-        <v>15</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="10">
@@ -7036,7 +7036,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
         <v>6</v>
@@ -7048,7 +7048,7 @@
         <v>7</v>
       </c>
       <c r="G13" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="14">
@@ -7061,7 +7061,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
         <v>12</v>
@@ -7073,7 +7073,7 @@
         <v>18</v>
       </c>
       <c r="G14" t="n">
-        <v>13.5</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="15">
@@ -7086,19 +7086,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F15" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G15" t="n">
-        <v>13.5</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="16">
@@ -7186,19 +7186,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D19" t="n">
         <v>13</v>
       </c>
       <c r="E19" t="n">
+        <v>13</v>
+      </c>
+      <c r="F19" t="n">
         <v>15</v>
       </c>
-      <c r="F19" t="n">
-        <v>13</v>
-      </c>
       <c r="G19" t="n">
-        <v>13.25</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="20">
@@ -7236,19 +7236,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G21" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="22">
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D24" t="n">
         <v>11</v>
@@ -7323,7 +7323,7 @@
         <v>12</v>
       </c>
       <c r="G24" t="n">
-        <v>12</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="25">
@@ -7336,19 +7336,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D25" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E25" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F25" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G25" t="n">
-        <v>16.75</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26">
@@ -7461,10 +7461,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E30" t="n">
         <v>7</v>
@@ -7473,7 +7473,7 @@
         <v>7</v>
       </c>
       <c r="G30" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="31">
@@ -7486,19 +7486,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D31" t="n">
         <v>12</v>
       </c>
       <c r="E31" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F31" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G31" t="n">
-        <v>13.5</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="32">
@@ -7536,7 +7536,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D33" t="n">
         <v>14</v>
@@ -7548,7 +7548,7 @@
         <v>14</v>
       </c>
       <c r="G33" t="n">
-        <v>13.25</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="34">
@@ -7586,19 +7586,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G35" t="n">
-        <v>5.75</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="36">
@@ -7611,19 +7611,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D36" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E36" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F36" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G36" t="n">
-        <v>8.5</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="37">
@@ -7661,19 +7661,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G38" t="n">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="39">
@@ -7714,7 +7714,7 @@
         <v>7</v>
       </c>
       <c r="D40" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E40" t="n">
         <v>8</v>
@@ -7723,7 +7723,7 @@
         <v>8</v>
       </c>
       <c r="G40" t="n">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="41">
@@ -7736,19 +7736,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D41" t="n">
         <v>13</v>
       </c>
       <c r="E41" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F41" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G41" t="n">
-        <v>16.25</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="42">
@@ -7786,19 +7786,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D43" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E43" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F43" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G43" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
@@ -7811,19 +7811,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F44" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G44" t="n">
-        <v>6.75</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="45">
@@ -7861,19 +7861,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F46" t="n">
+        <v>9</v>
+      </c>
+      <c r="G46" t="n">
         <v>8</v>
-      </c>
-      <c r="G46" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="47">
@@ -7886,19 +7886,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G47" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="48">
@@ -7911,19 +7911,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D48" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E48" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F48" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G48" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49">
@@ -7936,19 +7936,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D49" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E49" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F49" t="n">
+        <v>9</v>
+      </c>
+      <c r="G49" t="n">
         <v>8</v>
-      </c>
-      <c r="G49" t="n">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -8037,16 +8037,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C4" t="n">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="D4" t="n">
-        <v>684</v>
+        <v>641</v>
       </c>
       <c r="E4" t="n">
-        <v>2951</v>
+        <v>2719</v>
       </c>
     </row>
     <row r="5">
@@ -8132,16 +8132,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C9" t="n">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="D9" t="n">
-        <v>774</v>
+        <v>750</v>
       </c>
       <c r="E9" t="n">
-        <v>2540</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="10">
@@ -8208,16 +8208,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C13" t="n">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="D13" t="n">
-        <v>684</v>
+        <v>641</v>
       </c>
       <c r="E13" t="n">
-        <v>2951</v>
+        <v>2719</v>
       </c>
     </row>
     <row r="14">
@@ -8227,16 +8227,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C14" t="n">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="D14" t="n">
-        <v>693</v>
+        <v>609</v>
       </c>
       <c r="E14" t="n">
-        <v>2915</v>
+        <v>2724</v>
       </c>
     </row>
     <row r="15">
@@ -8246,16 +8246,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C15" t="n">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D15" t="n">
-        <v>750</v>
+        <v>689</v>
       </c>
       <c r="E15" t="n">
-        <v>3349</v>
+        <v>2899</v>
       </c>
     </row>
     <row r="16">
@@ -8322,16 +8322,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C19" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D19" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E19" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20">
@@ -8398,16 +8398,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C23" t="n">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="D23" t="n">
-        <v>774</v>
+        <v>750</v>
       </c>
       <c r="E23" t="n">
-        <v>2540</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="24">
@@ -8417,16 +8417,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C24" t="n">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="D24" t="n">
-        <v>766</v>
+        <v>727</v>
       </c>
       <c r="E24" t="n">
-        <v>2692</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="25">
@@ -8439,13 +8439,13 @@
         <v>80</v>
       </c>
       <c r="C25" t="n">
-        <v>301</v>
+        <v>255</v>
       </c>
       <c r="D25" t="n">
-        <v>874</v>
+        <v>835</v>
       </c>
       <c r="E25" t="n">
-        <v>2923</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="26">
@@ -8512,16 +8512,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C29" t="n">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="D29" t="n">
-        <v>693</v>
+        <v>609</v>
       </c>
       <c r="E29" t="n">
-        <v>2915</v>
+        <v>2724</v>
       </c>
     </row>
     <row r="30">
@@ -8531,16 +8531,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C30" t="n">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D30" t="n">
-        <v>750</v>
+        <v>689</v>
       </c>
       <c r="E30" t="n">
-        <v>3349</v>
+        <v>2899</v>
       </c>
     </row>
     <row r="31">
@@ -8550,16 +8550,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C31" t="n">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D31" t="n">
-        <v>771</v>
+        <v>688</v>
       </c>
       <c r="E31" t="n">
-        <v>3397</v>
+        <v>2663</v>
       </c>
     </row>
     <row r="32">
@@ -8588,16 +8588,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C33" t="n">
         <v>55</v>
       </c>
       <c r="D33" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E33" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34">
@@ -8645,16 +8645,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C36" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D36" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E36" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37">
@@ -8667,13 +8667,13 @@
         <v>32</v>
       </c>
       <c r="C37" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D37" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E37" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="38">
@@ -8702,16 +8702,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C39" t="n">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="D39" t="n">
-        <v>766</v>
+        <v>727</v>
       </c>
       <c r="E39" t="n">
-        <v>2692</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="40">
@@ -8724,13 +8724,13 @@
         <v>80</v>
       </c>
       <c r="C40" t="n">
-        <v>301</v>
+        <v>255</v>
       </c>
       <c r="D40" t="n">
-        <v>874</v>
+        <v>835</v>
       </c>
       <c r="E40" t="n">
-        <v>2923</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="41">
@@ -8740,16 +8740,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="C41" t="n">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="D41" t="n">
-        <v>957</v>
+        <v>936</v>
       </c>
       <c r="E41" t="n">
-        <v>3103</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="42">
@@ -8778,16 +8778,16 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C43" t="n">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D43" t="n">
-        <v>771</v>
+        <v>688</v>
       </c>
       <c r="E43" t="n">
-        <v>3397</v>
+        <v>2663</v>
       </c>
     </row>
     <row r="44">
@@ -8797,16 +8797,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C44" t="n">
         <v>55</v>
       </c>
       <c r="D44" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E44" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45">
@@ -8819,13 +8819,13 @@
         <v>36</v>
       </c>
       <c r="C45" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D45" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E45" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="46">
@@ -8857,13 +8857,13 @@
         <v>32</v>
       </c>
       <c r="C47" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D47" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E47" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="48">
@@ -8873,16 +8873,16 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="C48" t="n">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="D48" t="n">
-        <v>957</v>
+        <v>936</v>
       </c>
       <c r="E48" t="n">
-        <v>3103</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="49">
@@ -8895,13 +8895,13 @@
         <v>36</v>
       </c>
       <c r="C49" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D49" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E49" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Validasi/Hasil_Pengujian_Map_1_128_avg_length.xlsx
+++ b/Excel/Validasi/Hasil_Pengujian_Map_1_128_avg_length.xlsx
@@ -506,19 +506,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.000488</v>
+        <v>0.0004585</v>
       </c>
       <c r="D2" t="n">
-        <v>0.002934</v>
+        <v>0.0028168</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0191111</v>
+        <v>0.0190411</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1264418</v>
+        <v>0.121997</v>
       </c>
       <c r="G2" t="n">
-        <v>0.037243725</v>
+        <v>0.03607835</v>
       </c>
     </row>
     <row r="3">
@@ -531,19 +531,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.0003022</v>
+        <v>0.0003069</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0011951</v>
+        <v>0.0012239</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0049929</v>
+        <v>0.0048175</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0208262</v>
+        <v>0.0200653</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006829100000000001</v>
+        <v>0.006603400000000001</v>
       </c>
     </row>
     <row r="4">
@@ -556,19 +556,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0004053</v>
+        <v>0.0005399</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0018053</v>
+        <v>0.0018485</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0142213</v>
+        <v>0.0163242</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1646243</v>
+        <v>0.1526633</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04526405</v>
+        <v>0.042843975</v>
       </c>
     </row>
     <row r="5">
@@ -581,19 +581,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.0003970999999999999</v>
+        <v>0.0003932</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0023637</v>
+        <v>0.0023093</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0155513</v>
+        <v>0.0154216</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1113312</v>
+        <v>0.1059115</v>
       </c>
       <c r="G5" t="n">
-        <v>0.032410825</v>
+        <v>0.0310089</v>
       </c>
     </row>
     <row r="6">
@@ -606,19 +606,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0003778</v>
+        <v>0.0003333</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0009717</v>
+        <v>0.0009808</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0033759</v>
+        <v>0.003392399999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.012292</v>
+        <v>0.0122929</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00425435</v>
+        <v>0.004249849999999999</v>
       </c>
     </row>
     <row r="7">
@@ -631,19 +631,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0006016000000000001</v>
+        <v>0.000512</v>
       </c>
       <c r="D7" t="n">
-        <v>0.003082</v>
+        <v>0.0029314</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0195018</v>
+        <v>0.0183713</v>
       </c>
       <c r="F7" t="n">
-        <v>0.127873</v>
+        <v>0.1215531</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0377646</v>
+        <v>0.03584195</v>
       </c>
     </row>
     <row r="8">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0005254999999999999</v>
+        <v>0.000531</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0027902</v>
+        <v>0.0027971</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0178527</v>
+        <v>0.017198</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1198106</v>
+        <v>0.117049</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03524475</v>
+        <v>0.034393775</v>
       </c>
     </row>
     <row r="9">
@@ -681,19 +681,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0004429</v>
+        <v>0.0004536999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0016992</v>
+        <v>0.0019769</v>
       </c>
       <c r="E9" t="n">
-        <v>0.008820700000000001</v>
+        <v>0.0121841</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0528004</v>
+        <v>0.08451460000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0159408</v>
+        <v>0.024782325</v>
       </c>
     </row>
     <row r="10">
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0003189</v>
+        <v>0.0003224</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0013871</v>
+        <v>0.001383</v>
       </c>
       <c r="E10" t="n">
-        <v>0.005935</v>
+        <v>0.0057414</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0249958</v>
+        <v>0.024999</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0081592</v>
+        <v>0.008111449999999999</v>
       </c>
     </row>
     <row r="11">
@@ -731,19 +731,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0003365</v>
+        <v>0.0003191</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0013536</v>
+        <v>0.0013039</v>
       </c>
       <c r="E11" t="n">
-        <v>0.005054500000000001</v>
+        <v>0.0051039</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0217027</v>
+        <v>0.0209627</v>
       </c>
       <c r="G11" t="n">
-        <v>0.007111825</v>
+        <v>0.0069224</v>
       </c>
     </row>
     <row r="12">
@@ -756,19 +756,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0003193</v>
+        <v>0.0003317</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0014867</v>
+        <v>0.0014245</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0054447</v>
+        <v>0.005322</v>
       </c>
       <c r="F12" t="n">
-        <v>0.021916</v>
+        <v>0.0213904</v>
       </c>
       <c r="G12" t="n">
-        <v>0.007291674999999999</v>
+        <v>0.00711715</v>
       </c>
     </row>
     <row r="13">
@@ -781,19 +781,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0004682000000000001</v>
+        <v>0.0005563</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0019299</v>
+        <v>0.0020061</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0142374</v>
+        <v>0.0168071</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1669026</v>
+        <v>0.1526683</v>
       </c>
       <c r="G13" t="n">
-        <v>0.045884525</v>
+        <v>0.04300945</v>
       </c>
     </row>
     <row r="14">
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0004872</v>
+        <v>0.0005176</v>
       </c>
       <c r="D14" t="n">
-        <v>0.001915</v>
+        <v>0.001937</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0138306</v>
+        <v>0.0183092</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1616847</v>
+        <v>0.1633502</v>
       </c>
       <c r="G14" t="n">
-        <v>0.04447937499999999</v>
+        <v>0.0460285</v>
       </c>
     </row>
     <row r="15">
@@ -831,19 +831,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0005844</v>
+        <v>0.0005661</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0026095</v>
+        <v>0.0025919</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0183228</v>
+        <v>0.0192865</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1764387</v>
+        <v>0.1745935</v>
       </c>
       <c r="G15" t="n">
-        <v>0.04948885</v>
+        <v>0.0492595</v>
       </c>
     </row>
     <row r="16">
@@ -856,19 +856,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0004614</v>
+        <v>0.0004626</v>
       </c>
       <c r="D16" t="n">
-        <v>0.00241</v>
+        <v>0.0023947</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0156817</v>
+        <v>0.0154221</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1132413</v>
+        <v>0.1068417</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0329486</v>
+        <v>0.031280275</v>
       </c>
     </row>
     <row r="17">
@@ -881,19 +881,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0005739</v>
+        <v>0.0005595</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0035986</v>
+        <v>0.0033448</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0158411</v>
+        <v>0.0153551</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1056952</v>
+        <v>0.1014004</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0314272</v>
+        <v>0.03016495</v>
       </c>
     </row>
     <row r="18">
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0003591</v>
+        <v>0.0003228999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>0.00098</v>
+        <v>0.000915</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0028888</v>
+        <v>0.0028975</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0108466</v>
+        <v>0.010835</v>
       </c>
       <c r="G18" t="n">
-        <v>0.003768625</v>
+        <v>0.0037426</v>
       </c>
     </row>
     <row r="19">
@@ -931,19 +931,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0003145</v>
+        <v>0.0003366</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0008716999999999999</v>
+        <v>0.0009219999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0025937</v>
+        <v>0.0029943</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0121766</v>
+        <v>0.0106857</v>
       </c>
       <c r="G19" t="n">
-        <v>0.003989125</v>
+        <v>0.00373465</v>
       </c>
     </row>
     <row r="20">
@@ -956,19 +956,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.000361</v>
+        <v>0.0003364999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0011302</v>
+        <v>0.0010501</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0036276</v>
+        <v>0.0036458</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0133442</v>
+        <v>0.0131556</v>
       </c>
       <c r="G20" t="n">
-        <v>0.00461575</v>
+        <v>0.004547</v>
       </c>
     </row>
     <row r="21">
@@ -981,19 +981,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0003751</v>
+        <v>0.0003587999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0011003</v>
+        <v>0.0009927</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0034493</v>
+        <v>0.0033916</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0122192</v>
+        <v>0.0123284</v>
       </c>
       <c r="G21" t="n">
-        <v>0.004285975</v>
+        <v>0.004267874999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1006,19 +1006,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0005897000000000001</v>
+        <v>0.0005886999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0029227</v>
+        <v>0.0028023</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0182536</v>
+        <v>0.0172376</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1212913</v>
+        <v>0.117096</v>
       </c>
       <c r="G22" t="n">
-        <v>0.035764325</v>
+        <v>0.03443115</v>
       </c>
     </row>
     <row r="23">
@@ -1031,19 +1031,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0005002</v>
+        <v>0.0004895</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0017475</v>
+        <v>0.002076</v>
       </c>
       <c r="E23" t="n">
-        <v>0.008291099999999999</v>
+        <v>0.0126124</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0530564</v>
+        <v>0.0852088</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0158988</v>
+        <v>0.025096675</v>
       </c>
     </row>
     <row r="24">
@@ -1056,19 +1056,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0005290999999999999</v>
+        <v>0.0005012</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0017723</v>
+        <v>0.0021151</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0085497</v>
+        <v>0.0127391</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0533539</v>
+        <v>0.08367049999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>0.01605125</v>
+        <v>0.024756475</v>
       </c>
     </row>
     <row r="25">
@@ -1081,19 +1081,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0005549</v>
+        <v>0.0005079000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0023584</v>
+        <v>0.0026978</v>
       </c>
       <c r="E25" t="n">
-        <v>0.012572</v>
+        <v>0.0159835</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0846522</v>
+        <v>0.1215122</v>
       </c>
       <c r="G25" t="n">
-        <v>0.025034375</v>
+        <v>0.03517535</v>
       </c>
     </row>
     <row r="26">
@@ -1106,19 +1106,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0003788</v>
+        <v>0.0003762</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0015154</v>
+        <v>0.0014629</v>
       </c>
       <c r="E26" t="n">
-        <v>0.006075</v>
+        <v>0.0073336</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0262154</v>
+        <v>0.025562</v>
       </c>
       <c r="G26" t="n">
-        <v>0.008546149999999999</v>
+        <v>0.008683675</v>
       </c>
     </row>
     <row r="27">
@@ -1131,19 +1131,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0003761</v>
+        <v>0.0003649</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0016044</v>
+        <v>0.0016179</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0063856</v>
+        <v>0.0062774</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0264375</v>
+        <v>0.0266712</v>
       </c>
       <c r="G27" t="n">
-        <v>0.008700899999999999</v>
+        <v>0.008732849999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1156,19 +1156,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.000369</v>
+        <v>0.0003608</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0015119</v>
+        <v>0.0015419</v>
       </c>
       <c r="E28" t="n">
-        <v>0.005735599999999999</v>
+        <v>0.0055933</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0228551</v>
+        <v>0.0221864</v>
       </c>
       <c r="G28" t="n">
-        <v>0.007617899999999999</v>
+        <v>0.007420599999999999</v>
       </c>
     </row>
     <row r="29">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0005112000000000001</v>
+        <v>0.000537</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0020943</v>
+        <v>0.0019312</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0142882</v>
+        <v>0.0186731</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1643884</v>
+        <v>0.1643973</v>
       </c>
       <c r="G29" t="n">
-        <v>0.045320525</v>
+        <v>0.04638465000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1206,19 +1206,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0006200999999999999</v>
+        <v>0.0005811999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0025644</v>
+        <v>0.0026649</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0187376</v>
+        <v>0.0201055</v>
       </c>
       <c r="F30" t="n">
-        <v>0.179151</v>
+        <v>0.1749841</v>
       </c>
       <c r="G30" t="n">
-        <v>0.050268275</v>
+        <v>0.04958392500000001</v>
       </c>
     </row>
     <row r="31">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0006041</v>
+        <v>0.0005631</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0027139</v>
+        <v>0.002918599999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0179335</v>
+        <v>0.0205008</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1518734</v>
+        <v>0.1938393</v>
       </c>
       <c r="G31" t="n">
-        <v>0.043281225</v>
+        <v>0.05445545</v>
       </c>
     </row>
     <row r="32">
@@ -1256,19 +1256,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0006119</v>
+        <v>0.0006108000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0035223</v>
+        <v>0.0033888</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0160673</v>
+        <v>0.0156853</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1078077</v>
+        <v>0.1025261</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0320023</v>
+        <v>0.03055275</v>
       </c>
     </row>
     <row r="33">
@@ -1281,19 +1281,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0004094</v>
+        <v>0.0002847</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0011284</v>
+        <v>0.0009162</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0032717</v>
+        <v>0.002679400000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0107584</v>
+        <v>0.0082586</v>
       </c>
       <c r="G33" t="n">
-        <v>0.003891975</v>
+        <v>0.003034725</v>
       </c>
     </row>
     <row r="34">
@@ -1306,19 +1306,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0003128000000000001</v>
+        <v>0.0002686</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0010323</v>
+        <v>0.0009722999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0029806</v>
+        <v>0.0029487</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0113632</v>
+        <v>0.0110795</v>
       </c>
       <c r="G34" t="n">
-        <v>0.003922225000000001</v>
+        <v>0.003817275</v>
       </c>
     </row>
     <row r="35">
@@ -1331,19 +1331,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0004091</v>
+        <v>0.0003697999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0009947999999999999</v>
+        <v>0.0009679000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0029447</v>
+        <v>0.0029392</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0111221</v>
+        <v>0.0109433</v>
       </c>
       <c r="G35" t="n">
-        <v>0.003867675</v>
+        <v>0.00380505</v>
       </c>
     </row>
     <row r="36">
@@ -1356,19 +1356,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0003565</v>
+        <v>0.0003255</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0009288999999999999</v>
+        <v>0.0009538000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0025786</v>
+        <v>0.0030312</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0121538</v>
+        <v>0.0109231</v>
       </c>
       <c r="G36" t="n">
-        <v>0.00400445</v>
+        <v>0.0038084</v>
       </c>
     </row>
     <row r="37">
@@ -1381,19 +1381,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.000322</v>
+        <v>0.0003422</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0009711000000000001</v>
+        <v>0.0010449</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0026808</v>
+        <v>0.003267299999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0114559</v>
+        <v>0.0113351</v>
       </c>
       <c r="G37" t="n">
-        <v>0.00385745</v>
+        <v>0.003997374999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1406,19 +1406,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.0004107000000000001</v>
+        <v>0.0003655</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0012051</v>
+        <v>0.0011678</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0036779</v>
+        <v>0.0035601</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0133779</v>
+        <v>0.0133466</v>
       </c>
       <c r="G38" t="n">
-        <v>0.004667900000000001</v>
+        <v>0.00461</v>
       </c>
     </row>
     <row r="39">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.0005093000000000001</v>
+        <v>0.0005061</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0019482</v>
+        <v>0.0021872</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0090095</v>
+        <v>0.0127883</v>
       </c>
       <c r="F39" t="n">
-        <v>0.05484220000000001</v>
+        <v>0.08434139999999998</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0165773</v>
+        <v>0.02495575</v>
       </c>
     </row>
     <row r="40">
@@ -1456,19 +1456,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0005922</v>
+        <v>0.0005546</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0023443</v>
+        <v>0.0027382</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0129631</v>
+        <v>0.0163032</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0861218</v>
+        <v>0.1224412</v>
       </c>
       <c r="G40" t="n">
-        <v>0.02550535</v>
+        <v>0.0355093</v>
       </c>
     </row>
     <row r="41">
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.0006981</v>
+        <v>0.000541</v>
       </c>
       <c r="D41" t="n">
-        <v>0.002830099999999999</v>
+        <v>0.002822</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0139667</v>
+        <v>0.0177692</v>
       </c>
       <c r="F41" t="n">
-        <v>0.085648</v>
+        <v>0.1267977</v>
       </c>
       <c r="G41" t="n">
-        <v>0.025785725</v>
+        <v>0.036982475</v>
       </c>
     </row>
     <row r="42">
@@ -1506,19 +1506,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.000403</v>
+        <v>0.0004295</v>
       </c>
       <c r="D42" t="n">
-        <v>0.001654</v>
+        <v>0.0016831</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0066898</v>
+        <v>0.006527599999999999</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0271707</v>
+        <v>0.0270318</v>
       </c>
       <c r="G42" t="n">
-        <v>0.008979375</v>
+        <v>0.008918000000000001</v>
       </c>
     </row>
     <row r="43">
@@ -1531,19 +1531,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.0006057</v>
+        <v>0.0005872000000000001</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0028399</v>
+        <v>0.0030673</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0179021</v>
+        <v>0.0204914</v>
       </c>
       <c r="F43" t="n">
-        <v>0.1528052</v>
+        <v>0.1945755</v>
       </c>
       <c r="G43" t="n">
-        <v>0.04353822500000001</v>
+        <v>0.05468035</v>
       </c>
     </row>
     <row r="44">
@@ -1556,19 +1556,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.0003966</v>
+        <v>0.0003135999999999999</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0011272</v>
+        <v>0.0009923</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0032949</v>
+        <v>0.0027802</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0106684</v>
+        <v>0.008577599999999999</v>
       </c>
       <c r="G44" t="n">
-        <v>0.003871775</v>
+        <v>0.003165925</v>
       </c>
     </row>
     <row r="45">
@@ -1581,19 +1581,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.0004068</v>
+        <v>0.000273</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0014149</v>
+        <v>0.0008062</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0033747</v>
+        <v>0.002537</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0117605</v>
+        <v>0.0092368</v>
       </c>
       <c r="G45" t="n">
-        <v>0.004239224999999999</v>
+        <v>0.00321325</v>
       </c>
     </row>
     <row r="46">
@@ -1606,19 +1606,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.0003226</v>
+        <v>0.0003198</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0010937</v>
+        <v>0.0009858</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0030327</v>
+        <v>0.0030054</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0113453</v>
+        <v>0.0110127</v>
       </c>
       <c r="G46" t="n">
-        <v>0.003948574999999999</v>
+        <v>0.003830925</v>
       </c>
     </row>
     <row r="47">
@@ -1631,19 +1631,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.0003851</v>
+        <v>0.0003623</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0010217</v>
+        <v>0.001048</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0027238</v>
+        <v>0.0032298</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0114242</v>
+        <v>0.0111007</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0038887</v>
+        <v>0.003935200000000001</v>
       </c>
     </row>
     <row r="48">
@@ -1656,19 +1656,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.0007373</v>
+        <v>0.0005869</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0029201</v>
+        <v>0.0029482</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0142106</v>
+        <v>0.0179641</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0864718</v>
+        <v>0.126536</v>
       </c>
       <c r="G48" t="n">
-        <v>0.02608495</v>
+        <v>0.03700879999999999</v>
       </c>
     </row>
     <row r="49">
@@ -1681,19 +1681,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.0004337</v>
+        <v>0.000325</v>
       </c>
       <c r="D49" t="n">
-        <v>0.001344</v>
+        <v>0.0008420000000000001</v>
       </c>
       <c r="E49" t="n">
-        <v>0.003318</v>
+        <v>0.0026129</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0118754</v>
+        <v>0.009177299999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>0.004242775</v>
+        <v>0.0032393</v>
       </c>
     </row>
   </sheetData>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
         <v>44</v>
@@ -1819,7 +1819,7 @@
         <v>176</v>
       </c>
       <c r="G4" t="n">
-        <v>82.5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5">
@@ -1932,19 +1932,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E9" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="F9" t="n">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="G9" t="n">
-        <v>82.5</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="10">
@@ -2032,7 +2032,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
         <v>8</v>
@@ -2044,7 +2044,7 @@
         <v>9</v>
       </c>
       <c r="G13" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -2182,19 +2182,19 @@
         </is>
       </c>
       <c r="C19" t="n">
+        <v>18</v>
+      </c>
+      <c r="D19" t="n">
         <v>19</v>
       </c>
-      <c r="D19" t="n">
-        <v>20</v>
-      </c>
       <c r="E19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F19" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G19" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="20">
@@ -2282,19 +2282,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E23" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F23" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G23" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -2307,19 +2307,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D24" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E24" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="F24" t="n">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="G24" t="n">
-        <v>82.5</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25">
@@ -2463,13 +2463,13 @@
         <v>10</v>
       </c>
       <c r="E30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F30" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G30" t="n">
-        <v>9.5</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="31">
@@ -2485,16 +2485,16 @@
         <v>22</v>
       </c>
       <c r="D31" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E31" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="F31" t="n">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="G31" t="n">
-        <v>82.5</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32">
@@ -2532,7 +2532,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D33" t="n">
         <v>20</v>
@@ -2541,7 +2541,7 @@
         <v>20</v>
       </c>
       <c r="F33" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G33" t="n">
         <v>19.25</v>
@@ -2607,19 +2607,19 @@
         </is>
       </c>
       <c r="C36" t="n">
+        <v>8</v>
+      </c>
+      <c r="D36" t="n">
         <v>10</v>
       </c>
-      <c r="D36" t="n">
-        <v>11</v>
-      </c>
       <c r="E36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G36" t="n">
-        <v>11.75</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="37">
@@ -2682,19 +2682,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D39" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E39" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F39" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G39" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40">
@@ -2707,19 +2707,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D40" t="n">
         <v>10</v>
       </c>
       <c r="E40" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F40" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G40" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="41">
@@ -2732,19 +2732,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D41" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E41" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="F41" t="n">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="G41" t="n">
-        <v>82.5</v>
+        <v>92</v>
       </c>
     </row>
     <row r="42">
@@ -2785,16 +2785,16 @@
         <v>8</v>
       </c>
       <c r="D43" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E43" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F43" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G43" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="44">
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D44" t="n">
         <v>10</v>
@@ -2819,7 +2819,7 @@
         <v>11</v>
       </c>
       <c r="G44" t="n">
-        <v>10.25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45">
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D45" t="n">
         <v>20</v>
@@ -2844,7 +2844,7 @@
         <v>20</v>
       </c>
       <c r="G45" t="n">
-        <v>19.25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46">
@@ -2907,19 +2907,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D48" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E48" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F48" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G48" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="49">
@@ -2941,10 +2941,10 @@
         <v>10</v>
       </c>
       <c r="F49" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G49" t="n">
-        <v>10</v>
+        <v>9.75</v>
       </c>
     </row>
   </sheetData>
@@ -3058,19 +3058,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25.55634918610405</v>
+        <v>28.38477631085023</v>
       </c>
       <c r="D4" t="n">
         <v>52.52691193458119</v>
       </c>
       <c r="E4" t="n">
-        <v>106.4680374315355</v>
+        <v>107.2964645562817</v>
       </c>
       <c r="F4" t="n">
         <v>214.350288425444</v>
       </c>
       <c r="G4" t="n">
-        <v>99.72539674441619</v>
+        <v>100.6396103067893</v>
       </c>
     </row>
     <row r="5">
@@ -3183,19 +3183,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>25.55634918610405</v>
+        <v>27.55634918610405</v>
       </c>
       <c r="D9" t="n">
-        <v>52.52691193458119</v>
+        <v>56.52691193458119</v>
       </c>
       <c r="E9" t="n">
-        <v>107.2964645562817</v>
+        <v>117.7817459305202</v>
       </c>
       <c r="F9" t="n">
-        <v>215.1787155501902</v>
+        <v>235.6639969244288</v>
       </c>
       <c r="G9" t="n">
-        <v>100.1396103067893</v>
+        <v>109.3822509939086</v>
       </c>
     </row>
     <row r="10">
@@ -3283,19 +3283,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>24.41488446708389</v>
+        <v>26.22000231742804</v>
       </c>
       <c r="D13" t="n">
         <v>49.56011556674471</v>
       </c>
       <c r="E13" t="n">
-        <v>101.1164142094206</v>
+        <v>100.6044505332257</v>
       </c>
       <c r="F13" t="n">
-        <v>203.2348880049742</v>
+        <v>202.7891131507078</v>
       </c>
       <c r="G13" t="n">
-        <v>94.58157556205583</v>
+        <v>94.79342039202658</v>
       </c>
     </row>
     <row r="14">
@@ -3339,13 +3339,13 @@
         <v>54.87005768508881</v>
       </c>
       <c r="E15" t="n">
-        <v>108.6690475583121</v>
+        <v>110.3259018078045</v>
       </c>
       <c r="F15" t="n">
-        <v>217.9238815542512</v>
+        <v>221.2375900532359</v>
       </c>
       <c r="G15" t="n">
-        <v>102.254833995939</v>
+        <v>103.4974746830583</v>
       </c>
     </row>
     <row r="16">
@@ -3433,19 +3433,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>27.55634918610405</v>
+        <v>25.55634918610405</v>
       </c>
       <c r="D19" t="n">
-        <v>54.04163056034262</v>
+        <v>51.69848480983499</v>
       </c>
       <c r="E19" t="n">
-        <v>108.6690475583121</v>
+        <v>103.9827560572969</v>
       </c>
       <c r="F19" t="n">
-        <v>223.4386001800126</v>
+        <v>208.5512985522207</v>
       </c>
       <c r="G19" t="n">
-        <v>103.4264068711929</v>
+        <v>97.44722215136414</v>
       </c>
     </row>
     <row r="20">
@@ -3533,19 +3533,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24.41488446708389</v>
+        <v>26.4554706112443</v>
       </c>
       <c r="D23" t="n">
-        <v>49.60484583115361</v>
+        <v>52.67561329982938</v>
       </c>
       <c r="E23" t="n">
-        <v>101.1765739559945</v>
+        <v>108.790821278302</v>
       </c>
       <c r="F23" t="n">
-        <v>203.3015774098458</v>
+        <v>218.0487797413124</v>
       </c>
       <c r="G23" t="n">
-        <v>94.62447041601945</v>
+        <v>101.492671232672</v>
       </c>
     </row>
     <row r="24">
@@ -3558,19 +3558,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>25.55634918610405</v>
+        <v>27.55634918610405</v>
       </c>
       <c r="D24" t="n">
-        <v>52.52691193458119</v>
+        <v>56.52691193458119</v>
       </c>
       <c r="E24" t="n">
-        <v>106.4680374315355</v>
+        <v>116.953318805774</v>
       </c>
       <c r="F24" t="n">
-        <v>214.350288425444</v>
+        <v>232.8355697996826</v>
       </c>
       <c r="G24" t="n">
-        <v>99.72539674441619</v>
+        <v>108.4680374315355</v>
       </c>
     </row>
     <row r="25">
@@ -3583,7 +3583,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>27.55634918610405</v>
+        <v>26.72792206135786</v>
       </c>
       <c r="D25" t="n">
         <v>54.04163056034262</v>
@@ -3592,10 +3592,10 @@
         <v>109.4974746830583</v>
       </c>
       <c r="F25" t="n">
-        <v>218.7523086789974</v>
+        <v>222.0660171779821</v>
       </c>
       <c r="G25" t="n">
-        <v>102.4619407771256</v>
+        <v>103.0832611206852</v>
       </c>
     </row>
     <row r="26">
@@ -3692,10 +3692,10 @@
         <v>100.6044505332257</v>
       </c>
       <c r="F29" t="n">
-        <v>203.2348880049742</v>
+        <v>202.714772088272</v>
       </c>
       <c r="G29" t="n">
-        <v>94.45358464300712</v>
+        <v>94.32355566383158</v>
       </c>
     </row>
     <row r="30">
@@ -3714,13 +3714,13 @@
         <v>51.44598283082938</v>
       </c>
       <c r="E30" t="n">
-        <v>103.0023916359005</v>
+        <v>103.0999610655744</v>
       </c>
       <c r="F30" t="n">
-        <v>206.425148898921</v>
+        <v>207.3338489463796</v>
       </c>
       <c r="G30" t="n">
-        <v>96.6764618508823</v>
+        <v>96.92802922016543</v>
       </c>
     </row>
     <row r="31">
@@ -3736,16 +3736,16 @@
         <v>25.55634918610405</v>
       </c>
       <c r="D31" t="n">
-        <v>51.69848480983499</v>
+        <v>57.35533905932739</v>
       </c>
       <c r="E31" t="n">
-        <v>103.9827560572969</v>
+        <v>114.4680374315355</v>
       </c>
       <c r="F31" t="n">
-        <v>208.5512985522207</v>
+        <v>229.8650070512055</v>
       </c>
       <c r="G31" t="n">
-        <v>97.44722215136416</v>
+        <v>106.8111831820431</v>
       </c>
     </row>
     <row r="32">
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>27.55634918610405</v>
+        <v>26.72792206135786</v>
       </c>
       <c r="D33" t="n">
         <v>54.04163056034262</v>
@@ -3792,10 +3792,10 @@
         <v>108.6690475583121</v>
       </c>
       <c r="F33" t="n">
-        <v>217.9238815542512</v>
+        <v>270.0243866176395</v>
       </c>
       <c r="G33" t="n">
-        <v>102.0477272147525</v>
+        <v>114.865746699413</v>
       </c>
     </row>
     <row r="34">
@@ -3858,19 +3858,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>26.59251907515131</v>
+        <v>24.62280887594792</v>
       </c>
       <c r="D36" t="n">
-        <v>52.62700551746683</v>
+        <v>50.84539750584248</v>
       </c>
       <c r="E36" t="n">
-        <v>105.9675221282317</v>
+        <v>101.6414365392452</v>
       </c>
       <c r="F36" t="n">
-        <v>222.6622168960765</v>
+        <v>204.0006534257569</v>
       </c>
       <c r="G36" t="n">
-        <v>101.9623159042316</v>
+        <v>95.27757408669811</v>
       </c>
     </row>
     <row r="37">
@@ -3933,19 +3933,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>24.41488446708389</v>
+        <v>26.4554706112443</v>
       </c>
       <c r="D39" t="n">
-        <v>49.56011556674471</v>
+        <v>52.67561329982938</v>
       </c>
       <c r="E39" t="n">
-        <v>100.6198800153907</v>
+        <v>108.790821278302</v>
       </c>
       <c r="F39" t="n">
-        <v>203.2568471454369</v>
+        <v>217.9744386788767</v>
       </c>
       <c r="G39" t="n">
-        <v>94.46293179866406</v>
+        <v>101.4740859670631</v>
       </c>
     </row>
     <row r="40">
@@ -3958,19 +3958,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>25.71936168599622</v>
+        <v>25.94223753527842</v>
       </c>
       <c r="D40" t="n">
-        <v>51.44598283082938</v>
+        <v>51.85071541632139</v>
       </c>
       <c r="E40" t="n">
-        <v>103.0999610655744</v>
+        <v>103.5721897488897</v>
       </c>
       <c r="F40" t="n">
-        <v>206.5701584477096</v>
+        <v>208.3389878701951</v>
       </c>
       <c r="G40" t="n">
-        <v>96.7088660075274</v>
+        <v>97.42603264267115</v>
       </c>
     </row>
     <row r="41">
@@ -3983,19 +3983,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>25.55634918610405</v>
+        <v>26.72792206135786</v>
       </c>
       <c r="D41" t="n">
-        <v>52.52691193458119</v>
+        <v>54.87005768508881</v>
       </c>
       <c r="E41" t="n">
-        <v>104.8111831820431</v>
+        <v>116.4680374315355</v>
       </c>
       <c r="F41" t="n">
-        <v>209.3797256769669</v>
+        <v>234.6934341759516</v>
       </c>
       <c r="G41" t="n">
-        <v>98.0685424949238</v>
+        <v>108.1898628384834</v>
       </c>
     </row>
     <row r="42">
@@ -4036,16 +4036,16 @@
         <v>24.41488446708389</v>
       </c>
       <c r="D43" t="n">
-        <v>49.03946295574199</v>
+        <v>53.5266090104926</v>
       </c>
       <c r="E43" t="n">
-        <v>98.78888910980251</v>
+        <v>106.9151001083049</v>
       </c>
       <c r="F43" t="n">
-        <v>198.4048488856638</v>
+        <v>214.3653506435532</v>
       </c>
       <c r="G43" t="n">
-        <v>92.66202135457306</v>
+        <v>99.80548605735865</v>
       </c>
     </row>
     <row r="44">
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>26.59251907515131</v>
+        <v>25.94223753527842</v>
       </c>
       <c r="D44" t="n">
-        <v>52.12313371305741</v>
+        <v>52.1590137533636</v>
       </c>
       <c r="E44" t="n">
-        <v>104.9597785194129</v>
+        <v>104.3626331882609</v>
       </c>
       <c r="F44" t="n">
-        <v>210.8970608595957</v>
+        <v>216.807066810373</v>
       </c>
       <c r="G44" t="n">
-        <v>98.6431230418043</v>
+        <v>99.81773782181897</v>
       </c>
     </row>
     <row r="45">
@@ -4158,19 +4158,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>24.41488446708389</v>
+        <v>25.94223753527842</v>
       </c>
       <c r="D48" t="n">
-        <v>49.21635711250729</v>
+        <v>52.2265241682892</v>
       </c>
       <c r="E48" t="n">
-        <v>98.78888910980251</v>
+        <v>107.5808111303428</v>
       </c>
       <c r="F48" t="n">
-        <v>198.4048488856638</v>
+        <v>218.0501723215458</v>
       </c>
       <c r="G48" t="n">
-        <v>92.70624489376438</v>
+        <v>100.9499362888641</v>
       </c>
     </row>
     <row r="49">
@@ -4183,19 +4183,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>25.71936168599622</v>
+        <v>25.94223753527842</v>
       </c>
       <c r="D49" t="n">
-        <v>52.12313371305741</v>
+        <v>52.1590137533636</v>
       </c>
       <c r="E49" t="n">
-        <v>104.9597785194129</v>
+        <v>104.3626331882609</v>
       </c>
       <c r="F49" t="n">
-        <v>210.8970608595957</v>
+        <v>209.4868100138525</v>
       </c>
       <c r="G49" t="n">
-        <v>98.42483369451554</v>
+        <v>97.98767362268885</v>
       </c>
     </row>
   </sheetData>
@@ -4309,19 +4309,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D4" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="E4" t="n">
-        <v>276</v>
+        <v>331</v>
       </c>
       <c r="F4" t="n">
-        <v>606</v>
+        <v>836</v>
       </c>
       <c r="G4" t="n">
-        <v>252.75</v>
+        <v>327.75</v>
       </c>
     </row>
     <row r="5">
@@ -4434,19 +4434,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D9" t="n">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="E9" t="n">
-        <v>287</v>
+        <v>396</v>
       </c>
       <c r="F9" t="n">
-        <v>616</v>
+        <v>1009</v>
       </c>
       <c r="G9" t="n">
-        <v>262</v>
+        <v>396.75</v>
       </c>
     </row>
     <row r="10">
@@ -4534,19 +4534,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="E13" t="n">
-        <v>276</v>
+        <v>331</v>
       </c>
       <c r="F13" t="n">
-        <v>606</v>
+        <v>836</v>
       </c>
       <c r="G13" t="n">
-        <v>252.75</v>
+        <v>327.75</v>
       </c>
     </row>
     <row r="14">
@@ -4562,16 +4562,16 @@
         <v>33</v>
       </c>
       <c r="D14" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="E14" t="n">
-        <v>256</v>
+        <v>365</v>
       </c>
       <c r="F14" t="n">
-        <v>628</v>
+        <v>833</v>
       </c>
       <c r="G14" t="n">
-        <v>253</v>
+        <v>333.25</v>
       </c>
     </row>
     <row r="15">
@@ -4587,16 +4587,16 @@
         <v>29</v>
       </c>
       <c r="D15" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E15" t="n">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="F15" t="n">
-        <v>455</v>
+        <v>432</v>
       </c>
       <c r="G15" t="n">
-        <v>196.25</v>
+        <v>189.25</v>
       </c>
     </row>
     <row r="16">
@@ -4684,16 +4684,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E19" t="n">
         <v>13</v>
       </c>
       <c r="F19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G19" t="n">
         <v>12.75</v>
@@ -4784,19 +4784,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D23" t="n">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="E23" t="n">
-        <v>287</v>
+        <v>396</v>
       </c>
       <c r="F23" t="n">
-        <v>616</v>
+        <v>1009</v>
       </c>
       <c r="G23" t="n">
-        <v>262</v>
+        <v>396.75</v>
       </c>
     </row>
     <row r="24">
@@ -4809,19 +4809,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D24" t="n">
-        <v>92</v>
+        <v>145</v>
       </c>
       <c r="E24" t="n">
-        <v>249</v>
+        <v>427</v>
       </c>
       <c r="F24" t="n">
-        <v>508</v>
+        <v>1001</v>
       </c>
       <c r="G24" t="n">
-        <v>220.75</v>
+        <v>403.75</v>
       </c>
     </row>
     <row r="25">
@@ -4834,19 +4834,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D25" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="E25" t="n">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="F25" t="n">
-        <v>475</v>
+        <v>494</v>
       </c>
       <c r="G25" t="n">
-        <v>207.25</v>
+        <v>213.25</v>
       </c>
     </row>
     <row r="26">
@@ -4937,16 +4937,16 @@
         <v>33</v>
       </c>
       <c r="D29" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="E29" t="n">
-        <v>256</v>
+        <v>365</v>
       </c>
       <c r="F29" t="n">
-        <v>628</v>
+        <v>833</v>
       </c>
       <c r="G29" t="n">
-        <v>253</v>
+        <v>333.25</v>
       </c>
     </row>
     <row r="30">
@@ -4962,16 +4962,16 @@
         <v>29</v>
       </c>
       <c r="D30" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E30" t="n">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="F30" t="n">
-        <v>455</v>
+        <v>432</v>
       </c>
       <c r="G30" t="n">
-        <v>196.25</v>
+        <v>189.25</v>
       </c>
     </row>
     <row r="31">
@@ -4987,16 +4987,16 @@
         <v>28</v>
       </c>
       <c r="D31" t="n">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="E31" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F31" t="n">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="G31" t="n">
-        <v>221.5</v>
+        <v>226.75</v>
       </c>
     </row>
     <row r="32">
@@ -5034,19 +5034,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D33" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E33" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F33" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G33" t="n">
-        <v>15.75</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="34">
@@ -5109,16 +5109,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D36" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E36" t="n">
         <v>13</v>
       </c>
       <c r="F36" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G36" t="n">
         <v>12.75</v>
@@ -5137,16 +5137,16 @@
         <v>12</v>
       </c>
       <c r="D37" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E37" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F37" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G37" t="n">
-        <v>12</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="38">
@@ -5184,19 +5184,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D39" t="n">
-        <v>92</v>
+        <v>145</v>
       </c>
       <c r="E39" t="n">
-        <v>249</v>
+        <v>427</v>
       </c>
       <c r="F39" t="n">
-        <v>508</v>
+        <v>1001</v>
       </c>
       <c r="G39" t="n">
-        <v>220.75</v>
+        <v>403.75</v>
       </c>
     </row>
     <row r="40">
@@ -5209,19 +5209,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D40" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="E40" t="n">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="F40" t="n">
-        <v>475</v>
+        <v>494</v>
       </c>
       <c r="G40" t="n">
-        <v>207.25</v>
+        <v>213.25</v>
       </c>
     </row>
     <row r="41">
@@ -5234,19 +5234,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D41" t="n">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="E41" t="n">
-        <v>279</v>
+        <v>318</v>
       </c>
       <c r="F41" t="n">
-        <v>605</v>
+        <v>675</v>
       </c>
       <c r="G41" t="n">
-        <v>259.5</v>
+        <v>282.5</v>
       </c>
     </row>
     <row r="42">
@@ -5287,16 +5287,16 @@
         <v>28</v>
       </c>
       <c r="D43" t="n">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="E43" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F43" t="n">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="G43" t="n">
-        <v>221.5</v>
+        <v>226.75</v>
       </c>
     </row>
     <row r="44">
@@ -5309,19 +5309,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D44" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E44" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F44" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G44" t="n">
-        <v>15.75</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="45">
@@ -5337,13 +5337,13 @@
         <v>13</v>
       </c>
       <c r="D45" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E45" t="n">
         <v>18</v>
       </c>
       <c r="F45" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G45" t="n">
         <v>17</v>
@@ -5387,16 +5387,16 @@
         <v>12</v>
       </c>
       <c r="D47" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E47" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F47" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G47" t="n">
-        <v>12</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="48">
@@ -5409,19 +5409,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D48" t="n">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="E48" t="n">
-        <v>279</v>
+        <v>318</v>
       </c>
       <c r="F48" t="n">
-        <v>605</v>
+        <v>675</v>
       </c>
       <c r="G48" t="n">
-        <v>259.5</v>
+        <v>282.5</v>
       </c>
     </row>
     <row r="49">
@@ -5437,13 +5437,13 @@
         <v>13</v>
       </c>
       <c r="D49" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E49" t="n">
         <v>18</v>
       </c>
       <c r="F49" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G49" t="n">
         <v>17</v>
@@ -5560,19 +5560,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E4" t="n">
-        <v>365</v>
+        <v>395</v>
       </c>
       <c r="F4" t="n">
-        <v>2113</v>
+        <v>1847</v>
       </c>
       <c r="G4" t="n">
-        <v>646.75</v>
+        <v>588</v>
       </c>
     </row>
     <row r="5">
@@ -5685,19 +5685,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D9" t="n">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E9" t="n">
-        <v>463</v>
+        <v>494</v>
       </c>
       <c r="F9" t="n">
-        <v>1824</v>
+        <v>2034</v>
       </c>
       <c r="G9" t="n">
-        <v>613</v>
+        <v>668.75</v>
       </c>
     </row>
     <row r="10">
@@ -5785,19 +5785,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D13" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E13" t="n">
-        <v>365</v>
+        <v>395</v>
       </c>
       <c r="F13" t="n">
-        <v>2113</v>
+        <v>1847</v>
       </c>
       <c r="G13" t="n">
-        <v>646.75</v>
+        <v>588</v>
       </c>
     </row>
     <row r="14">
@@ -5810,19 +5810,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>439</v>
       </c>
       <c r="F14" t="n">
-        <v>2096</v>
+        <v>2007</v>
       </c>
       <c r="G14" t="n">
-        <v>639.75</v>
+        <v>636.75</v>
       </c>
     </row>
     <row r="15">
@@ -5835,19 +5835,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
         <v>110</v>
       </c>
       <c r="E15" t="n">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="F15" t="n">
-        <v>2444</v>
+        <v>2368</v>
       </c>
       <c r="G15" t="n">
-        <v>767.75</v>
+        <v>748.75</v>
       </c>
     </row>
     <row r="16">
@@ -5938,16 +5938,16 @@
         <v>20</v>
       </c>
       <c r="D19" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E19" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F19" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G19" t="n">
-        <v>31.25</v>
+        <v>29.75</v>
       </c>
     </row>
     <row r="20">
@@ -6035,19 +6035,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D23" t="n">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E23" t="n">
-        <v>463</v>
+        <v>494</v>
       </c>
       <c r="F23" t="n">
-        <v>1824</v>
+        <v>2034</v>
       </c>
       <c r="G23" t="n">
-        <v>613</v>
+        <v>668.75</v>
       </c>
     </row>
     <row r="24">
@@ -6060,19 +6060,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D24" t="n">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="E24" t="n">
-        <v>478</v>
+        <v>498</v>
       </c>
       <c r="F24" t="n">
-        <v>1954</v>
+        <v>1977</v>
       </c>
       <c r="G24" t="n">
-        <v>650</v>
+        <v>654</v>
       </c>
     </row>
     <row r="25">
@@ -6085,19 +6085,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D25" t="n">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="E25" t="n">
-        <v>605</v>
+        <v>586</v>
       </c>
       <c r="F25" t="n">
-        <v>2384</v>
+        <v>2504</v>
       </c>
       <c r="G25" t="n">
-        <v>800</v>
+        <v>819.75</v>
       </c>
     </row>
     <row r="26">
@@ -6185,19 +6185,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D29" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>439</v>
       </c>
       <c r="F29" t="n">
-        <v>2096</v>
+        <v>2007</v>
       </c>
       <c r="G29" t="n">
-        <v>639.75</v>
+        <v>636.75</v>
       </c>
     </row>
     <row r="30">
@@ -6210,19 +6210,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D30" t="n">
         <v>110</v>
       </c>
       <c r="E30" t="n">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="F30" t="n">
-        <v>2444</v>
+        <v>2368</v>
       </c>
       <c r="G30" t="n">
-        <v>767.75</v>
+        <v>748.75</v>
       </c>
     </row>
     <row r="31">
@@ -6235,19 +6235,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D31" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E31" t="n">
-        <v>454</v>
+        <v>478</v>
       </c>
       <c r="F31" t="n">
-        <v>2132</v>
+        <v>2594</v>
       </c>
       <c r="G31" t="n">
-        <v>683.25</v>
+        <v>804.5</v>
       </c>
     </row>
     <row r="32">
@@ -6285,19 +6285,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D33" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E33" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F33" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="G33" t="n">
-        <v>34.5</v>
+        <v>25.75</v>
       </c>
     </row>
     <row r="34">
@@ -6363,16 +6363,16 @@
         <v>20</v>
       </c>
       <c r="D36" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E36" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F36" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G36" t="n">
-        <v>31.25</v>
+        <v>29.75</v>
       </c>
     </row>
     <row r="37">
@@ -6385,19 +6385,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D37" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E37" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F37" t="n">
         <v>38</v>
       </c>
       <c r="G37" t="n">
-        <v>31</v>
+        <v>33.25</v>
       </c>
     </row>
     <row r="38">
@@ -6435,19 +6435,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D39" t="n">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="E39" t="n">
-        <v>478</v>
+        <v>498</v>
       </c>
       <c r="F39" t="n">
-        <v>1954</v>
+        <v>1977</v>
       </c>
       <c r="G39" t="n">
-        <v>650</v>
+        <v>654</v>
       </c>
     </row>
     <row r="40">
@@ -6460,19 +6460,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D40" t="n">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="E40" t="n">
-        <v>605</v>
+        <v>586</v>
       </c>
       <c r="F40" t="n">
-        <v>2384</v>
+        <v>2504</v>
       </c>
       <c r="G40" t="n">
-        <v>800</v>
+        <v>819.75</v>
       </c>
     </row>
     <row r="41">
@@ -6485,19 +6485,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="D41" t="n">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="E41" t="n">
-        <v>657</v>
+        <v>616</v>
       </c>
       <c r="F41" t="n">
-        <v>2515</v>
+        <v>2588</v>
       </c>
       <c r="G41" t="n">
-        <v>851.75</v>
+        <v>848</v>
       </c>
     </row>
     <row r="42">
@@ -6535,19 +6535,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D43" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E43" t="n">
-        <v>454</v>
+        <v>478</v>
       </c>
       <c r="F43" t="n">
-        <v>2132</v>
+        <v>2594</v>
       </c>
       <c r="G43" t="n">
-        <v>683.25</v>
+        <v>804.5</v>
       </c>
     </row>
     <row r="44">
@@ -6560,19 +6560,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D44" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E44" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F44" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="G44" t="n">
-        <v>34.5</v>
+        <v>25.75</v>
       </c>
     </row>
     <row r="45">
@@ -6585,19 +6585,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D45" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E45" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="F45" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="G45" t="n">
-        <v>35.75</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="46">
@@ -6635,19 +6635,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D47" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E47" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F47" t="n">
         <v>38</v>
       </c>
       <c r="G47" t="n">
-        <v>31</v>
+        <v>33.25</v>
       </c>
     </row>
     <row r="48">
@@ -6660,19 +6660,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="D48" t="n">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="E48" t="n">
-        <v>657</v>
+        <v>616</v>
       </c>
       <c r="F48" t="n">
-        <v>2515</v>
+        <v>2588</v>
       </c>
       <c r="G48" t="n">
-        <v>851.75</v>
+        <v>848</v>
       </c>
     </row>
     <row r="49">
@@ -6685,19 +6685,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D49" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E49" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="F49" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="G49" t="n">
-        <v>35.75</v>
+        <v>25.5</v>
       </c>
     </row>
   </sheetData>
@@ -6814,10 +6814,10 @@
         <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F4" t="n">
         <v>24</v>
@@ -6939,16 +6939,16 @@
         <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E9" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F9" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G9" t="n">
-        <v>14.25</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="10">
@@ -7036,7 +7036,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
         <v>6</v>
@@ -7048,7 +7048,7 @@
         <v>7</v>
       </c>
       <c r="G13" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -7061,19 +7061,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
         <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F14" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G14" t="n">
-        <v>13.75</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="15">
@@ -7086,19 +7086,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E15" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F15" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G15" t="n">
-        <v>18.75</v>
+        <v>21.75</v>
       </c>
     </row>
     <row r="16">
@@ -7186,19 +7186,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E19" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F19" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G19" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
@@ -7286,19 +7286,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G23" t="n">
-        <v>6.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -7314,16 +7314,16 @@
         <v>11</v>
       </c>
       <c r="D24" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E24" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F24" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G24" t="n">
-        <v>12.25</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="25">
@@ -7336,19 +7336,19 @@
         </is>
       </c>
       <c r="C25" t="n">
+        <v>10</v>
+      </c>
+      <c r="D25" t="n">
+        <v>12</v>
+      </c>
+      <c r="E25" t="n">
         <v>16</v>
       </c>
-      <c r="D25" t="n">
-        <v>16</v>
-      </c>
-      <c r="E25" t="n">
-        <v>24</v>
-      </c>
       <c r="F25" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G25" t="n">
-        <v>21</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="26">
@@ -7467,13 +7467,13 @@
         <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G30" t="n">
-        <v>7.5</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="31">
@@ -7486,19 +7486,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D31" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E31" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F31" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G31" t="n">
-        <v>11.75</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="32">
@@ -7536,19 +7536,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D33" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E33" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F33" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G33" t="n">
-        <v>13.75</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="34">
@@ -7611,19 +7611,19 @@
         </is>
       </c>
       <c r="C36" t="n">
+        <v>6</v>
+      </c>
+      <c r="D36" t="n">
         <v>8</v>
       </c>
-      <c r="D36" t="n">
-        <v>9</v>
-      </c>
       <c r="E36" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F36" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G36" t="n">
-        <v>9.75</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="37">
@@ -7686,19 +7686,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E39" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F39" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G39" t="n">
-        <v>6.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40">
@@ -7717,13 +7717,13 @@
         <v>8</v>
       </c>
       <c r="E40" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F40" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G40" t="n">
-        <v>7.75</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="41">
@@ -7736,19 +7736,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D41" t="n">
         <v>13</v>
       </c>
       <c r="E41" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F41" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G41" t="n">
-        <v>13.5</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="42">
@@ -7789,16 +7789,16 @@
         <v>6</v>
       </c>
       <c r="D43" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E43" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F43" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G43" t="n">
-        <v>6</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="44">
@@ -7811,7 +7811,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D44" t="n">
         <v>8</v>
@@ -7823,7 +7823,7 @@
         <v>9</v>
       </c>
       <c r="G44" t="n">
-        <v>8.25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
@@ -7836,19 +7836,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D45" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E45" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F45" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G45" t="n">
-        <v>13.75</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="46">
@@ -7911,19 +7911,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D48" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E48" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F48" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G48" t="n">
-        <v>6</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="49">
@@ -7945,10 +7945,10 @@
         <v>8</v>
       </c>
       <c r="F49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G49" t="n">
-        <v>8</v>
+        <v>7.75</v>
       </c>
     </row>
   </sheetData>
@@ -8037,16 +8037,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D4" t="n">
-        <v>641</v>
+        <v>726</v>
       </c>
       <c r="E4" t="n">
-        <v>2719</v>
+        <v>2683</v>
       </c>
     </row>
     <row r="5">
@@ -8132,16 +8132,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>231</v>
+        <v>253</v>
       </c>
       <c r="D9" t="n">
-        <v>750</v>
+        <v>890</v>
       </c>
       <c r="E9" t="n">
-        <v>2440</v>
+        <v>3043</v>
       </c>
     </row>
     <row r="10">
@@ -8208,16 +8208,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="C13" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D13" t="n">
-        <v>641</v>
+        <v>726</v>
       </c>
       <c r="E13" t="n">
-        <v>2719</v>
+        <v>2683</v>
       </c>
     </row>
     <row r="14">
@@ -8227,16 +8227,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C14" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D14" t="n">
-        <v>609</v>
+        <v>804</v>
       </c>
       <c r="E14" t="n">
-        <v>2724</v>
+        <v>2840</v>
       </c>
     </row>
     <row r="15">
@@ -8246,16 +8246,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C15" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D15" t="n">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="E15" t="n">
-        <v>2899</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="16">
@@ -8322,16 +8322,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C19" t="n">
         <v>42</v>
       </c>
       <c r="D19" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E19" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20">
@@ -8398,16 +8398,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C23" t="n">
-        <v>231</v>
+        <v>253</v>
       </c>
       <c r="D23" t="n">
-        <v>750</v>
+        <v>890</v>
       </c>
       <c r="E23" t="n">
-        <v>2440</v>
+        <v>3043</v>
       </c>
     </row>
     <row r="24">
@@ -8417,16 +8417,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C24" t="n">
-        <v>220</v>
+        <v>252</v>
       </c>
       <c r="D24" t="n">
-        <v>727</v>
+        <v>925</v>
       </c>
       <c r="E24" t="n">
-        <v>2462</v>
+        <v>2978</v>
       </c>
     </row>
     <row r="25">
@@ -8436,16 +8436,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C25" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D25" t="n">
-        <v>835</v>
+        <v>809</v>
       </c>
       <c r="E25" t="n">
-        <v>2859</v>
+        <v>2998</v>
       </c>
     </row>
     <row r="26">
@@ -8512,16 +8512,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C29" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D29" t="n">
-        <v>609</v>
+        <v>804</v>
       </c>
       <c r="E29" t="n">
-        <v>2724</v>
+        <v>2840</v>
       </c>
     </row>
     <row r="30">
@@ -8531,16 +8531,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C30" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D30" t="n">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="E30" t="n">
-        <v>2899</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="31">
@@ -8550,16 +8550,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C31" t="n">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="D31" t="n">
-        <v>688</v>
+        <v>713</v>
       </c>
       <c r="E31" t="n">
-        <v>2663</v>
+        <v>3131</v>
       </c>
     </row>
     <row r="32">
@@ -8588,16 +8588,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C33" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D33" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34">
@@ -8645,16 +8645,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C36" t="n">
         <v>42</v>
       </c>
       <c r="D36" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E36" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37">
@@ -8664,16 +8664,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C37" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D37" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E37" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38">
@@ -8702,16 +8702,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C39" t="n">
-        <v>220</v>
+        <v>252</v>
       </c>
       <c r="D39" t="n">
-        <v>727</v>
+        <v>925</v>
       </c>
       <c r="E39" t="n">
-        <v>2462</v>
+        <v>2978</v>
       </c>
     </row>
     <row r="40">
@@ -8721,16 +8721,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C40" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D40" t="n">
-        <v>835</v>
+        <v>809</v>
       </c>
       <c r="E40" t="n">
-        <v>2859</v>
+        <v>2998</v>
       </c>
     </row>
     <row r="41">
@@ -8740,16 +8740,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="C41" t="n">
-        <v>295</v>
+        <v>256</v>
       </c>
       <c r="D41" t="n">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="E41" t="n">
-        <v>3120</v>
+        <v>3263</v>
       </c>
     </row>
     <row r="42">
@@ -8778,16 +8778,16 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C43" t="n">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="D43" t="n">
-        <v>688</v>
+        <v>713</v>
       </c>
       <c r="E43" t="n">
-        <v>2663</v>
+        <v>3131</v>
       </c>
     </row>
     <row r="44">
@@ -8797,16 +8797,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C44" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D44" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
     </row>
     <row r="45">
@@ -8816,16 +8816,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C45" t="n">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="D45" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="E45" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="46">
@@ -8854,16 +8854,16 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C47" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D47" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E47" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="48">
@@ -8873,16 +8873,16 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="C48" t="n">
-        <v>295</v>
+        <v>256</v>
       </c>
       <c r="D48" t="n">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="E48" t="n">
-        <v>3120</v>
+        <v>3263</v>
       </c>
     </row>
     <row r="49">
@@ -8892,16 +8892,16 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C49" t="n">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="D49" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="E49" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
